--- a/ai収集/分析_新台診断_v0.3.xlsx
+++ b/ai収集/分析_新台診断_v0.3.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +47,11 @@
     <font>
       <color rgb="00555555"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
     </font>
     <font>
       <color rgb="00C77B00"/>
@@ -110,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -133,8 +138,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -506,16 +514,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="115" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>新台診断テーブル ― 指標の説明</t>
+          <t>新台診断テーブル ― 指標の説明（2軸: 稼働値×持続率）</t>
         </is>
       </c>
     </row>
@@ -525,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>【目的】台数やIPは“入口”でしかなく、台の生死を決めるのは『波が客を離さない力＝持続率』。それを早期に数値化して優秀/危険を見抜く。</t>
+          <t>【考え方】台数やIPは“入口”でしかない。台の生死は『人気(稼働値)』と『定着(持続率)』の2軸で決まる。2週で仮説→4週/8週で検証。</t>
         </is>
       </c>
     </row>
@@ -535,80 +543,104 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>● 初月持続率(4週) = 4週目アウト ÷ 初週アウト</t>
+          <t>● 稼働値 = アウト ÷ その週の全機種アウト中央値 ×100（人気・絶対需要。市場が来たか）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   判定: 優秀≥66% / 注意≥50% / 危険&lt;50%。実データで長寿台の平均66%・短命台47%と明確に分かれた中核指標。</t>
+          <t xml:space="preserve">   寿命別平均: 長寿 初週335%/2週291% ・ 短命 初週262%/2週190%。判別力1.0前後で有効。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>● 2週持続率 = 2週目アウト ÷ 初週アウト</t>
+          <t>● 持続率 = ◯週目アウト ÷ 初週アウト ×100（定着・減衰）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   出て間もない新台(4週未満)の早期サイン。暫定判定: 優秀≥83% / 注意≥73% / 危険&lt;73%（較正値）。</t>
+          <t xml:space="preserve">   初月(4週): 優秀≥66/注意≥50/危険&lt;50（長寿66 vs 短命47）。2週: 長寿86 vs 短命72。判別力最強(1.31)。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>● 8週持続率 = 8週目アウト ÷ 初週アウト  … 中期の定着度。</t>
+          <t>● 8週持続率 … 中期の定着度。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>● 台数(初週→現在 / 推移% / ピーク) = 1店あたり平均設置台数の変化。減少=店が見切って撤去。</t>
+          <t>● 台数(初週→現在 / 推移% / ピーク) = 1店あたり平均設置台数の変化。減少=店が撤去。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ⚠ 大量導入(ピーク≥6台)なのに初月持続率が低い → 『供給過剰の疑い』(戦国乙女型)。台数で稼ぎ初動は出るが客が薄まり失速。</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>● 稼働貢献週 / 状況 = SISで稼働を計上した週数と継続中/終了（『◯週継続中』『◯週で終了』）。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>● 稼働貢献週 / 状況 = SISで稼働を計上した週数と、継続中/終了。『◯週継続中』『◯週で終了』。</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>● 判定 = 4週が揃えばその基準、まだ揃わない新台は2週基準(暫定)。『計測中』は2週も未到達。</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>【判定ロジック】</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・4週が揃う → 初月持続率で確定: 優秀≥66% / 注意≥50% / 危険&lt;50%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>【補足・数字の罠】機械割(設定6)は規則で全台115%未満に張り付き＝比較情報価値ゼロ。型式試験は1回約181万円・適合率10〜20%で“運”要素大。</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・4週未到達(新台) → 2週で暫定: 稼働値≥260%かつ持続率≥83%=優秀 / 稼働値&lt;190%または持続率&lt;73%=危険 / 中間=注意</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>【データ源】SIS週次(sis_weekly_data)。生成: scripts/misc/build_diagnosis_table.py。直近の週次更新に追従。</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・2週も未到達 → 計測中</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・⚠供給過剰 = 大量導入(台数ピーク≥6)なのに判定が注意/危険（戦国乙女型。台数で初動は出るが客が薄まる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>【非採用】割数(判別力0.34)・台数初動(0.7)は寿命をほぼ分けず材料にしない。機械割(設定6)は規則で全台115%未満に張付き＝比較情報ゼロ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>【データ源】SIS週次(sis_weekly_data)。生成: scripts/misc/build_diagnosis_table.py。週次更新に追従。</t>
         </is>
       </c>
     </row>
@@ -623,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M189"/>
+  <dimension ref="A1:O189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -632,84 +664,96 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>※直近導入順。判定/しきい値の意味は『説明』シート参照。</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>※直近導入順。判定/しきい値の意味は『説明』シート参照。稼働値=アウト÷週中央値、持続率=◯週÷初週。</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>機種</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>初週</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>継続表示</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>稼働貢献週</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>状況</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>初週稼働値</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>2週稼働値</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>2週持続率</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>初月持続率(4週)</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>8週持続率</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="K2" s="10" t="inlineStr">
         <is>
           <t>台数初週</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="L2" s="10" t="inlineStr">
         <is>
           <t>台数現在</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t>台数ピーク</t>
         </is>
       </c>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>台数推移%</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr">
+      <c r="O2" s="10" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
@@ -740,21 +784,27 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>289</v>
+      </c>
+      <c r="G3" t="n">
+        <v>205</v>
+      </c>
+      <c r="H3" t="n">
         <v>72</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
       </c>
       <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" s="10" t="inlineStr">
+      <c r="O3" s="11" t="inlineStr">
         <is>
           <t>危険(暫定)</t>
         </is>
@@ -785,28 +835,34 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>484</v>
+      </c>
+      <c r="G4" t="n">
+        <v>452</v>
+      </c>
+      <c r="H4" t="n">
         <v>94</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
       </c>
       <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>優秀(暫定)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>L戦国乙女5業火を穿つ宿焔の双刃</t>
         </is>
@@ -830,21 +886,27 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>500</v>
+      </c>
+      <c r="G5" t="n">
+        <v>461</v>
+      </c>
+      <c r="H5" t="n">
         <v>93</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>6.5</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>6.7</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>6.7</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>優秀(暫定)</t>
         </is>
@@ -875,24 +937,30 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>302</v>
+      </c>
+      <c r="G6" t="n">
+        <v>230</v>
+      </c>
+      <c r="H6" t="n">
         <v>78</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>53</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.2</v>
       </c>
       <c r="K6" t="n">
         <v>1.2</v>
       </c>
       <c r="L6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="13" t="inlineStr">
+      <c r="O6" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -923,24 +991,30 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>398</v>
+      </c>
+      <c r="G7" t="n">
+        <v>332</v>
+      </c>
+      <c r="H7" t="n">
         <v>83</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>65</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>3.1</v>
       </c>
       <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N7" t="n">
         <v>-3</v>
       </c>
-      <c r="M7" s="13" t="inlineStr">
+      <c r="O7" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -971,24 +1045,30 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>388</v>
+      </c>
+      <c r="G8" t="n">
+        <v>323</v>
+      </c>
+      <c r="H8" t="n">
         <v>83</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>66</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.7</v>
       </c>
       <c r="K8" t="n">
         <v>1.7</v>
       </c>
       <c r="L8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="11" t="inlineStr">
+      <c r="O8" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1019,24 +1099,30 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>380</v>
+      </c>
+      <c r="G9" t="n">
+        <v>298</v>
+      </c>
+      <c r="H9" t="n">
         <v>78</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>53</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.3</v>
       </c>
       <c r="K9" t="n">
         <v>4.7</v>
       </c>
       <c r="L9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N9" t="n">
         <v>-9</v>
       </c>
-      <c r="M9" s="13" t="inlineStr">
+      <c r="O9" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1067,24 +1153,30 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>352</v>
+      </c>
+      <c r="G10" t="n">
+        <v>285</v>
+      </c>
+      <c r="H10" t="n">
         <v>80</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>56</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>4.1</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>3.9</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>4.2</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>-5</v>
       </c>
-      <c r="M10" s="13" t="inlineStr">
+      <c r="O10" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1115,27 +1207,33 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>278</v>
+      </c>
+      <c r="G11" t="n">
+        <v>237</v>
+      </c>
+      <c r="H11" t="n">
         <v>101</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>71</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>56</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.3</v>
       </c>
       <c r="K11" t="n">
         <v>1.4</v>
       </c>
       <c r="L11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N11" t="n">
         <v>-7</v>
       </c>
-      <c r="M11" s="11" t="inlineStr">
+      <c r="O11" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1166,27 +1264,33 @@
         </is>
       </c>
       <c r="F12" t="n">
+        <v>457</v>
+      </c>
+      <c r="G12" t="n">
+        <v>371</v>
+      </c>
+      <c r="H12" t="n">
         <v>96</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>69</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>53</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>8.4</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>8.5</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>8.6</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="M12" s="11" t="inlineStr">
+      <c r="O12" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1217,27 +1321,33 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>318</v>
+      </c>
+      <c r="G13" t="n">
+        <v>206</v>
+      </c>
+      <c r="H13" t="n">
         <v>76</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>33</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>18</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.2</v>
       </c>
       <c r="K13" t="n">
         <v>3.3</v>
       </c>
       <c r="L13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N13" t="n">
         <v>-33</v>
       </c>
-      <c r="M13" s="10" t="inlineStr">
+      <c r="O13" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -1268,27 +1378,33 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>343</v>
+      </c>
+      <c r="G14" t="n">
+        <v>296</v>
+      </c>
+      <c r="H14" t="n">
         <v>85</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>75</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>52</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.5</v>
       </c>
       <c r="K14" t="n">
         <v>1.5</v>
       </c>
       <c r="L14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="11" t="inlineStr">
+      <c r="O14" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1319,27 +1435,33 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>357</v>
+      </c>
+      <c r="G15" t="n">
+        <v>289</v>
+      </c>
+      <c r="H15" t="n">
         <v>80</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>60</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>33</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.4</v>
       </c>
       <c r="K15" t="n">
         <v>1.7</v>
       </c>
       <c r="L15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N15" t="n">
         <v>-18</v>
       </c>
-      <c r="M15" s="13" t="inlineStr">
+      <c r="O15" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1370,27 +1492,33 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>378</v>
+      </c>
+      <c r="G16" t="n">
+        <v>299</v>
+      </c>
+      <c r="H16" t="n">
         <v>78</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>56</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>27</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.9</v>
       </c>
       <c r="K16" t="n">
         <v>2.4</v>
       </c>
       <c r="L16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N16" t="n">
         <v>-21</v>
       </c>
-      <c r="M16" s="13" t="inlineStr">
+      <c r="O16" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1421,27 +1549,33 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>403</v>
+      </c>
+      <c r="G17" t="n">
+        <v>380</v>
+      </c>
+      <c r="H17" t="n">
         <v>93</v>
       </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
         <v>80</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>66</v>
-      </c>
-      <c r="I17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.7</v>
       </c>
       <c r="K17" t="n">
         <v>3.7</v>
       </c>
       <c r="L17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N17" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="11" t="inlineStr">
+      <c r="O17" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1472,27 +1606,33 @@
         </is>
       </c>
       <c r="F18" t="n">
+        <v>406</v>
+      </c>
+      <c r="G18" t="n">
+        <v>366</v>
+      </c>
+      <c r="H18" t="n">
         <v>89</v>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>76</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>48</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.5</v>
       </c>
       <c r="K18" t="n">
         <v>1.6</v>
       </c>
       <c r="L18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N18" t="n">
         <v>-6</v>
       </c>
-      <c r="M18" s="11" t="inlineStr">
+      <c r="O18" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1523,27 +1663,33 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>315</v>
+      </c>
+      <c r="G19" t="n">
+        <v>278</v>
+      </c>
+      <c r="H19" t="n">
         <v>81</v>
       </c>
-      <c r="G19" t="n">
+      <c r="I19" t="n">
         <v>67</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>63</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
       </c>
       <c r="K19" t="n">
         <v>2.1</v>
       </c>
       <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N19" t="n">
         <v>-5</v>
       </c>
-      <c r="M19" s="11" t="inlineStr">
+      <c r="O19" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1574,27 +1720,33 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>462</v>
+      </c>
+      <c r="G20" t="n">
+        <v>479</v>
+      </c>
+      <c r="H20" t="n">
         <v>95</v>
       </c>
-      <c r="G20" t="n">
+      <c r="I20" t="n">
         <v>84</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>66</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>9.9</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>9.9</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>12</v>
       </c>
-      <c r="M20" s="11" t="inlineStr">
+      <c r="O20" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1625,27 +1777,33 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>441</v>
+      </c>
+      <c r="G21" t="n">
+        <v>436</v>
+      </c>
+      <c r="H21" t="n">
         <v>101</v>
       </c>
-      <c r="G21" t="n">
+      <c r="I21" t="n">
         <v>97</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>79</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>1.4</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>1.6</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>1.6</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>14</v>
       </c>
-      <c r="M21" s="11" t="inlineStr">
+      <c r="O21" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1676,27 +1834,33 @@
         </is>
       </c>
       <c r="F22" t="n">
+        <v>345</v>
+      </c>
+      <c r="G22" t="n">
+        <v>269</v>
+      </c>
+      <c r="H22" t="n">
         <v>80</v>
       </c>
-      <c r="G22" t="n">
+      <c r="I22" t="n">
         <v>53</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>25</v>
-      </c>
-      <c r="I22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1.4</v>
       </c>
       <c r="K22" t="n">
         <v>3.6</v>
       </c>
       <c r="L22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N22" t="n">
         <v>-61</v>
       </c>
-      <c r="M22" s="13" t="inlineStr">
+      <c r="O22" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1727,27 +1891,33 @@
         </is>
       </c>
       <c r="F23" t="n">
+        <v>354</v>
+      </c>
+      <c r="G23" t="n">
+        <v>296</v>
+      </c>
+      <c r="H23" t="n">
         <v>86</v>
       </c>
-      <c r="G23" t="n">
+      <c r="I23" t="n">
         <v>71</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>52</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>3</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>2.9</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>3.1</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>-3</v>
       </c>
-      <c r="M23" s="11" t="inlineStr">
+      <c r="O23" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1778,27 +1948,33 @@
         </is>
       </c>
       <c r="F24" t="n">
+        <v>416</v>
+      </c>
+      <c r="G24" t="n">
+        <v>376</v>
+      </c>
+      <c r="H24" t="n">
         <v>93</v>
       </c>
-      <c r="G24" t="n">
+      <c r="I24" t="n">
         <v>83</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>60</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.7</v>
       </c>
       <c r="K24" t="n">
         <v>2.7</v>
       </c>
       <c r="L24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N24" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="11" t="inlineStr">
+      <c r="O24" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1829,27 +2005,33 @@
         </is>
       </c>
       <c r="F25" t="n">
+        <v>432</v>
+      </c>
+      <c r="G25" t="n">
+        <v>394</v>
+      </c>
+      <c r="H25" t="n">
         <v>93</v>
       </c>
-      <c r="G25" t="n">
+      <c r="I25" t="n">
         <v>84</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>59</v>
-      </c>
-      <c r="I25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4.1</v>
       </c>
       <c r="K25" t="n">
         <v>4.2</v>
       </c>
       <c r="L25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N25" t="n">
         <v>-2</v>
       </c>
-      <c r="M25" s="11" t="inlineStr">
+      <c r="O25" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1880,27 +2062,33 @@
         </is>
       </c>
       <c r="F26" t="n">
+        <v>350</v>
+      </c>
+      <c r="G26" t="n">
+        <v>289</v>
+      </c>
+      <c r="H26" t="n">
         <v>85</v>
       </c>
-      <c r="G26" t="n">
+      <c r="I26" t="n">
         <v>63</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>35</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1.2</v>
       </c>
       <c r="K26" t="n">
         <v>2.2</v>
       </c>
       <c r="L26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N26" t="n">
         <v>-45</v>
       </c>
-      <c r="M26" s="13" t="inlineStr">
+      <c r="O26" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1931,27 +2119,33 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>387</v>
+      </c>
+      <c r="G27" t="n">
+        <v>347</v>
+      </c>
+      <c r="H27" t="n">
         <v>86</v>
       </c>
-      <c r="G27" t="n">
+      <c r="I27" t="n">
         <v>68</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>51</v>
-      </c>
-      <c r="I27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.7</v>
       </c>
       <c r="K27" t="n">
         <v>4.9</v>
       </c>
       <c r="L27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N27" t="n">
         <v>-45</v>
       </c>
-      <c r="M27" s="11" t="inlineStr">
+      <c r="O27" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1982,27 +2176,33 @@
         </is>
       </c>
       <c r="F28" t="n">
+        <v>283</v>
+      </c>
+      <c r="G28" t="n">
+        <v>225</v>
+      </c>
+      <c r="H28" t="n">
         <v>77</v>
       </c>
-      <c r="G28" t="n">
+      <c r="I28" t="n">
         <v>69</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>63</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>5.8</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>5.8</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>5.9</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>0</v>
       </c>
-      <c r="M28" s="11" t="inlineStr">
+      <c r="O28" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2033,27 +2233,33 @@
         </is>
       </c>
       <c r="F29" t="n">
+        <v>421</v>
+      </c>
+      <c r="G29" t="n">
+        <v>390</v>
+      </c>
+      <c r="H29" t="n">
         <v>89</v>
       </c>
-      <c r="G29" t="n">
+      <c r="I29" t="n">
         <v>71</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>62</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>10.9</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>10.5</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>11.8</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>-4</v>
       </c>
-      <c r="M29" s="11" t="inlineStr">
+      <c r="O29" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2084,27 +2290,33 @@
         </is>
       </c>
       <c r="F30" t="n">
+        <v>375</v>
+      </c>
+      <c r="G30" t="n">
+        <v>268</v>
+      </c>
+      <c r="H30" t="n">
         <v>89</v>
       </c>
-      <c r="G30" t="n">
+      <c r="I30" t="n">
         <v>71</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>53</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1.4</v>
       </c>
       <c r="K30" t="n">
         <v>1.5</v>
       </c>
       <c r="L30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N30" t="n">
         <v>-7</v>
       </c>
-      <c r="M30" s="11" t="inlineStr">
+      <c r="O30" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2135,27 +2347,33 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>235</v>
+      </c>
+      <c r="G31" t="n">
+        <v>193</v>
+      </c>
+      <c r="H31" t="n">
         <v>102</v>
       </c>
-      <c r="G31" t="n">
+      <c r="I31" t="n">
         <v>72</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>62</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>10.7</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>6.3</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>10.8</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>-41</v>
       </c>
-      <c r="M31" s="11" t="inlineStr">
+      <c r="O31" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2186,27 +2404,33 @@
         </is>
       </c>
       <c r="F32" t="n">
+        <v>421</v>
+      </c>
+      <c r="G32" t="n">
+        <v>304</v>
+      </c>
+      <c r="H32" t="n">
         <v>90</v>
       </c>
-      <c r="G32" t="n">
+      <c r="I32" t="n">
         <v>61</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>45</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>2</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>1.6</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>2.2</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>-20</v>
       </c>
-      <c r="M32" s="13" t="inlineStr">
+      <c r="O32" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -2237,27 +2461,33 @@
         </is>
       </c>
       <c r="F33" t="n">
+        <v>366</v>
+      </c>
+      <c r="G33" t="n">
+        <v>261</v>
+      </c>
+      <c r="H33" t="n">
         <v>88</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>54</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>38</v>
-      </c>
-      <c r="I33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1.7</v>
       </c>
       <c r="K33" t="n">
         <v>3.5</v>
       </c>
       <c r="L33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N33" t="n">
         <v>-51</v>
       </c>
-      <c r="M33" s="13" t="inlineStr">
+      <c r="O33" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -2288,27 +2518,33 @@
         </is>
       </c>
       <c r="F34" t="n">
+        <v>400</v>
+      </c>
+      <c r="G34" t="n">
+        <v>331</v>
+      </c>
+      <c r="H34" t="n">
         <v>87</v>
       </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
         <v>68</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>39</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>1.6</v>
       </c>
       <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N34" t="n">
         <v>-38</v>
       </c>
-      <c r="M34" s="11" t="inlineStr">
+      <c r="O34" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2339,27 +2575,33 @@
         </is>
       </c>
       <c r="F35" t="n">
+        <v>390</v>
+      </c>
+      <c r="G35" t="n">
+        <v>322</v>
+      </c>
+      <c r="H35" t="n">
         <v>87</v>
       </c>
-      <c r="G35" t="n">
+      <c r="I35" t="n">
         <v>77</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>50</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1.5</v>
       </c>
       <c r="K35" t="n">
         <v>2</v>
       </c>
       <c r="L35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" t="n">
         <v>-25</v>
       </c>
-      <c r="M35" s="11" t="inlineStr">
+      <c r="O35" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2390,27 +2632,33 @@
         </is>
       </c>
       <c r="F36" t="n">
+        <v>506</v>
+      </c>
+      <c r="G36" t="n">
+        <v>453</v>
+      </c>
+      <c r="H36" t="n">
         <v>94</v>
       </c>
-      <c r="G36" t="n">
+      <c r="I36" t="n">
         <v>85</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>57</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>3.7</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>3.4</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>4</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>-8</v>
       </c>
-      <c r="M36" s="11" t="inlineStr">
+      <c r="O36" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2441,27 +2689,33 @@
         </is>
       </c>
       <c r="F37" t="n">
+        <v>310</v>
+      </c>
+      <c r="G37" t="n">
+        <v>291</v>
+      </c>
+      <c r="H37" t="n">
         <v>99</v>
       </c>
-      <c r="G37" t="n">
+      <c r="I37" t="n">
         <v>73</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>46</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1.1</v>
       </c>
       <c r="K37" t="n">
         <v>1.4</v>
       </c>
       <c r="L37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N37" t="n">
         <v>-21</v>
       </c>
-      <c r="M37" s="11" t="inlineStr">
+      <c r="O37" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2492,27 +2746,33 @@
         </is>
       </c>
       <c r="F38" t="n">
+        <v>426</v>
+      </c>
+      <c r="G38" t="n">
+        <v>315</v>
+      </c>
+      <c r="H38" t="n">
         <v>86</v>
       </c>
-      <c r="G38" t="n">
+      <c r="I38" t="n">
         <v>59</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>41</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1.3</v>
       </c>
       <c r="K38" t="n">
         <v>2</v>
       </c>
       <c r="L38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2</v>
+      </c>
+      <c r="N38" t="n">
         <v>-35</v>
       </c>
-      <c r="M38" s="13" t="inlineStr">
+      <c r="O38" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -2543,27 +2803,33 @@
         </is>
       </c>
       <c r="F39" t="n">
+        <v>463</v>
+      </c>
+      <c r="G39" t="n">
+        <v>399</v>
+      </c>
+      <c r="H39" t="n">
         <v>84</v>
       </c>
-      <c r="G39" t="n">
+      <c r="I39" t="n">
         <v>69</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>56</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>6.2</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>9.5</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>-33</v>
       </c>
-      <c r="M39" s="11" t="inlineStr">
+      <c r="O39" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2594,27 +2860,33 @@
         </is>
       </c>
       <c r="F40" t="n">
+        <v>445</v>
+      </c>
+      <c r="G40" t="n">
+        <v>400</v>
+      </c>
+      <c r="H40" t="n">
         <v>88</v>
       </c>
-      <c r="G40" t="n">
+      <c r="I40" t="n">
         <v>77</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>54</v>
-      </c>
-      <c r="I40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1.4</v>
       </c>
       <c r="K40" t="n">
         <v>2.4</v>
       </c>
       <c r="L40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N40" t="n">
         <v>-42</v>
       </c>
-      <c r="M40" s="11" t="inlineStr">
+      <c r="O40" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2645,27 +2917,33 @@
         </is>
       </c>
       <c r="F41" t="n">
+        <v>344</v>
+      </c>
+      <c r="G41" t="n">
+        <v>267</v>
+      </c>
+      <c r="H41" t="n">
         <v>76</v>
       </c>
-      <c r="G41" t="n">
+      <c r="I41" t="n">
         <v>54</v>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>35</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1.1</v>
       </c>
       <c r="K41" t="n">
         <v>1.8</v>
       </c>
       <c r="L41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N41" t="n">
         <v>-39</v>
       </c>
-      <c r="M41" s="13" t="inlineStr">
+      <c r="O41" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -2696,27 +2974,33 @@
         </is>
       </c>
       <c r="F42" t="n">
+        <v>390</v>
+      </c>
+      <c r="G42" t="n">
+        <v>339</v>
+      </c>
+      <c r="H42" t="n">
         <v>89</v>
       </c>
-      <c r="G42" t="n">
+      <c r="I42" t="n">
         <v>72</v>
       </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>63</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J42" t="n">
-        <v>1.4</v>
       </c>
       <c r="K42" t="n">
         <v>1.5</v>
       </c>
       <c r="L42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N42" t="n">
         <v>-7</v>
       </c>
-      <c r="M42" s="11" t="inlineStr">
+      <c r="O42" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2747,24 +3031,30 @@
         </is>
       </c>
       <c r="F43" t="n">
+        <v>334</v>
+      </c>
+      <c r="G43" t="n">
+        <v>228</v>
+      </c>
+      <c r="H43" t="n">
         <v>70</v>
       </c>
-      <c r="G43" t="n">
+      <c r="I43" t="n">
         <v>40</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J43" t="n">
-        <v>1.7</v>
       </c>
       <c r="K43" t="n">
         <v>1.9</v>
       </c>
       <c r="L43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N43" t="n">
         <v>-11</v>
       </c>
-      <c r="M43" s="10" t="inlineStr">
+      <c r="O43" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -2795,27 +3085,33 @@
         </is>
       </c>
       <c r="F44" t="n">
+        <v>410</v>
+      </c>
+      <c r="G44" t="n">
+        <v>365</v>
+      </c>
+      <c r="H44" t="n">
         <v>91</v>
       </c>
-      <c r="G44" t="n">
+      <c r="I44" t="n">
         <v>69</v>
       </c>
-      <c r="H44" t="n">
+      <c r="J44" t="n">
         <v>49</v>
-      </c>
-      <c r="I44" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1.7</v>
       </c>
       <c r="K44" t="n">
         <v>3.7</v>
       </c>
       <c r="L44" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N44" t="n">
         <v>-54</v>
       </c>
-      <c r="M44" s="11" t="inlineStr">
+      <c r="O44" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2846,27 +3142,33 @@
         </is>
       </c>
       <c r="F45" t="n">
+        <v>455</v>
+      </c>
+      <c r="G45" t="n">
+        <v>397</v>
+      </c>
+      <c r="H45" t="n">
         <v>89</v>
       </c>
-      <c r="G45" t="n">
+      <c r="I45" t="n">
         <v>71</v>
       </c>
-      <c r="H45" t="n">
+      <c r="J45" t="n">
         <v>52</v>
-      </c>
-      <c r="I45" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.9</v>
       </c>
       <c r="K45" t="n">
         <v>6.1</v>
       </c>
       <c r="L45" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M45" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N45" t="n">
         <v>-52</v>
       </c>
-      <c r="M45" s="11" t="inlineStr">
+      <c r="O45" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2897,27 +3199,33 @@
         </is>
       </c>
       <c r="F46" t="n">
+        <v>224</v>
+      </c>
+      <c r="G46" t="n">
+        <v>143</v>
+      </c>
+      <c r="H46" t="n">
         <v>65</v>
       </c>
-      <c r="G46" t="n">
+      <c r="I46" t="n">
         <v>34</v>
       </c>
-      <c r="H46" t="n">
+      <c r="J46" t="n">
         <v>18</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1.1</v>
       </c>
       <c r="K46" t="n">
         <v>1.6</v>
       </c>
       <c r="L46" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N46" t="n">
         <v>-31</v>
       </c>
-      <c r="M46" s="10" t="inlineStr">
+      <c r="O46" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -2948,27 +3256,33 @@
         </is>
       </c>
       <c r="F47" t="n">
+        <v>360</v>
+      </c>
+      <c r="G47" t="n">
+        <v>314</v>
+      </c>
+      <c r="H47" t="n">
         <v>79</v>
       </c>
-      <c r="G47" t="n">
+      <c r="I47" t="n">
         <v>55</v>
       </c>
-      <c r="H47" t="n">
+      <c r="J47" t="n">
         <v>36</v>
-      </c>
-      <c r="I47" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J47" t="n">
-        <v>1.1</v>
       </c>
       <c r="K47" t="n">
         <v>1.6</v>
       </c>
       <c r="L47" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N47" t="n">
         <v>-31</v>
       </c>
-      <c r="M47" s="13" t="inlineStr">
+      <c r="O47" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -2999,27 +3313,33 @@
         </is>
       </c>
       <c r="F48" t="n">
+        <v>466</v>
+      </c>
+      <c r="G48" t="n">
+        <v>414</v>
+      </c>
+      <c r="H48" t="n">
         <v>89</v>
       </c>
-      <c r="G48" t="n">
+      <c r="I48" t="n">
         <v>72</v>
       </c>
-      <c r="H48" t="n">
+      <c r="J48" t="n">
         <v>54</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1.6</v>
       </c>
       <c r="K48" t="n">
         <v>1.9</v>
       </c>
       <c r="L48" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N48" t="n">
         <v>-16</v>
       </c>
-      <c r="M48" s="11" t="inlineStr">
+      <c r="O48" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3050,27 +3370,33 @@
         </is>
       </c>
       <c r="F49" t="n">
+        <v>317</v>
+      </c>
+      <c r="G49" t="n">
+        <v>251</v>
+      </c>
+      <c r="H49" t="n">
         <v>79</v>
       </c>
-      <c r="G49" t="n">
+      <c r="I49" t="n">
         <v>58</v>
       </c>
-      <c r="H49" t="n">
+      <c r="J49" t="n">
         <v>40</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1.1</v>
       </c>
       <c r="K49" t="n">
         <v>1.5</v>
       </c>
       <c r="L49" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N49" t="n">
         <v>-27</v>
       </c>
-      <c r="M49" s="13" t="inlineStr">
+      <c r="O49" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3101,27 +3427,33 @@
         </is>
       </c>
       <c r="F50" t="n">
+        <v>488</v>
+      </c>
+      <c r="G50" t="n">
+        <v>427</v>
+      </c>
+      <c r="H50" t="n">
         <v>88</v>
       </c>
-      <c r="G50" t="n">
+      <c r="I50" t="n">
         <v>70</v>
       </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
         <v>48</v>
-      </c>
-      <c r="I50" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.6</v>
       </c>
       <c r="K50" t="n">
         <v>7.2</v>
       </c>
       <c r="L50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M50" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N50" t="n">
         <v>-64</v>
       </c>
-      <c r="M50" s="11" t="inlineStr">
+      <c r="O50" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3152,27 +3484,33 @@
         </is>
       </c>
       <c r="F51" t="n">
+        <v>368</v>
+      </c>
+      <c r="G51" t="n">
+        <v>267</v>
+      </c>
+      <c r="H51" t="n">
         <v>95</v>
       </c>
-      <c r="G51" t="n">
+      <c r="I51" t="n">
         <v>64</v>
       </c>
-      <c r="H51" t="n">
+      <c r="J51" t="n">
         <v>43</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1.1</v>
       </c>
       <c r="K51" t="n">
         <v>2.1</v>
       </c>
       <c r="L51" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N51" t="n">
         <v>-48</v>
       </c>
-      <c r="M51" s="13" t="inlineStr">
+      <c r="O51" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3203,27 +3541,33 @@
         </is>
       </c>
       <c r="F52" t="n">
+        <v>249</v>
+      </c>
+      <c r="G52" t="n">
+        <v>180</v>
+      </c>
+      <c r="H52" t="n">
         <v>94</v>
       </c>
-      <c r="G52" t="n">
+      <c r="I52" t="n">
         <v>59</v>
       </c>
-      <c r="H52" t="n">
+      <c r="J52" t="n">
         <v>42</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1.2</v>
       </c>
       <c r="K52" t="n">
         <v>1.9</v>
       </c>
       <c r="L52" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N52" t="n">
         <v>-37</v>
       </c>
-      <c r="M52" s="13" t="inlineStr">
+      <c r="O52" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3254,27 +3598,33 @@
         </is>
       </c>
       <c r="F53" t="n">
+        <v>409</v>
+      </c>
+      <c r="G53" t="n">
+        <v>325</v>
+      </c>
+      <c r="H53" t="n">
         <v>104</v>
       </c>
-      <c r="G53" t="n">
+      <c r="I53" t="n">
         <v>86</v>
       </c>
-      <c r="H53" t="n">
+      <c r="J53" t="n">
         <v>75</v>
       </c>
-      <c r="I53" t="n">
+      <c r="K53" t="n">
         <v>2.2</v>
       </c>
-      <c r="J53" t="n">
+      <c r="L53" t="n">
         <v>2</v>
       </c>
-      <c r="K53" t="n">
+      <c r="M53" t="n">
         <v>2.5</v>
       </c>
-      <c r="L53" t="n">
+      <c r="N53" t="n">
         <v>-9</v>
       </c>
-      <c r="M53" s="11" t="inlineStr">
+      <c r="O53" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3305,27 +3655,33 @@
         </is>
       </c>
       <c r="F54" t="n">
+        <v>360</v>
+      </c>
+      <c r="G54" t="n">
+        <v>252</v>
+      </c>
+      <c r="H54" t="n">
         <v>92</v>
       </c>
-      <c r="G54" t="n">
+      <c r="I54" t="n">
         <v>60</v>
       </c>
-      <c r="H54" t="n">
+      <c r="J54" t="n">
         <v>41</v>
-      </c>
-      <c r="I54" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1.3</v>
       </c>
       <c r="K54" t="n">
         <v>3.8</v>
       </c>
       <c r="L54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N54" t="n">
         <v>-66</v>
       </c>
-      <c r="M54" s="13" t="inlineStr">
+      <c r="O54" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3356,27 +3712,33 @@
         </is>
       </c>
       <c r="F55" t="n">
+        <v>381</v>
+      </c>
+      <c r="G55" t="n">
+        <v>266</v>
+      </c>
+      <c r="H55" t="n">
         <v>91</v>
       </c>
-      <c r="G55" t="n">
+      <c r="I55" t="n">
         <v>60</v>
       </c>
-      <c r="H55" t="n">
+      <c r="J55" t="n">
         <v>40</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1.1</v>
       </c>
       <c r="K55" t="n">
         <v>2.2</v>
       </c>
       <c r="L55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N55" t="n">
         <v>-50</v>
       </c>
-      <c r="M55" s="13" t="inlineStr">
+      <c r="O55" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3407,27 +3769,33 @@
         </is>
       </c>
       <c r="F56" t="n">
+        <v>311</v>
+      </c>
+      <c r="G56" t="n">
+        <v>322</v>
+      </c>
+      <c r="H56" t="n">
         <v>92</v>
       </c>
-      <c r="G56" t="n">
+      <c r="I56" t="n">
         <v>92</v>
       </c>
-      <c r="H56" t="n">
+      <c r="J56" t="n">
         <v>72</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1.7</v>
       </c>
       <c r="K56" t="n">
         <v>1.9</v>
       </c>
       <c r="L56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N56" t="n">
         <v>-11</v>
       </c>
-      <c r="M56" s="11" t="inlineStr">
+      <c r="O56" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3458,27 +3826,33 @@
         </is>
       </c>
       <c r="F57" t="n">
+        <v>292</v>
+      </c>
+      <c r="G57" t="n">
+        <v>285</v>
+      </c>
+      <c r="H57" t="n">
         <v>87</v>
       </c>
-      <c r="G57" t="n">
+      <c r="I57" t="n">
         <v>82</v>
       </c>
-      <c r="H57" t="n">
+      <c r="J57" t="n">
         <v>57</v>
       </c>
-      <c r="I57" t="n">
+      <c r="K57" t="n">
         <v>3.2</v>
       </c>
-      <c r="J57" t="n">
+      <c r="L57" t="n">
         <v>1.6</v>
       </c>
-      <c r="K57" t="n">
+      <c r="M57" t="n">
         <v>3.3</v>
       </c>
-      <c r="L57" t="n">
+      <c r="N57" t="n">
         <v>-50</v>
       </c>
-      <c r="M57" s="11" t="inlineStr">
+      <c r="O57" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3509,27 +3883,33 @@
         </is>
       </c>
       <c r="F58" t="n">
+        <v>254</v>
+      </c>
+      <c r="G58" t="n">
+        <v>241</v>
+      </c>
+      <c r="H58" t="n">
         <v>84</v>
       </c>
-      <c r="G58" t="n">
+      <c r="I58" t="n">
         <v>76</v>
       </c>
-      <c r="H58" t="n">
+      <c r="J58" t="n">
         <v>48</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1.1</v>
       </c>
       <c r="K58" t="n">
         <v>2</v>
       </c>
       <c r="L58" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2</v>
+      </c>
+      <c r="N58" t="n">
         <v>-45</v>
       </c>
-      <c r="M58" s="11" t="inlineStr">
+      <c r="O58" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3560,27 +3940,33 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="G59" t="n">
         <v>100</v>
       </c>
       <c r="H59" t="n">
+        <v>85</v>
+      </c>
+      <c r="I59" t="n">
+        <v>100</v>
+      </c>
+      <c r="J59" t="n">
         <v>72</v>
-      </c>
-      <c r="I59" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J59" t="n">
-        <v>1.5</v>
       </c>
       <c r="K59" t="n">
         <v>4.9</v>
       </c>
       <c r="L59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M59" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N59" t="n">
         <v>-69</v>
       </c>
-      <c r="M59" s="11" t="inlineStr">
+      <c r="O59" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3611,27 +3997,33 @@
         </is>
       </c>
       <c r="F60" t="n">
+        <v>314</v>
+      </c>
+      <c r="G60" t="n">
+        <v>228</v>
+      </c>
+      <c r="H60" t="n">
         <v>72</v>
       </c>
-      <c r="G60" t="n">
+      <c r="I60" t="n">
         <v>35</v>
       </c>
-      <c r="H60" t="n">
+      <c r="J60" t="n">
         <v>19</v>
-      </c>
-      <c r="I60" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1</v>
       </c>
       <c r="K60" t="n">
         <v>1.5</v>
       </c>
       <c r="L60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N60" t="n">
         <v>-33</v>
       </c>
-      <c r="M60" s="10" t="inlineStr">
+      <c r="O60" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -3662,27 +4054,33 @@
         </is>
       </c>
       <c r="F61" t="n">
+        <v>303</v>
+      </c>
+      <c r="G61" t="n">
+        <v>219</v>
+      </c>
+      <c r="H61" t="n">
         <v>73</v>
       </c>
-      <c r="G61" t="n">
+      <c r="I61" t="n">
         <v>54</v>
       </c>
-      <c r="H61" t="n">
+      <c r="J61" t="n">
         <v>28</v>
-      </c>
-      <c r="I61" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1.2</v>
       </c>
       <c r="K61" t="n">
         <v>2.2</v>
       </c>
       <c r="L61" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M61" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N61" t="n">
         <v>-45</v>
       </c>
-      <c r="M61" s="13" t="inlineStr">
+      <c r="O61" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3713,27 +4111,33 @@
         </is>
       </c>
       <c r="F62" t="n">
+        <v>346</v>
+      </c>
+      <c r="G62" t="n">
+        <v>303</v>
+      </c>
+      <c r="H62" t="n">
         <v>89</v>
       </c>
-      <c r="G62" t="n">
+      <c r="I62" t="n">
         <v>71</v>
       </c>
-      <c r="H62" t="n">
+      <c r="J62" t="n">
         <v>43</v>
-      </c>
-      <c r="I62" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" t="n">
-        <v>1.1</v>
       </c>
       <c r="K62" t="n">
         <v>2</v>
       </c>
       <c r="L62" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2</v>
+      </c>
+      <c r="N62" t="n">
         <v>-45</v>
       </c>
-      <c r="M62" s="11" t="inlineStr">
+      <c r="O62" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3764,27 +4168,33 @@
         </is>
       </c>
       <c r="F63" t="n">
+        <v>469</v>
+      </c>
+      <c r="G63" t="n">
+        <v>446</v>
+      </c>
+      <c r="H63" t="n">
         <v>97</v>
       </c>
-      <c r="G63" t="n">
+      <c r="I63" t="n">
         <v>87</v>
       </c>
-      <c r="H63" t="n">
+      <c r="J63" t="n">
         <v>63</v>
       </c>
-      <c r="I63" t="n">
+      <c r="K63" t="n">
         <v>3.3</v>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>2.6</v>
       </c>
-      <c r="K63" t="n">
+      <c r="M63" t="n">
         <v>4.6</v>
       </c>
-      <c r="L63" t="n">
+      <c r="N63" t="n">
         <v>-21</v>
       </c>
-      <c r="M63" s="11" t="inlineStr">
+      <c r="O63" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3815,27 +4225,33 @@
         </is>
       </c>
       <c r="F64" t="n">
+        <v>394</v>
+      </c>
+      <c r="G64" t="n">
+        <v>294</v>
+      </c>
+      <c r="H64" t="n">
         <v>76</v>
       </c>
-      <c r="G64" t="n">
+      <c r="I64" t="n">
         <v>48</v>
       </c>
-      <c r="H64" t="n">
+      <c r="J64" t="n">
         <v>24</v>
-      </c>
-      <c r="I64" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J64" t="n">
-        <v>1.2</v>
       </c>
       <c r="K64" t="n">
         <v>2.4</v>
       </c>
       <c r="L64" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N64" t="n">
         <v>-50</v>
       </c>
-      <c r="M64" s="10" t="inlineStr">
+      <c r="O64" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -3866,27 +4282,33 @@
         </is>
       </c>
       <c r="F65" t="n">
+        <v>402</v>
+      </c>
+      <c r="G65" t="n">
+        <v>321</v>
+      </c>
+      <c r="H65" t="n">
         <v>81</v>
       </c>
-      <c r="G65" t="n">
+      <c r="I65" t="n">
         <v>57</v>
       </c>
-      <c r="H65" t="n">
+      <c r="J65" t="n">
         <v>37</v>
-      </c>
-      <c r="I65" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J65" t="n">
-        <v>1.3</v>
       </c>
       <c r="K65" t="n">
         <v>3.3</v>
       </c>
       <c r="L65" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N65" t="n">
         <v>-61</v>
       </c>
-      <c r="M65" s="13" t="inlineStr">
+      <c r="O65" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3917,27 +4339,33 @@
         </is>
       </c>
       <c r="F66" t="n">
+        <v>321</v>
+      </c>
+      <c r="G66" t="n">
+        <v>245</v>
+      </c>
+      <c r="H66" t="n">
         <v>77</v>
       </c>
-      <c r="G66" t="n">
+      <c r="I66" t="n">
         <v>59</v>
       </c>
-      <c r="H66" t="n">
+      <c r="J66" t="n">
         <v>29</v>
-      </c>
-      <c r="I66" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J66" t="n">
-        <v>1.1</v>
       </c>
       <c r="K66" t="n">
         <v>1.2</v>
       </c>
       <c r="L66" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N66" t="n">
         <v>-8</v>
       </c>
-      <c r="M66" s="13" t="inlineStr">
+      <c r="O66" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3968,27 +4396,33 @@
         </is>
       </c>
       <c r="F67" t="n">
+        <v>306</v>
+      </c>
+      <c r="G67" t="n">
+        <v>217</v>
+      </c>
+      <c r="H67" t="n">
         <v>72</v>
       </c>
-      <c r="G67" t="n">
+      <c r="I67" t="n">
         <v>50</v>
       </c>
-      <c r="H67" t="n">
+      <c r="J67" t="n">
         <v>33</v>
-      </c>
-      <c r="I67" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J67" t="n">
-        <v>1.1</v>
       </c>
       <c r="K67" t="n">
         <v>1.3</v>
       </c>
       <c r="L67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N67" t="n">
         <v>-15</v>
       </c>
-      <c r="M67" s="13" t="inlineStr">
+      <c r="O67" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4019,27 +4453,33 @@
         </is>
       </c>
       <c r="F68" t="n">
+        <v>241</v>
+      </c>
+      <c r="G68" t="n">
+        <v>157</v>
+      </c>
+      <c r="H68" t="n">
         <v>66</v>
       </c>
-      <c r="G68" t="n">
+      <c r="I68" t="n">
         <v>40</v>
       </c>
-      <c r="H68" t="n">
+      <c r="J68" t="n">
         <v>23</v>
-      </c>
-      <c r="I68" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J68" t="n">
-        <v>1.1</v>
       </c>
       <c r="K68" t="n">
         <v>1.4</v>
       </c>
       <c r="L68" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N68" t="n">
         <v>-21</v>
       </c>
-      <c r="M68" s="10" t="inlineStr">
+      <c r="O68" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4070,27 +4510,33 @@
         </is>
       </c>
       <c r="F69" t="n">
+        <v>422</v>
+      </c>
+      <c r="G69" t="n">
+        <v>365</v>
+      </c>
+      <c r="H69" t="n">
         <v>84</v>
       </c>
-      <c r="G69" t="n">
+      <c r="I69" t="n">
         <v>60</v>
       </c>
-      <c r="H69" t="n">
+      <c r="J69" t="n">
         <v>61</v>
-      </c>
-      <c r="I69" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J69" t="n">
-        <v>2</v>
       </c>
       <c r="K69" t="n">
         <v>3.4</v>
       </c>
       <c r="L69" t="n">
+        <v>2</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N69" t="n">
         <v>-41</v>
       </c>
-      <c r="M69" s="13" t="inlineStr">
+      <c r="O69" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4121,27 +4567,33 @@
         </is>
       </c>
       <c r="F70" t="n">
+        <v>351</v>
+      </c>
+      <c r="G70" t="n">
+        <v>244</v>
+      </c>
+      <c r="H70" t="n">
         <v>67</v>
       </c>
-      <c r="G70" t="n">
+      <c r="I70" t="n">
         <v>37</v>
       </c>
-      <c r="H70" t="n">
+      <c r="J70" t="n">
         <v>31</v>
-      </c>
-      <c r="I70" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J70" t="n">
-        <v>3.3</v>
       </c>
       <c r="K70" t="n">
         <v>11.3</v>
       </c>
       <c r="L70" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M70" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="N70" t="n">
         <v>-71</v>
       </c>
-      <c r="M70" s="10" t="inlineStr">
+      <c r="O70" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4172,27 +4624,33 @@
         </is>
       </c>
       <c r="F71" t="n">
+        <v>353</v>
+      </c>
+      <c r="G71" t="n">
+        <v>339</v>
+      </c>
+      <c r="H71" t="n">
         <v>72</v>
       </c>
-      <c r="G71" t="n">
+      <c r="I71" t="n">
         <v>48</v>
       </c>
-      <c r="H71" t="n">
+      <c r="J71" t="n">
         <v>24</v>
-      </c>
-      <c r="I71" t="n">
-        <v>2</v>
-      </c>
-      <c r="J71" t="n">
-        <v>1.1</v>
       </c>
       <c r="K71" t="n">
         <v>2</v>
       </c>
       <c r="L71" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M71" t="n">
+        <v>2</v>
+      </c>
+      <c r="N71" t="n">
         <v>-45</v>
       </c>
-      <c r="M71" s="10" t="inlineStr">
+      <c r="O71" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4223,27 +4681,33 @@
         </is>
       </c>
       <c r="F72" t="n">
+        <v>313</v>
+      </c>
+      <c r="G72" t="n">
+        <v>292</v>
+      </c>
+      <c r="H72" t="n">
         <v>70</v>
       </c>
-      <c r="G72" t="n">
+      <c r="I72" t="n">
         <v>45</v>
       </c>
-      <c r="H72" t="n">
+      <c r="J72" t="n">
         <v>29</v>
-      </c>
-      <c r="I72" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J72" t="n">
-        <v>1.2</v>
       </c>
       <c r="K72" t="n">
         <v>5.2</v>
       </c>
       <c r="L72" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M72" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N72" t="n">
         <v>-77</v>
       </c>
-      <c r="M72" s="10" t="inlineStr">
+      <c r="O72" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4274,27 +4738,33 @@
         </is>
       </c>
       <c r="F73" t="n">
+        <v>362</v>
+      </c>
+      <c r="G73" t="n">
+        <v>384</v>
+      </c>
+      <c r="H73" t="n">
         <v>80</v>
       </c>
-      <c r="G73" t="n">
+      <c r="I73" t="n">
         <v>57</v>
       </c>
-      <c r="H73" t="n">
+      <c r="J73" t="n">
         <v>35</v>
-      </c>
-      <c r="I73" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J73" t="n">
-        <v>1.1</v>
       </c>
       <c r="K73" t="n">
         <v>3.8</v>
       </c>
       <c r="L73" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M73" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N73" t="n">
         <v>-71</v>
       </c>
-      <c r="M73" s="13" t="inlineStr">
+      <c r="O73" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4325,27 +4795,33 @@
         </is>
       </c>
       <c r="F74" t="n">
+        <v>412</v>
+      </c>
+      <c r="G74" t="n">
+        <v>338</v>
+      </c>
+      <c r="H74" t="n">
         <v>95</v>
       </c>
-      <c r="G74" t="n">
+      <c r="I74" t="n">
         <v>53</v>
       </c>
-      <c r="H74" t="n">
+      <c r="J74" t="n">
         <v>35</v>
-      </c>
-      <c r="I74" t="n">
-        <v>3</v>
-      </c>
-      <c r="J74" t="n">
-        <v>1.1</v>
       </c>
       <c r="K74" t="n">
         <v>3</v>
       </c>
       <c r="L74" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M74" t="n">
+        <v>3</v>
+      </c>
+      <c r="N74" t="n">
         <v>-63</v>
       </c>
-      <c r="M74" s="13" t="inlineStr">
+      <c r="O74" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4376,27 +4852,33 @@
         </is>
       </c>
       <c r="F75" t="n">
+        <v>442</v>
+      </c>
+      <c r="G75" t="n">
+        <v>384</v>
+      </c>
+      <c r="H75" t="n">
         <v>101</v>
       </c>
-      <c r="G75" t="n">
+      <c r="I75" t="n">
         <v>77</v>
       </c>
-      <c r="H75" t="n">
+      <c r="J75" t="n">
         <v>66</v>
       </c>
-      <c r="I75" t="n">
+      <c r="K75" t="n">
         <v>4</v>
       </c>
-      <c r="J75" t="n">
+      <c r="L75" t="n">
         <v>2.2</v>
       </c>
-      <c r="K75" t="n">
+      <c r="M75" t="n">
         <v>4.4</v>
       </c>
-      <c r="L75" t="n">
+      <c r="N75" t="n">
         <v>-45</v>
       </c>
-      <c r="M75" s="11" t="inlineStr">
+      <c r="O75" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -4427,27 +4909,33 @@
         </is>
       </c>
       <c r="F76" t="n">
+        <v>317</v>
+      </c>
+      <c r="G76" t="n">
+        <v>218</v>
+      </c>
+      <c r="H76" t="n">
         <v>80</v>
       </c>
-      <c r="G76" t="n">
+      <c r="I76" t="n">
         <v>35</v>
       </c>
-      <c r="H76" t="n">
+      <c r="J76" t="n">
         <v>20</v>
-      </c>
-      <c r="I76" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J76" t="n">
-        <v>1.1</v>
       </c>
       <c r="K76" t="n">
         <v>2.7</v>
       </c>
       <c r="L76" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N76" t="n">
         <v>-59</v>
       </c>
-      <c r="M76" s="10" t="inlineStr">
+      <c r="O76" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4478,27 +4966,33 @@
         </is>
       </c>
       <c r="F77" t="n">
+        <v>376</v>
+      </c>
+      <c r="G77" t="n">
+        <v>324</v>
+      </c>
+      <c r="H77" t="n">
         <v>86</v>
       </c>
-      <c r="G77" t="n">
+      <c r="I77" t="n">
         <v>66</v>
       </c>
-      <c r="H77" t="n">
+      <c r="J77" t="n">
         <v>38</v>
       </c>
-      <c r="I77" t="n">
+      <c r="K77" t="n">
         <v>2.3</v>
       </c>
-      <c r="J77" t="n">
+      <c r="L77" t="n">
         <v>1.2</v>
       </c>
-      <c r="K77" t="n">
+      <c r="M77" t="n">
         <v>2.4</v>
       </c>
-      <c r="L77" t="n">
+      <c r="N77" t="n">
         <v>-48</v>
       </c>
-      <c r="M77" s="11" t="inlineStr">
+      <c r="O77" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -4529,27 +5023,33 @@
         </is>
       </c>
       <c r="F78" t="n">
+        <v>504</v>
+      </c>
+      <c r="G78" t="n">
+        <v>479</v>
+      </c>
+      <c r="H78" t="n">
         <v>95</v>
       </c>
-      <c r="G78" t="n">
+      <c r="I78" t="n">
         <v>87</v>
       </c>
-      <c r="H78" t="n">
+      <c r="J78" t="n">
         <v>62</v>
       </c>
-      <c r="I78" t="n">
+      <c r="K78" t="n">
         <v>3.9</v>
       </c>
-      <c r="J78" t="n">
+      <c r="L78" t="n">
         <v>3.5</v>
       </c>
-      <c r="K78" t="n">
+      <c r="M78" t="n">
         <v>4.5</v>
       </c>
-      <c r="L78" t="n">
+      <c r="N78" t="n">
         <v>-10</v>
       </c>
-      <c r="M78" s="11" t="inlineStr">
+      <c r="O78" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -4580,24 +5080,30 @@
         </is>
       </c>
       <c r="F79" t="n">
+        <v>247</v>
+      </c>
+      <c r="G79" t="n">
+        <v>168</v>
+      </c>
+      <c r="H79" t="n">
         <v>68</v>
       </c>
-      <c r="G79" t="n">
+      <c r="I79" t="n">
         <v>46</v>
-      </c>
-      <c r="I79" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J79" t="n">
-        <v>2.4</v>
       </c>
       <c r="K79" t="n">
         <v>2.7</v>
       </c>
       <c r="L79" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N79" t="n">
         <v>-11</v>
       </c>
-      <c r="M79" s="10" t="inlineStr">
+      <c r="O79" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4628,27 +5134,33 @@
         </is>
       </c>
       <c r="F80" t="n">
+        <v>307</v>
+      </c>
+      <c r="G80" t="n">
+        <v>201</v>
+      </c>
+      <c r="H80" t="n">
         <v>66</v>
       </c>
-      <c r="G80" t="n">
+      <c r="I80" t="n">
         <v>40</v>
       </c>
-      <c r="H80" t="n">
+      <c r="J80" t="n">
         <v>17</v>
-      </c>
-      <c r="I80" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J80" t="n">
-        <v>1.1</v>
       </c>
       <c r="K80" t="n">
         <v>2.6</v>
       </c>
       <c r="L80" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M80" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N80" t="n">
         <v>-58</v>
       </c>
-      <c r="M80" s="10" t="inlineStr">
+      <c r="O80" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4679,27 +5191,33 @@
         </is>
       </c>
       <c r="F81" t="n">
+        <v>249</v>
+      </c>
+      <c r="G81" t="n">
+        <v>191</v>
+      </c>
+      <c r="H81" t="n">
         <v>71</v>
       </c>
-      <c r="G81" t="n">
+      <c r="I81" t="n">
         <v>42</v>
       </c>
-      <c r="H81" t="n">
+      <c r="J81" t="n">
         <v>28</v>
-      </c>
-      <c r="I81" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J81" t="n">
-        <v>1.1</v>
       </c>
       <c r="K81" t="n">
         <v>1.5</v>
       </c>
       <c r="L81" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N81" t="n">
         <v>-27</v>
       </c>
-      <c r="M81" s="10" t="inlineStr">
+      <c r="O81" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4730,27 +5248,33 @@
         </is>
       </c>
       <c r="F82" t="n">
+        <v>361</v>
+      </c>
+      <c r="G82" t="n">
+        <v>315</v>
+      </c>
+      <c r="H82" t="n">
         <v>77</v>
       </c>
-      <c r="G82" t="n">
+      <c r="I82" t="n">
         <v>56</v>
       </c>
-      <c r="H82" t="n">
+      <c r="J82" t="n">
         <v>34</v>
-      </c>
-      <c r="I82" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J82" t="n">
-        <v>1.1</v>
       </c>
       <c r="K82" t="n">
         <v>2.4</v>
       </c>
       <c r="L82" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N82" t="n">
         <v>-54</v>
       </c>
-      <c r="M82" s="13" t="inlineStr">
+      <c r="O82" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4781,27 +5305,33 @@
         </is>
       </c>
       <c r="F83" t="n">
+        <v>432</v>
+      </c>
+      <c r="G83" t="n">
+        <v>430</v>
+      </c>
+      <c r="H83" t="n">
         <v>88</v>
       </c>
-      <c r="G83" t="n">
+      <c r="I83" t="n">
         <v>69</v>
       </c>
-      <c r="H83" t="n">
+      <c r="J83" t="n">
         <v>49</v>
       </c>
-      <c r="I83" t="n">
+      <c r="K83" t="n">
         <v>3.6</v>
       </c>
-      <c r="J83" t="n">
+      <c r="L83" t="n">
         <v>1.5</v>
       </c>
-      <c r="K83" t="n">
+      <c r="M83" t="n">
         <v>4.1</v>
       </c>
-      <c r="L83" t="n">
+      <c r="N83" t="n">
         <v>-58</v>
       </c>
-      <c r="M83" s="11" t="inlineStr">
+      <c r="O83" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -4832,27 +5362,33 @@
         </is>
       </c>
       <c r="F84" t="n">
+        <v>381</v>
+      </c>
+      <c r="G84" t="n">
+        <v>360</v>
+      </c>
+      <c r="H84" t="n">
         <v>84</v>
       </c>
-      <c r="G84" t="n">
+      <c r="I84" t="n">
         <v>58</v>
       </c>
-      <c r="H84" t="n">
+      <c r="J84" t="n">
         <v>38</v>
-      </c>
-      <c r="I84" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J84" t="n">
-        <v>1.1</v>
       </c>
       <c r="K84" t="n">
         <v>2.6</v>
       </c>
       <c r="L84" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M84" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N84" t="n">
         <v>-58</v>
       </c>
-      <c r="M84" s="13" t="inlineStr">
+      <c r="O84" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4883,27 +5419,33 @@
         </is>
       </c>
       <c r="F85" t="n">
+        <v>415</v>
+      </c>
+      <c r="G85" t="n">
+        <v>436</v>
+      </c>
+      <c r="H85" t="n">
         <v>93</v>
       </c>
-      <c r="G85" t="n">
+      <c r="I85" t="n">
         <v>85</v>
       </c>
-      <c r="H85" t="n">
+      <c r="J85" t="n">
         <v>70</v>
       </c>
-      <c r="I85" t="n">
+      <c r="K85" t="n">
         <v>1.5</v>
       </c>
-      <c r="J85" t="n">
+      <c r="L85" t="n">
         <v>1.3</v>
       </c>
-      <c r="K85" t="n">
+      <c r="M85" t="n">
         <v>1.7</v>
       </c>
-      <c r="L85" t="n">
+      <c r="N85" t="n">
         <v>-13</v>
       </c>
-      <c r="M85" s="11" t="inlineStr">
+      <c r="O85" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -4934,27 +5476,33 @@
         </is>
       </c>
       <c r="F86" t="n">
+        <v>145</v>
+      </c>
+      <c r="G86" t="n">
+        <v>115</v>
+      </c>
+      <c r="H86" t="n">
         <v>70</v>
       </c>
-      <c r="G86" t="n">
+      <c r="I86" t="n">
         <v>48</v>
       </c>
-      <c r="H86" t="n">
+      <c r="J86" t="n">
         <v>49</v>
-      </c>
-      <c r="I86" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J86" t="n">
-        <v>2.3</v>
       </c>
       <c r="K86" t="n">
         <v>5.6</v>
       </c>
       <c r="L86" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M86" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N86" t="n">
         <v>-59</v>
       </c>
-      <c r="M86" s="10" t="inlineStr">
+      <c r="O86" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4985,27 +5533,33 @@
         </is>
       </c>
       <c r="F87" t="n">
+        <v>357</v>
+      </c>
+      <c r="G87" t="n">
+        <v>278</v>
+      </c>
+      <c r="H87" t="n">
         <v>86</v>
       </c>
-      <c r="G87" t="n">
+      <c r="I87" t="n">
         <v>64</v>
       </c>
-      <c r="H87" t="n">
+      <c r="J87" t="n">
         <v>38</v>
-      </c>
-      <c r="I87" t="n">
-        <v>3</v>
-      </c>
-      <c r="J87" t="n">
-        <v>1.1</v>
       </c>
       <c r="K87" t="n">
         <v>3</v>
       </c>
       <c r="L87" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M87" t="n">
+        <v>3</v>
+      </c>
+      <c r="N87" t="n">
         <v>-63</v>
       </c>
-      <c r="M87" s="13" t="inlineStr">
+      <c r="O87" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5036,27 +5590,33 @@
         </is>
       </c>
       <c r="F88" t="n">
+        <v>391</v>
+      </c>
+      <c r="G88" t="n">
+        <v>314</v>
+      </c>
+      <c r="H88" t="n">
         <v>89</v>
       </c>
-      <c r="G88" t="n">
+      <c r="I88" t="n">
         <v>70</v>
       </c>
-      <c r="H88" t="n">
+      <c r="J88" t="n">
         <v>45</v>
-      </c>
-      <c r="I88" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J88" t="n">
-        <v>1.5</v>
       </c>
       <c r="K88" t="n">
         <v>2.5</v>
       </c>
       <c r="L88" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M88" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N88" t="n">
         <v>-40</v>
       </c>
-      <c r="M88" s="11" t="inlineStr">
+      <c r="O88" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5087,27 +5647,33 @@
         </is>
       </c>
       <c r="F89" t="n">
+        <v>426</v>
+      </c>
+      <c r="G89" t="n">
+        <v>352</v>
+      </c>
+      <c r="H89" t="n">
         <v>91</v>
       </c>
-      <c r="G89" t="n">
+      <c r="I89" t="n">
         <v>80</v>
       </c>
-      <c r="H89" t="n">
+      <c r="J89" t="n">
         <v>63</v>
-      </c>
-      <c r="I89" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J89" t="n">
-        <v>2.1</v>
       </c>
       <c r="K89" t="n">
         <v>3.7</v>
       </c>
       <c r="L89" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M89" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N89" t="n">
         <v>-43</v>
       </c>
-      <c r="M89" s="11" t="inlineStr">
+      <c r="O89" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5138,27 +5704,33 @@
         </is>
       </c>
       <c r="F90" t="n">
+        <v>471</v>
+      </c>
+      <c r="G90" t="n">
+        <v>417</v>
+      </c>
+      <c r="H90" t="n">
         <v>98</v>
       </c>
-      <c r="G90" t="n">
+      <c r="I90" t="n">
         <v>91</v>
       </c>
-      <c r="H90" t="n">
+      <c r="J90" t="n">
         <v>78</v>
       </c>
-      <c r="I90" t="n">
+      <c r="K90" t="n">
         <v>4.6</v>
       </c>
-      <c r="J90" t="n">
+      <c r="L90" t="n">
         <v>11.2</v>
       </c>
-      <c r="K90" t="n">
+      <c r="M90" t="n">
         <v>11.3</v>
       </c>
-      <c r="L90" t="n">
+      <c r="N90" t="n">
         <v>143</v>
       </c>
-      <c r="M90" s="11" t="inlineStr">
+      <c r="O90" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5189,27 +5761,33 @@
         </is>
       </c>
       <c r="F91" t="n">
+        <v>328</v>
+      </c>
+      <c r="G91" t="n">
+        <v>247</v>
+      </c>
+      <c r="H91" t="n">
         <v>75</v>
       </c>
-      <c r="G91" t="n">
+      <c r="I91" t="n">
         <v>64</v>
       </c>
-      <c r="H91" t="n">
+      <c r="J91" t="n">
         <v>48</v>
       </c>
-      <c r="I91" t="n">
+      <c r="K91" t="n">
         <v>5.6</v>
       </c>
-      <c r="J91" t="n">
+      <c r="L91" t="n">
         <v>3.2</v>
       </c>
-      <c r="K91" t="n">
+      <c r="M91" t="n">
         <v>6.3</v>
       </c>
-      <c r="L91" t="n">
+      <c r="N91" t="n">
         <v>-43</v>
       </c>
-      <c r="M91" s="13" t="inlineStr">
+      <c r="O91" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5240,27 +5818,33 @@
         </is>
       </c>
       <c r="F92" t="n">
+        <v>428</v>
+      </c>
+      <c r="G92" t="n">
+        <v>408</v>
+      </c>
+      <c r="H92" t="n">
         <v>95</v>
       </c>
-      <c r="G92" t="n">
+      <c r="I92" t="n">
         <v>87</v>
       </c>
-      <c r="H92" t="n">
+      <c r="J92" t="n">
         <v>71</v>
       </c>
-      <c r="I92" t="n">
+      <c r="K92" t="n">
         <v>1.9</v>
       </c>
-      <c r="J92" t="n">
+      <c r="L92" t="n">
         <v>2</v>
       </c>
-      <c r="K92" t="n">
+      <c r="M92" t="n">
         <v>2.3</v>
       </c>
-      <c r="L92" t="n">
+      <c r="N92" t="n">
         <v>5</v>
       </c>
-      <c r="M92" s="11" t="inlineStr">
+      <c r="O92" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5291,27 +5875,33 @@
         </is>
       </c>
       <c r="F93" t="n">
+        <v>437</v>
+      </c>
+      <c r="G93" t="n">
+        <v>411</v>
+      </c>
+      <c r="H93" t="n">
         <v>94</v>
       </c>
-      <c r="G93" t="n">
+      <c r="I93" t="n">
         <v>70</v>
       </c>
-      <c r="H93" t="n">
+      <c r="J93" t="n">
         <v>54</v>
       </c>
-      <c r="I93" t="n">
+      <c r="K93" t="n">
         <v>1.5</v>
       </c>
-      <c r="J93" t="n">
+      <c r="L93" t="n">
         <v>1.2</v>
       </c>
-      <c r="K93" t="n">
+      <c r="M93" t="n">
         <v>1.8</v>
       </c>
-      <c r="L93" t="n">
+      <c r="N93" t="n">
         <v>-20</v>
       </c>
-      <c r="M93" s="11" t="inlineStr">
+      <c r="O93" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5342,27 +5932,33 @@
         </is>
       </c>
       <c r="F94" t="n">
+        <v>380</v>
+      </c>
+      <c r="G94" t="n">
+        <v>288</v>
+      </c>
+      <c r="H94" t="n">
         <v>76</v>
       </c>
-      <c r="G94" t="n">
+      <c r="I94" t="n">
         <v>42</v>
       </c>
-      <c r="H94" t="n">
+      <c r="J94" t="n">
         <v>24</v>
-      </c>
-      <c r="I94" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J94" t="n">
-        <v>1.2</v>
       </c>
       <c r="K94" t="n">
         <v>3.2</v>
       </c>
       <c r="L94" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M94" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N94" t="n">
         <v>-62</v>
       </c>
-      <c r="M94" s="10" t="inlineStr">
+      <c r="O94" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -5393,27 +5989,33 @@
         </is>
       </c>
       <c r="F95" t="n">
+        <v>364</v>
+      </c>
+      <c r="G95" t="n">
+        <v>298</v>
+      </c>
+      <c r="H95" t="n">
         <v>82</v>
       </c>
-      <c r="G95" t="n">
+      <c r="I95" t="n">
         <v>47</v>
       </c>
-      <c r="H95" t="n">
+      <c r="J95" t="n">
         <v>25</v>
-      </c>
-      <c r="I95" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J95" t="n">
-        <v>1.1</v>
       </c>
       <c r="K95" t="n">
         <v>2.2</v>
       </c>
       <c r="L95" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M95" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N95" t="n">
         <v>-50</v>
       </c>
-      <c r="M95" s="10" t="inlineStr">
+      <c r="O95" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -5444,27 +6046,33 @@
         </is>
       </c>
       <c r="F96" t="n">
+        <v>254</v>
+      </c>
+      <c r="G96" t="n">
+        <v>200</v>
+      </c>
+      <c r="H96" t="n">
         <v>79</v>
       </c>
-      <c r="G96" t="n">
+      <c r="I96" t="n">
         <v>59</v>
       </c>
-      <c r="H96" t="n">
+      <c r="J96" t="n">
         <v>45</v>
-      </c>
-      <c r="I96" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J96" t="n">
-        <v>1.6</v>
       </c>
       <c r="K96" t="n">
         <v>10.7</v>
       </c>
       <c r="L96" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M96" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="N96" t="n">
         <v>-85</v>
       </c>
-      <c r="M96" s="13" t="inlineStr">
+      <c r="O96" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5495,27 +6103,33 @@
         </is>
       </c>
       <c r="F97" t="n">
+        <v>424</v>
+      </c>
+      <c r="G97" t="n">
+        <v>335</v>
+      </c>
+      <c r="H97" t="n">
         <v>83</v>
       </c>
-      <c r="G97" t="n">
+      <c r="I97" t="n">
         <v>57</v>
       </c>
-      <c r="H97" t="n">
+      <c r="J97" t="n">
         <v>39</v>
-      </c>
-      <c r="I97" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J97" t="n">
-        <v>1.1</v>
       </c>
       <c r="K97" t="n">
         <v>2.3</v>
       </c>
       <c r="L97" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M97" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N97" t="n">
         <v>-52</v>
       </c>
-      <c r="M97" s="13" t="inlineStr">
+      <c r="O97" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5546,27 +6160,33 @@
         </is>
       </c>
       <c r="F98" t="n">
+        <v>240</v>
+      </c>
+      <c r="G98" t="n">
+        <v>173</v>
+      </c>
+      <c r="H98" t="n">
         <v>76</v>
       </c>
-      <c r="G98" t="n">
+      <c r="I98" t="n">
         <v>61</v>
       </c>
-      <c r="H98" t="n">
+      <c r="J98" t="n">
         <v>51</v>
       </c>
-      <c r="I98" t="n">
+      <c r="K98" t="n">
         <v>4.8</v>
       </c>
-      <c r="J98" t="n">
+      <c r="L98" t="n">
         <v>2.5</v>
       </c>
-      <c r="K98" t="n">
+      <c r="M98" t="n">
         <v>4.9</v>
       </c>
-      <c r="L98" t="n">
+      <c r="N98" t="n">
         <v>-48</v>
       </c>
-      <c r="M98" s="13" t="inlineStr">
+      <c r="O98" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5597,27 +6217,33 @@
         </is>
       </c>
       <c r="F99" t="n">
+        <v>378</v>
+      </c>
+      <c r="G99" t="n">
+        <v>293</v>
+      </c>
+      <c r="H99" t="n">
         <v>89</v>
       </c>
-      <c r="G99" t="n">
+      <c r="I99" t="n">
         <v>74</v>
       </c>
-      <c r="H99" t="n">
+      <c r="J99" t="n">
         <v>65</v>
       </c>
-      <c r="I99" t="n">
+      <c r="K99" t="n">
         <v>2.8</v>
       </c>
-      <c r="J99" t="n">
+      <c r="L99" t="n">
         <v>1.8</v>
       </c>
-      <c r="K99" t="n">
+      <c r="M99" t="n">
         <v>3.1</v>
       </c>
-      <c r="L99" t="n">
+      <c r="N99" t="n">
         <v>-36</v>
       </c>
-      <c r="M99" s="11" t="inlineStr">
+      <c r="O99" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5648,27 +6274,33 @@
         </is>
       </c>
       <c r="F100" t="n">
+        <v>395</v>
+      </c>
+      <c r="G100" t="n">
+        <v>285</v>
+      </c>
+      <c r="H100" t="n">
         <v>83</v>
       </c>
-      <c r="G100" t="n">
+      <c r="I100" t="n">
         <v>54</v>
       </c>
-      <c r="H100" t="n">
+      <c r="J100" t="n">
         <v>42</v>
       </c>
-      <c r="I100" t="n">
+      <c r="K100" t="n">
         <v>6</v>
       </c>
-      <c r="J100" t="n">
+      <c r="L100" t="n">
         <v>1.3</v>
       </c>
-      <c r="K100" t="n">
+      <c r="M100" t="n">
         <v>6.1</v>
       </c>
-      <c r="L100" t="n">
+      <c r="N100" t="n">
         <v>-78</v>
       </c>
-      <c r="M100" s="13" t="inlineStr">
+      <c r="O100" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5699,27 +6331,33 @@
         </is>
       </c>
       <c r="F101" t="n">
+        <v>403</v>
+      </c>
+      <c r="G101" t="n">
+        <v>271</v>
+      </c>
+      <c r="H101" t="n">
         <v>77</v>
       </c>
-      <c r="G101" t="n">
+      <c r="I101" t="n">
         <v>45</v>
       </c>
-      <c r="H101" t="n">
+      <c r="J101" t="n">
         <v>26</v>
       </c>
-      <c r="I101" t="n">
+      <c r="K101" t="n">
         <v>2.9</v>
       </c>
-      <c r="J101" t="n">
+      <c r="L101" t="n">
         <v>1.2</v>
       </c>
-      <c r="K101" t="n">
+      <c r="M101" t="n">
         <v>3</v>
       </c>
-      <c r="L101" t="n">
+      <c r="N101" t="n">
         <v>-59</v>
       </c>
-      <c r="M101" s="10" t="inlineStr">
+      <c r="O101" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -5750,27 +6388,33 @@
         </is>
       </c>
       <c r="F102" t="n">
+        <v>469</v>
+      </c>
+      <c r="G102" t="n">
+        <v>398</v>
+      </c>
+      <c r="H102" t="n">
         <v>89</v>
       </c>
-      <c r="G102" t="n">
+      <c r="I102" t="n">
         <v>61</v>
       </c>
-      <c r="H102" t="n">
+      <c r="J102" t="n">
         <v>40</v>
-      </c>
-      <c r="I102" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J102" t="n">
-        <v>1</v>
       </c>
       <c r="K102" t="n">
         <v>2.3</v>
       </c>
       <c r="L102" t="n">
+        <v>1</v>
+      </c>
+      <c r="M102" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N102" t="n">
         <v>-57</v>
       </c>
-      <c r="M102" s="13" t="inlineStr">
+      <c r="O102" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5801,27 +6445,33 @@
         </is>
       </c>
       <c r="F103" t="n">
+        <v>466</v>
+      </c>
+      <c r="G103" t="n">
+        <v>403</v>
+      </c>
+      <c r="H103" t="n">
         <v>91</v>
       </c>
-      <c r="G103" t="n">
+      <c r="I103" t="n">
         <v>67</v>
       </c>
-      <c r="H103" t="n">
+      <c r="J103" t="n">
         <v>53</v>
-      </c>
-      <c r="I103" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J103" t="n">
-        <v>1.2</v>
       </c>
       <c r="K103" t="n">
         <v>3.2</v>
       </c>
       <c r="L103" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M103" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N103" t="n">
         <v>-62</v>
       </c>
-      <c r="M103" s="11" t="inlineStr">
+      <c r="O103" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5852,27 +6502,33 @@
         </is>
       </c>
       <c r="F104" t="n">
+        <v>453</v>
+      </c>
+      <c r="G104" t="n">
+        <v>366</v>
+      </c>
+      <c r="H104" t="n">
         <v>85</v>
       </c>
-      <c r="G104" t="n">
+      <c r="I104" t="n">
         <v>59</v>
       </c>
-      <c r="H104" t="n">
+      <c r="J104" t="n">
         <v>42</v>
-      </c>
-      <c r="I104" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J104" t="n">
-        <v>1</v>
       </c>
       <c r="K104" t="n">
         <v>1.6</v>
       </c>
       <c r="L104" t="n">
+        <v>1</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N104" t="n">
         <v>-38</v>
       </c>
-      <c r="M104" s="13" t="inlineStr">
+      <c r="O104" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5903,27 +6559,33 @@
         </is>
       </c>
       <c r="F105" t="n">
+        <v>411</v>
+      </c>
+      <c r="G105" t="n">
+        <v>337</v>
+      </c>
+      <c r="H105" t="n">
         <v>86</v>
       </c>
-      <c r="G105" t="n">
+      <c r="I105" t="n">
         <v>51</v>
       </c>
-      <c r="H105" t="n">
+      <c r="J105" t="n">
         <v>29</v>
-      </c>
-      <c r="I105" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J105" t="n">
-        <v>1.1</v>
       </c>
       <c r="K105" t="n">
         <v>2.9</v>
       </c>
       <c r="L105" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M105" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N105" t="n">
         <v>-62</v>
       </c>
-      <c r="M105" s="13" t="inlineStr">
+      <c r="O105" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5954,27 +6616,33 @@
         </is>
       </c>
       <c r="F106" t="n">
+        <v>533</v>
+      </c>
+      <c r="G106" t="n">
+        <v>497</v>
+      </c>
+      <c r="H106" t="n">
         <v>97</v>
       </c>
-      <c r="G106" t="n">
+      <c r="I106" t="n">
         <v>77</v>
       </c>
-      <c r="H106" t="n">
+      <c r="J106" t="n">
         <v>70</v>
       </c>
-      <c r="I106" t="n">
+      <c r="K106" t="n">
         <v>5.1</v>
       </c>
-      <c r="J106" t="n">
+      <c r="L106" t="n">
         <v>3</v>
       </c>
-      <c r="K106" t="n">
+      <c r="M106" t="n">
         <v>6</v>
       </c>
-      <c r="L106" t="n">
+      <c r="N106" t="n">
         <v>-41</v>
       </c>
-      <c r="M106" s="11" t="inlineStr">
+      <c r="O106" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -6005,21 +6673,27 @@
         </is>
       </c>
       <c r="F107" t="n">
+        <v>260</v>
+      </c>
+      <c r="G107" t="n">
+        <v>172</v>
+      </c>
+      <c r="H107" t="n">
         <v>69</v>
-      </c>
-      <c r="I107" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J107" t="n">
-        <v>1.2</v>
       </c>
       <c r="K107" t="n">
         <v>1.2</v>
       </c>
       <c r="L107" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N107" t="n">
         <v>0</v>
       </c>
-      <c r="M107" s="10" t="inlineStr">
+      <c r="O107" s="11" t="inlineStr">
         <is>
           <t>危険(暫定)</t>
         </is>
@@ -6050,27 +6724,33 @@
         </is>
       </c>
       <c r="F108" t="n">
+        <v>334</v>
+      </c>
+      <c r="G108" t="n">
+        <v>246</v>
+      </c>
+      <c r="H108" t="n">
         <v>76</v>
       </c>
-      <c r="G108" t="n">
+      <c r="I108" t="n">
         <v>43</v>
       </c>
-      <c r="H108" t="n">
+      <c r="J108" t="n">
         <v>30</v>
-      </c>
-      <c r="I108" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J108" t="n">
-        <v>1.5</v>
       </c>
       <c r="K108" t="n">
         <v>1.9</v>
       </c>
       <c r="L108" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M108" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N108" t="n">
         <v>-21</v>
       </c>
-      <c r="M108" s="10" t="inlineStr">
+      <c r="O108" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -6101,27 +6781,33 @@
         </is>
       </c>
       <c r="F109" t="n">
+        <v>391</v>
+      </c>
+      <c r="G109" t="n">
+        <v>299</v>
+      </c>
+      <c r="H109" t="n">
         <v>71</v>
       </c>
-      <c r="G109" t="n">
+      <c r="I109" t="n">
         <v>48</v>
       </c>
-      <c r="H109" t="n">
+      <c r="J109" t="n">
         <v>33</v>
-      </c>
-      <c r="I109" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J109" t="n">
-        <v>1.6</v>
       </c>
       <c r="K109" t="n">
         <v>3.4</v>
       </c>
       <c r="L109" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M109" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N109" t="n">
         <v>-53</v>
       </c>
-      <c r="M109" s="10" t="inlineStr">
+      <c r="O109" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -6152,27 +6838,33 @@
         </is>
       </c>
       <c r="F110" t="n">
+        <v>351</v>
+      </c>
+      <c r="G110" t="n">
+        <v>297</v>
+      </c>
+      <c r="H110" t="n">
         <v>79</v>
       </c>
-      <c r="G110" t="n">
+      <c r="I110" t="n">
         <v>52</v>
       </c>
-      <c r="H110" t="n">
+      <c r="J110" t="n">
         <v>33</v>
-      </c>
-      <c r="I110" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J110" t="n">
-        <v>1</v>
       </c>
       <c r="K110" t="n">
         <v>1.6</v>
       </c>
       <c r="L110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N110" t="n">
         <v>-38</v>
       </c>
-      <c r="M110" s="13" t="inlineStr">
+      <c r="O110" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6203,27 +6895,33 @@
         </is>
       </c>
       <c r="F111" t="n">
+        <v>468</v>
+      </c>
+      <c r="G111" t="n">
+        <v>372</v>
+      </c>
+      <c r="H111" t="n">
         <v>79</v>
       </c>
-      <c r="G111" t="n">
+      <c r="I111" t="n">
         <v>47</v>
       </c>
-      <c r="H111" t="n">
+      <c r="J111" t="n">
         <v>31</v>
-      </c>
-      <c r="I111" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J111" t="n">
-        <v>1.3</v>
       </c>
       <c r="K111" t="n">
         <v>7.5</v>
       </c>
       <c r="L111" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M111" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N111" t="n">
         <v>-83</v>
       </c>
-      <c r="M111" s="10" t="inlineStr">
+      <c r="O111" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -6254,27 +6952,33 @@
         </is>
       </c>
       <c r="F112" t="n">
+        <v>417</v>
+      </c>
+      <c r="G112" t="n">
+        <v>356</v>
+      </c>
+      <c r="H112" t="n">
         <v>85</v>
       </c>
-      <c r="G112" t="n">
+      <c r="I112" t="n">
         <v>58</v>
       </c>
-      <c r="H112" t="n">
+      <c r="J112" t="n">
         <v>44</v>
-      </c>
-      <c r="I112" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J112" t="n">
-        <v>1.2</v>
       </c>
       <c r="K112" t="n">
         <v>2.5</v>
       </c>
       <c r="L112" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M112" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N112" t="n">
         <v>-52</v>
       </c>
-      <c r="M112" s="13" t="inlineStr">
+      <c r="O112" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6305,27 +7009,33 @@
         </is>
       </c>
       <c r="F113" t="n">
+        <v>438</v>
+      </c>
+      <c r="G113" t="n">
+        <v>381</v>
+      </c>
+      <c r="H113" t="n">
         <v>87</v>
       </c>
-      <c r="G113" t="n">
+      <c r="I113" t="n">
         <v>61</v>
       </c>
-      <c r="H113" t="n">
+      <c r="J113" t="n">
         <v>43</v>
-      </c>
-      <c r="I113" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J113" t="n">
-        <v>1.1</v>
       </c>
       <c r="K113" t="n">
         <v>1.7</v>
       </c>
       <c r="L113" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N113" t="n">
         <v>-35</v>
       </c>
-      <c r="M113" s="13" t="inlineStr">
+      <c r="O113" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6356,27 +7066,33 @@
         </is>
       </c>
       <c r="F114" t="n">
+        <v>446</v>
+      </c>
+      <c r="G114" t="n">
+        <v>410</v>
+      </c>
+      <c r="H114" t="n">
         <v>92</v>
       </c>
-      <c r="G114" t="n">
+      <c r="I114" t="n">
         <v>70</v>
       </c>
-      <c r="H114" t="n">
+      <c r="J114" t="n">
         <v>53</v>
-      </c>
-      <c r="I114" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J114" t="n">
-        <v>1.2</v>
       </c>
       <c r="K114" t="n">
         <v>1.9</v>
       </c>
       <c r="L114" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N114" t="n">
         <v>-37</v>
       </c>
-      <c r="M114" s="11" t="inlineStr">
+      <c r="O114" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -6407,27 +7123,33 @@
         </is>
       </c>
       <c r="F115" t="n">
+        <v>415</v>
+      </c>
+      <c r="G115" t="n">
+        <v>305</v>
+      </c>
+      <c r="H115" t="n">
         <v>73</v>
       </c>
-      <c r="G115" t="n">
+      <c r="I115" t="n">
         <v>41</v>
       </c>
-      <c r="H115" t="n">
+      <c r="J115" t="n">
         <v>26</v>
-      </c>
-      <c r="I115" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J115" t="n">
-        <v>1.4</v>
       </c>
       <c r="K115" t="n">
         <v>3.3</v>
       </c>
       <c r="L115" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M115" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N115" t="n">
         <v>-58</v>
       </c>
-      <c r="M115" s="10" t="inlineStr">
+      <c r="O115" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -6458,27 +7180,33 @@
         </is>
       </c>
       <c r="F116" t="n">
+        <v>401</v>
+      </c>
+      <c r="G116" t="n">
+        <v>348</v>
+      </c>
+      <c r="H116" t="n">
         <v>87</v>
       </c>
-      <c r="G116" t="n">
+      <c r="I116" t="n">
         <v>71</v>
       </c>
-      <c r="H116" t="n">
+      <c r="J116" t="n">
         <v>46</v>
-      </c>
-      <c r="I116" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J116" t="n">
-        <v>1.1</v>
       </c>
       <c r="K116" t="n">
         <v>1.7</v>
       </c>
       <c r="L116" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N116" t="n">
         <v>-35</v>
       </c>
-      <c r="M116" s="11" t="inlineStr">
+      <c r="O116" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -6509,27 +7237,33 @@
         </is>
       </c>
       <c r="F117" t="n">
+        <v>374</v>
+      </c>
+      <c r="G117" t="n">
+        <v>299</v>
+      </c>
+      <c r="H117" t="n">
         <v>80</v>
       </c>
-      <c r="G117" t="n">
+      <c r="I117" t="n">
         <v>61</v>
       </c>
-      <c r="H117" t="n">
+      <c r="J117" t="n">
         <v>43</v>
-      </c>
-      <c r="I117" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J117" t="n">
-        <v>1.1</v>
       </c>
       <c r="K117" t="n">
         <v>1.7</v>
       </c>
       <c r="L117" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N117" t="n">
         <v>-35</v>
       </c>
-      <c r="M117" s="13" t="inlineStr">
+      <c r="O117" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6560,27 +7294,33 @@
         </is>
       </c>
       <c r="F118" t="n">
+        <v>449</v>
+      </c>
+      <c r="G118" t="n">
+        <v>412</v>
+      </c>
+      <c r="H118" t="n">
         <v>92</v>
       </c>
-      <c r="G118" t="n">
+      <c r="I118" t="n">
         <v>84</v>
       </c>
-      <c r="H118" t="n">
+      <c r="J118" t="n">
         <v>66</v>
-      </c>
-      <c r="I118" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J118" t="n">
-        <v>3.6</v>
       </c>
       <c r="K118" t="n">
         <v>6.7</v>
       </c>
       <c r="L118" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M118" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N118" t="n">
         <v>-46</v>
       </c>
-      <c r="M118" s="11" t="inlineStr">
+      <c r="O118" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -6611,27 +7351,33 @@
         </is>
       </c>
       <c r="F119" t="n">
+        <v>323</v>
+      </c>
+      <c r="G119" t="n">
+        <v>246</v>
+      </c>
+      <c r="H119" t="n">
         <v>76</v>
       </c>
-      <c r="G119" t="n">
+      <c r="I119" t="n">
         <v>49</v>
       </c>
-      <c r="H119" t="n">
+      <c r="J119" t="n">
         <v>25</v>
-      </c>
-      <c r="I119" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J119" t="n">
-        <v>1.2</v>
       </c>
       <c r="K119" t="n">
         <v>2.8</v>
       </c>
       <c r="L119" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M119" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N119" t="n">
         <v>-57</v>
       </c>
-      <c r="M119" s="10" t="inlineStr">
+      <c r="O119" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -6662,27 +7408,33 @@
         </is>
       </c>
       <c r="F120" t="n">
+        <v>246</v>
+      </c>
+      <c r="G120" t="n">
+        <v>163</v>
+      </c>
+      <c r="H120" t="n">
         <v>83</v>
       </c>
-      <c r="G120" t="n">
+      <c r="I120" t="n">
         <v>58</v>
       </c>
-      <c r="H120" t="n">
+      <c r="J120" t="n">
         <v>34</v>
-      </c>
-      <c r="I120" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J120" t="n">
-        <v>1.1</v>
       </c>
       <c r="K120" t="n">
         <v>2.5</v>
       </c>
       <c r="L120" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M120" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N120" t="n">
         <v>-56</v>
       </c>
-      <c r="M120" s="13" t="inlineStr">
+      <c r="O120" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6713,27 +7465,33 @@
         </is>
       </c>
       <c r="F121" t="n">
+        <v>341</v>
+      </c>
+      <c r="G121" t="n">
+        <v>249</v>
+      </c>
+      <c r="H121" t="n">
         <v>91</v>
       </c>
-      <c r="G121" t="n">
+      <c r="I121" t="n">
         <v>62</v>
       </c>
-      <c r="H121" t="n">
+      <c r="J121" t="n">
         <v>37</v>
-      </c>
-      <c r="I121" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J121" t="n">
-        <v>1</v>
       </c>
       <c r="K121" t="n">
         <v>3.4</v>
       </c>
       <c r="L121" t="n">
+        <v>1</v>
+      </c>
+      <c r="M121" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N121" t="n">
         <v>-71</v>
       </c>
-      <c r="M121" s="13" t="inlineStr">
+      <c r="O121" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6764,27 +7522,33 @@
         </is>
       </c>
       <c r="F122" t="n">
+        <v>152</v>
+      </c>
+      <c r="G122" t="n">
+        <v>107</v>
+      </c>
+      <c r="H122" t="n">
         <v>88</v>
       </c>
-      <c r="G122" t="n">
+      <c r="I122" t="n">
         <v>56</v>
       </c>
-      <c r="H122" t="n">
+      <c r="J122" t="n">
         <v>39</v>
-      </c>
-      <c r="I122" t="n">
-        <v>3</v>
-      </c>
-      <c r="J122" t="n">
-        <v>1.4</v>
       </c>
       <c r="K122" t="n">
         <v>3</v>
       </c>
       <c r="L122" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M122" t="n">
+        <v>3</v>
+      </c>
+      <c r="N122" t="n">
         <v>-53</v>
       </c>
-      <c r="M122" s="13" t="inlineStr">
+      <c r="O122" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6815,27 +7579,33 @@
         </is>
       </c>
       <c r="F123" t="n">
+        <v>359</v>
+      </c>
+      <c r="G123" t="n">
+        <v>272</v>
+      </c>
+      <c r="H123" t="n">
         <v>95</v>
       </c>
-      <c r="G123" t="n">
+      <c r="I123" t="n">
         <v>63</v>
       </c>
-      <c r="H123" t="n">
+      <c r="J123" t="n">
         <v>32</v>
-      </c>
-      <c r="I123" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J123" t="n">
-        <v>1.1</v>
       </c>
       <c r="K123" t="n">
         <v>2.3</v>
       </c>
       <c r="L123" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M123" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N123" t="n">
         <v>-52</v>
       </c>
-      <c r="M123" s="13" t="inlineStr">
+      <c r="O123" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6866,27 +7636,33 @@
         </is>
       </c>
       <c r="F124" t="n">
+        <v>419</v>
+      </c>
+      <c r="G124" t="n">
+        <v>417</v>
+      </c>
+      <c r="H124" t="n">
         <v>95</v>
       </c>
-      <c r="G124" t="n">
+      <c r="I124" t="n">
         <v>88</v>
       </c>
-      <c r="H124" t="n">
+      <c r="J124" t="n">
         <v>66</v>
       </c>
-      <c r="I124" t="n">
+      <c r="K124" t="n">
         <v>4.3</v>
       </c>
-      <c r="J124" t="n">
+      <c r="L124" t="n">
         <v>3.4</v>
       </c>
-      <c r="K124" t="n">
+      <c r="M124" t="n">
         <v>5.9</v>
       </c>
-      <c r="L124" t="n">
+      <c r="N124" t="n">
         <v>-21</v>
       </c>
-      <c r="M124" s="11" t="inlineStr">
+      <c r="O124" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -6917,27 +7693,33 @@
         </is>
       </c>
       <c r="F125" t="n">
+        <v>394</v>
+      </c>
+      <c r="G125" t="n">
+        <v>349</v>
+      </c>
+      <c r="H125" t="n">
         <v>84</v>
       </c>
-      <c r="G125" t="n">
+      <c r="I125" t="n">
         <v>75</v>
       </c>
-      <c r="H125" t="n">
+      <c r="J125" t="n">
         <v>48</v>
-      </c>
-      <c r="I125" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J125" t="n">
-        <v>1.2</v>
       </c>
       <c r="K125" t="n">
         <v>1.7</v>
       </c>
       <c r="L125" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N125" t="n">
         <v>-29</v>
       </c>
-      <c r="M125" s="11" t="inlineStr">
+      <c r="O125" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -6968,27 +7750,33 @@
         </is>
       </c>
       <c r="F126" t="n">
+        <v>253</v>
+      </c>
+      <c r="G126" t="n">
+        <v>177</v>
+      </c>
+      <c r="H126" t="n">
         <v>66</v>
       </c>
-      <c r="G126" t="n">
+      <c r="I126" t="n">
         <v>47</v>
       </c>
-      <c r="H126" t="n">
+      <c r="J126" t="n">
         <v>24</v>
-      </c>
-      <c r="I126" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J126" t="n">
-        <v>1.2</v>
       </c>
       <c r="K126" t="n">
         <v>2.8</v>
       </c>
       <c r="L126" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M126" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N126" t="n">
         <v>-57</v>
       </c>
-      <c r="M126" s="10" t="inlineStr">
+      <c r="O126" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -7019,27 +7807,33 @@
         </is>
       </c>
       <c r="F127" t="n">
+        <v>258</v>
+      </c>
+      <c r="G127" t="n">
+        <v>175</v>
+      </c>
+      <c r="H127" t="n">
         <v>68</v>
       </c>
-      <c r="G127" t="n">
+      <c r="I127" t="n">
         <v>35</v>
       </c>
-      <c r="H127" t="n">
+      <c r="J127" t="n">
         <v>21</v>
       </c>
-      <c r="I127" t="n">
+      <c r="K127" t="n">
         <v>2.1</v>
       </c>
-      <c r="J127" t="n">
+      <c r="L127" t="n">
         <v>1.1</v>
       </c>
-      <c r="K127" t="n">
+      <c r="M127" t="n">
         <v>2.2</v>
       </c>
-      <c r="L127" t="n">
+      <c r="N127" t="n">
         <v>-48</v>
       </c>
-      <c r="M127" s="10" t="inlineStr">
+      <c r="O127" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -7070,27 +7864,33 @@
         </is>
       </c>
       <c r="F128" t="n">
+        <v>333</v>
+      </c>
+      <c r="G128" t="n">
+        <v>262</v>
+      </c>
+      <c r="H128" t="n">
         <v>78</v>
       </c>
-      <c r="G128" t="n">
+      <c r="I128" t="n">
         <v>47</v>
       </c>
-      <c r="H128" t="n">
+      <c r="J128" t="n">
         <v>36</v>
-      </c>
-      <c r="I128" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J128" t="n">
-        <v>1.2</v>
       </c>
       <c r="K128" t="n">
         <v>4.4</v>
       </c>
       <c r="L128" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M128" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N128" t="n">
         <v>-73</v>
       </c>
-      <c r="M128" s="10" t="inlineStr">
+      <c r="O128" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -7121,27 +7921,33 @@
         </is>
       </c>
       <c r="F129" t="n">
+        <v>369</v>
+      </c>
+      <c r="G129" t="n">
+        <v>311</v>
+      </c>
+      <c r="H129" t="n">
         <v>84</v>
       </c>
-      <c r="G129" t="n">
+      <c r="I129" t="n">
         <v>55</v>
       </c>
-      <c r="H129" t="n">
+      <c r="J129" t="n">
         <v>37</v>
-      </c>
-      <c r="I129" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J129" t="n">
-        <v>1.2</v>
       </c>
       <c r="K129" t="n">
         <v>5.4</v>
       </c>
       <c r="L129" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M129" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N129" t="n">
         <v>-78</v>
       </c>
-      <c r="M129" s="13" t="inlineStr">
+      <c r="O129" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7172,27 +7978,33 @@
         </is>
       </c>
       <c r="F130" t="n">
+        <v>353</v>
+      </c>
+      <c r="G130" t="n">
+        <v>358</v>
+      </c>
+      <c r="H130" t="n">
         <v>92</v>
       </c>
-      <c r="G130" t="n">
+      <c r="I130" t="n">
         <v>88</v>
       </c>
-      <c r="H130" t="n">
+      <c r="J130" t="n">
         <v>77</v>
       </c>
-      <c r="I130" t="n">
+      <c r="K130" t="n">
         <v>2.9</v>
       </c>
-      <c r="J130" t="n">
+      <c r="L130" t="n">
         <v>1.8</v>
       </c>
-      <c r="K130" t="n">
+      <c r="M130" t="n">
         <v>4.2</v>
       </c>
-      <c r="L130" t="n">
+      <c r="N130" t="n">
         <v>-38</v>
       </c>
-      <c r="M130" s="11" t="inlineStr">
+      <c r="O130" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7223,27 +8035,33 @@
         </is>
       </c>
       <c r="F131" t="n">
+        <v>239</v>
+      </c>
+      <c r="G131" t="n">
+        <v>191</v>
+      </c>
+      <c r="H131" t="n">
         <v>72</v>
       </c>
-      <c r="G131" t="n">
+      <c r="I131" t="n">
         <v>56</v>
       </c>
-      <c r="H131" t="n">
+      <c r="J131" t="n">
         <v>41</v>
-      </c>
-      <c r="I131" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J131" t="n">
-        <v>1.2</v>
       </c>
       <c r="K131" t="n">
         <v>2.1</v>
       </c>
       <c r="L131" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M131" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N131" t="n">
         <v>-43</v>
       </c>
-      <c r="M131" s="13" t="inlineStr">
+      <c r="O131" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7274,27 +8092,33 @@
         </is>
       </c>
       <c r="F132" t="n">
+        <v>323</v>
+      </c>
+      <c r="G132" t="n">
+        <v>322</v>
+      </c>
+      <c r="H132" t="n">
         <v>90</v>
       </c>
-      <c r="G132" t="n">
+      <c r="I132" t="n">
         <v>77</v>
       </c>
-      <c r="H132" t="n">
+      <c r="J132" t="n">
         <v>60</v>
-      </c>
-      <c r="I132" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J132" t="n">
-        <v>1.6</v>
       </c>
       <c r="K132" t="n">
         <v>2.7</v>
       </c>
       <c r="L132" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M132" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N132" t="n">
         <v>-41</v>
       </c>
-      <c r="M132" s="11" t="inlineStr">
+      <c r="O132" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7325,27 +8149,33 @@
         </is>
       </c>
       <c r="F133" t="n">
+        <v>367</v>
+      </c>
+      <c r="G133" t="n">
+        <v>368</v>
+      </c>
+      <c r="H133" t="n">
         <v>91</v>
       </c>
-      <c r="G133" t="n">
+      <c r="I133" t="n">
         <v>77</v>
       </c>
-      <c r="H133" t="n">
+      <c r="J133" t="n">
         <v>51</v>
       </c>
-      <c r="I133" t="n">
+      <c r="K133" t="n">
         <v>5.1</v>
       </c>
-      <c r="J133" t="n">
+      <c r="L133" t="n">
         <v>1.4</v>
       </c>
-      <c r="K133" t="n">
+      <c r="M133" t="n">
         <v>5.8</v>
       </c>
-      <c r="L133" t="n">
+      <c r="N133" t="n">
         <v>-73</v>
       </c>
-      <c r="M133" s="11" t="inlineStr">
+      <c r="O133" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7376,27 +8206,33 @@
         </is>
       </c>
       <c r="F134" t="n">
+        <v>282</v>
+      </c>
+      <c r="G134" t="n">
+        <v>233</v>
+      </c>
+      <c r="H134" t="n">
         <v>72</v>
       </c>
-      <c r="G134" t="n">
+      <c r="I134" t="n">
         <v>51</v>
       </c>
-      <c r="H134" t="n">
+      <c r="J134" t="n">
         <v>34</v>
-      </c>
-      <c r="I134" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J134" t="n">
-        <v>1.1</v>
       </c>
       <c r="K134" t="n">
         <v>1.9</v>
       </c>
       <c r="L134" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M134" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N134" t="n">
         <v>-42</v>
       </c>
-      <c r="M134" s="13" t="inlineStr">
+      <c r="O134" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7427,27 +8263,33 @@
         </is>
       </c>
       <c r="F135" t="n">
+        <v>325</v>
+      </c>
+      <c r="G135" t="n">
+        <v>258</v>
+      </c>
+      <c r="H135" t="n">
         <v>69</v>
       </c>
-      <c r="G135" t="n">
+      <c r="I135" t="n">
         <v>42</v>
       </c>
-      <c r="H135" t="n">
+      <c r="J135" t="n">
         <v>22</v>
-      </c>
-      <c r="I135" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J135" t="n">
-        <v>1.2</v>
       </c>
       <c r="K135" t="n">
         <v>3.6</v>
       </c>
       <c r="L135" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M135" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N135" t="n">
         <v>-67</v>
       </c>
-      <c r="M135" s="10" t="inlineStr">
+      <c r="O135" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -7478,27 +8320,33 @@
         </is>
       </c>
       <c r="F136" t="n">
+        <v>397</v>
+      </c>
+      <c r="G136" t="n">
+        <v>411</v>
+      </c>
+      <c r="H136" t="n">
         <v>90</v>
       </c>
-      <c r="G136" t="n">
+      <c r="I136" t="n">
         <v>74</v>
       </c>
-      <c r="H136" t="n">
+      <c r="J136" t="n">
         <v>58</v>
       </c>
-      <c r="I136" t="n">
+      <c r="K136" t="n">
         <v>3.4</v>
       </c>
-      <c r="J136" t="n">
+      <c r="L136" t="n">
         <v>1.5</v>
       </c>
-      <c r="K136" t="n">
+      <c r="M136" t="n">
         <v>4.2</v>
       </c>
-      <c r="L136" t="n">
+      <c r="N136" t="n">
         <v>-56</v>
       </c>
-      <c r="M136" s="11" t="inlineStr">
+      <c r="O136" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7529,27 +8377,33 @@
         </is>
       </c>
       <c r="F137" t="n">
+        <v>383</v>
+      </c>
+      <c r="G137" t="n">
+        <v>297</v>
+      </c>
+      <c r="H137" t="n">
         <v>96</v>
       </c>
-      <c r="G137" t="n">
+      <c r="I137" t="n">
         <v>71</v>
       </c>
-      <c r="H137" t="n">
+      <c r="J137" t="n">
         <v>53</v>
       </c>
-      <c r="I137" t="n">
+      <c r="K137" t="n">
         <v>6</v>
       </c>
-      <c r="J137" t="n">
+      <c r="L137" t="n">
         <v>1.5</v>
       </c>
-      <c r="K137" t="n">
+      <c r="M137" t="n">
         <v>7</v>
       </c>
-      <c r="L137" t="n">
+      <c r="N137" t="n">
         <v>-75</v>
       </c>
-      <c r="M137" s="11" t="inlineStr">
+      <c r="O137" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7580,27 +8434,33 @@
         </is>
       </c>
       <c r="F138" t="n">
+        <v>298</v>
+      </c>
+      <c r="G138" t="n">
+        <v>242</v>
+      </c>
+      <c r="H138" t="n">
         <v>79</v>
       </c>
-      <c r="G138" t="n">
+      <c r="I138" t="n">
         <v>66</v>
       </c>
-      <c r="H138" t="n">
+      <c r="J138" t="n">
         <v>36</v>
-      </c>
-      <c r="I138" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J138" t="n">
-        <v>1.1</v>
       </c>
       <c r="K138" t="n">
         <v>1.8</v>
       </c>
       <c r="L138" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N138" t="n">
         <v>-39</v>
       </c>
-      <c r="M138" s="11" t="inlineStr">
+      <c r="O138" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7631,27 +8491,33 @@
         </is>
       </c>
       <c r="F139" t="n">
+        <v>359</v>
+      </c>
+      <c r="G139" t="n">
+        <v>308</v>
+      </c>
+      <c r="H139" t="n">
         <v>84</v>
       </c>
-      <c r="G139" t="n">
+      <c r="I139" t="n">
         <v>66</v>
       </c>
-      <c r="H139" t="n">
+      <c r="J139" t="n">
         <v>33</v>
-      </c>
-      <c r="I139" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J139" t="n">
-        <v>1.1</v>
       </c>
       <c r="K139" t="n">
         <v>3.8</v>
       </c>
       <c r="L139" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M139" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N139" t="n">
         <v>-71</v>
       </c>
-      <c r="M139" s="11" t="inlineStr">
+      <c r="O139" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7682,27 +8548,33 @@
         </is>
       </c>
       <c r="F140" t="n">
+        <v>332</v>
+      </c>
+      <c r="G140" t="n">
+        <v>294</v>
+      </c>
+      <c r="H140" t="n">
         <v>86</v>
       </c>
-      <c r="G140" t="n">
+      <c r="I140" t="n">
         <v>72</v>
       </c>
-      <c r="H140" t="n">
+      <c r="J140" t="n">
         <v>44</v>
-      </c>
-      <c r="I140" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J140" t="n">
-        <v>1</v>
       </c>
       <c r="K140" t="n">
         <v>1.4</v>
       </c>
       <c r="L140" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N140" t="n">
         <v>-29</v>
       </c>
-      <c r="M140" s="11" t="inlineStr">
+      <c r="O140" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7733,27 +8605,33 @@
         </is>
       </c>
       <c r="F141" t="n">
+        <v>289</v>
+      </c>
+      <c r="G141" t="n">
+        <v>257</v>
+      </c>
+      <c r="H141" t="n">
         <v>84</v>
       </c>
-      <c r="G141" t="n">
+      <c r="I141" t="n">
         <v>61</v>
       </c>
-      <c r="H141" t="n">
+      <c r="J141" t="n">
         <v>35</v>
-      </c>
-      <c r="I141" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J141" t="n">
-        <v>1.2</v>
       </c>
       <c r="K141" t="n">
         <v>2.9</v>
       </c>
       <c r="L141" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M141" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N141" t="n">
         <v>-59</v>
       </c>
-      <c r="M141" s="13" t="inlineStr">
+      <c r="O141" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7784,27 +8662,33 @@
         </is>
       </c>
       <c r="F142" t="n">
+        <v>228</v>
+      </c>
+      <c r="G142" t="n">
+        <v>166</v>
+      </c>
+      <c r="H142" t="n">
         <v>77</v>
       </c>
-      <c r="G142" t="n">
+      <c r="I142" t="n">
         <v>60</v>
       </c>
-      <c r="H142" t="n">
+      <c r="J142" t="n">
         <v>54</v>
       </c>
-      <c r="I142" t="n">
+      <c r="K142" t="n">
         <v>4.4</v>
       </c>
-      <c r="J142" t="n">
+      <c r="L142" t="n">
         <v>3.3</v>
       </c>
-      <c r="K142" t="n">
+      <c r="M142" t="n">
         <v>4.7</v>
       </c>
-      <c r="L142" t="n">
+      <c r="N142" t="n">
         <v>-25</v>
       </c>
-      <c r="M142" s="13" t="inlineStr">
+      <c r="O142" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7835,27 +8719,33 @@
         </is>
       </c>
       <c r="F143" t="n">
+        <v>291</v>
+      </c>
+      <c r="G143" t="n">
+        <v>280</v>
+      </c>
+      <c r="H143" t="n">
         <v>82</v>
       </c>
-      <c r="G143" t="n">
+      <c r="I143" t="n">
         <v>62</v>
       </c>
-      <c r="H143" t="n">
+      <c r="J143" t="n">
         <v>45</v>
-      </c>
-      <c r="I143" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J143" t="n">
-        <v>1.2</v>
       </c>
       <c r="K143" t="n">
         <v>2.6</v>
       </c>
       <c r="L143" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M143" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N143" t="n">
         <v>-54</v>
       </c>
-      <c r="M143" s="13" t="inlineStr">
+      <c r="O143" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7886,27 +8776,33 @@
         </is>
       </c>
       <c r="F144" t="n">
+        <v>264</v>
+      </c>
+      <c r="G144" t="n">
+        <v>315</v>
+      </c>
+      <c r="H144" t="n">
         <v>102</v>
       </c>
-      <c r="G144" t="n">
+      <c r="I144" t="n">
         <v>98</v>
       </c>
-      <c r="H144" t="n">
+      <c r="J144" t="n">
         <v>92</v>
       </c>
-      <c r="I144" t="n">
+      <c r="K144" t="n">
         <v>12.1</v>
       </c>
-      <c r="J144" t="n">
+      <c r="L144" t="n">
         <v>4.1</v>
       </c>
-      <c r="K144" t="n">
+      <c r="M144" t="n">
         <v>12.2</v>
       </c>
-      <c r="L144" t="n">
+      <c r="N144" t="n">
         <v>-66</v>
       </c>
-      <c r="M144" s="11" t="inlineStr">
+      <c r="O144" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7937,27 +8833,33 @@
         </is>
       </c>
       <c r="F145" t="n">
+        <v>270</v>
+      </c>
+      <c r="G145" t="n">
+        <v>264</v>
+      </c>
+      <c r="H145" t="n">
         <v>84</v>
       </c>
-      <c r="G145" t="n">
+      <c r="I145" t="n">
         <v>65</v>
       </c>
-      <c r="H145" t="n">
+      <c r="J145" t="n">
         <v>50</v>
-      </c>
-      <c r="I145" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J145" t="n">
-        <v>1.5</v>
       </c>
       <c r="K145" t="n">
         <v>5.5</v>
       </c>
       <c r="L145" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M145" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N145" t="n">
         <v>-73</v>
       </c>
-      <c r="M145" s="13" t="inlineStr">
+      <c r="O145" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7988,27 +8890,33 @@
         </is>
       </c>
       <c r="F146" t="n">
+        <v>246</v>
+      </c>
+      <c r="G146" t="n">
+        <v>224</v>
+      </c>
+      <c r="H146" t="n">
         <v>88</v>
       </c>
-      <c r="G146" t="n">
+      <c r="I146" t="n">
         <v>73</v>
       </c>
-      <c r="H146" t="n">
+      <c r="J146" t="n">
         <v>55</v>
-      </c>
-      <c r="I146" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J146" t="n">
-        <v>1.1</v>
       </c>
       <c r="K146" t="n">
         <v>1.5</v>
       </c>
       <c r="L146" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M146" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N146" t="n">
         <v>-27</v>
       </c>
-      <c r="M146" s="11" t="inlineStr">
+      <c r="O146" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8039,27 +8947,33 @@
         </is>
       </c>
       <c r="F147" t="n">
+        <v>274</v>
+      </c>
+      <c r="G147" t="n">
+        <v>235</v>
+      </c>
+      <c r="H147" t="n">
         <v>83</v>
       </c>
-      <c r="G147" t="n">
+      <c r="I147" t="n">
         <v>59</v>
       </c>
-      <c r="H147" t="n">
+      <c r="J147" t="n">
         <v>40</v>
-      </c>
-      <c r="I147" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J147" t="n">
-        <v>1.2</v>
       </c>
       <c r="K147" t="n">
         <v>3.8</v>
       </c>
       <c r="L147" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M147" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N147" t="n">
         <v>-68</v>
       </c>
-      <c r="M147" s="13" t="inlineStr">
+      <c r="O147" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8090,27 +9004,33 @@
         </is>
       </c>
       <c r="F148" t="n">
+        <v>267</v>
+      </c>
+      <c r="G148" t="n">
+        <v>277</v>
+      </c>
+      <c r="H148" t="n">
         <v>100</v>
       </c>
-      <c r="G148" t="n">
+      <c r="I148" t="n">
         <v>90</v>
       </c>
-      <c r="H148" t="n">
+      <c r="J148" t="n">
         <v>72</v>
       </c>
-      <c r="I148" t="n">
+      <c r="K148" t="n">
         <v>2.3</v>
       </c>
-      <c r="J148" t="n">
+      <c r="L148" t="n">
         <v>1.4</v>
       </c>
-      <c r="K148" t="n">
+      <c r="M148" t="n">
         <v>3.8</v>
       </c>
-      <c r="L148" t="n">
+      <c r="N148" t="n">
         <v>-39</v>
       </c>
-      <c r="M148" s="11" t="inlineStr">
+      <c r="O148" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8141,27 +9061,33 @@
         </is>
       </c>
       <c r="F149" t="n">
+        <v>189</v>
+      </c>
+      <c r="G149" t="n">
+        <v>136</v>
+      </c>
+      <c r="H149" t="n">
         <v>70</v>
       </c>
-      <c r="G149" t="n">
+      <c r="I149" t="n">
         <v>46</v>
       </c>
-      <c r="H149" t="n">
+      <c r="J149" t="n">
         <v>28</v>
-      </c>
-      <c r="I149" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J149" t="n">
-        <v>1.2</v>
       </c>
       <c r="K149" t="n">
         <v>2.5</v>
       </c>
       <c r="L149" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M149" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N149" t="n">
         <v>-52</v>
       </c>
-      <c r="M149" s="10" t="inlineStr">
+      <c r="O149" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -8192,27 +9118,33 @@
         </is>
       </c>
       <c r="F150" t="n">
+        <v>217</v>
+      </c>
+      <c r="G150" t="n">
+        <v>188</v>
+      </c>
+      <c r="H150" t="n">
         <v>84</v>
       </c>
-      <c r="G150" t="n">
+      <c r="I150" t="n">
         <v>68</v>
       </c>
-      <c r="H150" t="n">
+      <c r="J150" t="n">
         <v>47</v>
-      </c>
-      <c r="I150" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J150" t="n">
-        <v>1</v>
       </c>
       <c r="K150" t="n">
         <v>1.7</v>
       </c>
       <c r="L150" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N150" t="n">
         <v>-41</v>
       </c>
-      <c r="M150" s="11" t="inlineStr">
+      <c r="O150" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8243,27 +9175,33 @@
         </is>
       </c>
       <c r="F151" t="n">
+        <v>262</v>
+      </c>
+      <c r="G151" t="n">
+        <v>218</v>
+      </c>
+      <c r="H151" t="n">
         <v>81</v>
       </c>
-      <c r="G151" t="n">
+      <c r="I151" t="n">
         <v>60</v>
       </c>
-      <c r="H151" t="n">
+      <c r="J151" t="n">
         <v>41</v>
-      </c>
-      <c r="I151" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J151" t="n">
-        <v>1.3</v>
       </c>
       <c r="K151" t="n">
         <v>4.1</v>
       </c>
       <c r="L151" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M151" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N151" t="n">
         <v>-68</v>
       </c>
-      <c r="M151" s="13" t="inlineStr">
+      <c r="O151" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8294,27 +9232,33 @@
         </is>
       </c>
       <c r="F152" t="n">
+        <v>149</v>
+      </c>
+      <c r="G152" t="n">
+        <v>88</v>
+      </c>
+      <c r="H152" t="n">
         <v>57</v>
       </c>
-      <c r="G152" t="n">
+      <c r="I152" t="n">
         <v>33</v>
       </c>
-      <c r="H152" t="n">
+      <c r="J152" t="n">
         <v>19</v>
-      </c>
-      <c r="I152" t="n">
-        <v>2</v>
-      </c>
-      <c r="J152" t="n">
-        <v>1.1</v>
       </c>
       <c r="K152" t="n">
         <v>2</v>
       </c>
       <c r="L152" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M152" t="n">
+        <v>2</v>
+      </c>
+      <c r="N152" t="n">
         <v>-45</v>
       </c>
-      <c r="M152" s="10" t="inlineStr">
+      <c r="O152" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -8345,27 +9289,33 @@
         </is>
       </c>
       <c r="F153" t="n">
+        <v>297</v>
+      </c>
+      <c r="G153" t="n">
+        <v>242</v>
+      </c>
+      <c r="H153" t="n">
         <v>76</v>
       </c>
-      <c r="G153" t="n">
+      <c r="I153" t="n">
         <v>50</v>
       </c>
-      <c r="H153" t="n">
+      <c r="J153" t="n">
         <v>35</v>
-      </c>
-      <c r="I153" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J153" t="n">
-        <v>1.2</v>
       </c>
       <c r="K153" t="n">
         <v>3.2</v>
       </c>
       <c r="L153" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M153" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N153" t="n">
         <v>-62</v>
       </c>
-      <c r="M153" s="13" t="inlineStr">
+      <c r="O153" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8396,27 +9346,33 @@
         </is>
       </c>
       <c r="F154" t="n">
+        <v>305</v>
+      </c>
+      <c r="G154" t="n">
+        <v>279</v>
+      </c>
+      <c r="H154" t="n">
         <v>85</v>
       </c>
-      <c r="G154" t="n">
+      <c r="I154" t="n">
         <v>66</v>
       </c>
-      <c r="H154" t="n">
+      <c r="J154" t="n">
         <v>47</v>
-      </c>
-      <c r="I154" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J154" t="n">
-        <v>1.1</v>
       </c>
       <c r="K154" t="n">
         <v>1.4</v>
       </c>
       <c r="L154" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M154" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N154" t="n">
         <v>-21</v>
       </c>
-      <c r="M154" s="11" t="inlineStr">
+      <c r="O154" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8447,27 +9403,33 @@
         </is>
       </c>
       <c r="F155" t="n">
+        <v>322</v>
+      </c>
+      <c r="G155" t="n">
+        <v>291</v>
+      </c>
+      <c r="H155" t="n">
         <v>84</v>
       </c>
-      <c r="G155" t="n">
+      <c r="I155" t="n">
         <v>63</v>
       </c>
-      <c r="H155" t="n">
+      <c r="J155" t="n">
         <v>41</v>
-      </c>
-      <c r="I155" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J155" t="n">
-        <v>1.1</v>
       </c>
       <c r="K155" t="n">
         <v>3.4</v>
       </c>
       <c r="L155" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M155" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N155" t="n">
         <v>-68</v>
       </c>
-      <c r="M155" s="13" t="inlineStr">
+      <c r="O155" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8498,27 +9460,33 @@
         </is>
       </c>
       <c r="F156" t="n">
+        <v>305</v>
+      </c>
+      <c r="G156" t="n">
+        <v>267</v>
+      </c>
+      <c r="H156" t="n">
         <v>81</v>
       </c>
-      <c r="G156" t="n">
+      <c r="I156" t="n">
         <v>53</v>
       </c>
-      <c r="H156" t="n">
+      <c r="J156" t="n">
         <v>30</v>
-      </c>
-      <c r="I156" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J156" t="n">
-        <v>1.2</v>
       </c>
       <c r="K156" t="n">
         <v>4.2</v>
       </c>
       <c r="L156" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M156" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N156" t="n">
         <v>-71</v>
       </c>
-      <c r="M156" s="13" t="inlineStr">
+      <c r="O156" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8549,34 +9517,40 @@
         </is>
       </c>
       <c r="F157" t="n">
+        <v>423</v>
+      </c>
+      <c r="G157" t="n">
+        <v>325</v>
+      </c>
+      <c r="H157" t="n">
         <v>94</v>
       </c>
-      <c r="G157" t="n">
+      <c r="I157" t="n">
         <v>76</v>
       </c>
-      <c r="H157" t="n">
+      <c r="J157" t="n">
         <v>55</v>
       </c>
-      <c r="I157" t="n">
+      <c r="K157" t="n">
         <v>7.2</v>
       </c>
-      <c r="J157" t="n">
+      <c r="L157" t="n">
         <v>2.1</v>
       </c>
-      <c r="K157" t="n">
+      <c r="M157" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="L157" t="n">
+      <c r="N157" t="n">
         <v>-71</v>
       </c>
-      <c r="M157" s="11" t="inlineStr">
+      <c r="O157" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="12" t="inlineStr">
+      <c r="A158" s="13" t="inlineStr">
         <is>
           <t>LスマスロモンキーターンＶ</t>
         </is>
@@ -8600,27 +9574,33 @@
         </is>
       </c>
       <c r="F158" t="n">
+        <v>338</v>
+      </c>
+      <c r="G158" t="n">
+        <v>309</v>
+      </c>
+      <c r="H158" t="n">
         <v>95</v>
       </c>
-      <c r="G158" t="n">
+      <c r="I158" t="n">
         <v>83</v>
       </c>
-      <c r="H158" t="n">
+      <c r="J158" t="n">
         <v>77</v>
       </c>
-      <c r="I158" t="n">
+      <c r="K158" t="n">
         <v>4.2</v>
       </c>
-      <c r="J158" t="n">
+      <c r="L158" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K158" t="n">
+      <c r="M158" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="L158" t="n">
+      <c r="N158" t="n">
         <v>95</v>
       </c>
-      <c r="M158" s="11" t="inlineStr">
+      <c r="O158" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8651,27 +9631,33 @@
         </is>
       </c>
       <c r="F159" t="n">
+        <v>295</v>
+      </c>
+      <c r="G159" t="n">
+        <v>243</v>
+      </c>
+      <c r="H159" t="n">
         <v>86</v>
       </c>
-      <c r="G159" t="n">
+      <c r="I159" t="n">
         <v>71</v>
       </c>
-      <c r="H159" t="n">
+      <c r="J159" t="n">
         <v>51</v>
       </c>
-      <c r="I159" t="n">
+      <c r="K159" t="n">
         <v>2</v>
       </c>
-      <c r="J159" t="n">
+      <c r="L159" t="n">
         <v>1.3</v>
       </c>
-      <c r="K159" t="n">
+      <c r="M159" t="n">
         <v>2.1</v>
       </c>
-      <c r="L159" t="n">
+      <c r="N159" t="n">
         <v>-35</v>
       </c>
-      <c r="M159" s="11" t="inlineStr">
+      <c r="O159" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8702,27 +9688,33 @@
         </is>
       </c>
       <c r="F160" t="n">
+        <v>298</v>
+      </c>
+      <c r="G160" t="n">
+        <v>255</v>
+      </c>
+      <c r="H160" t="n">
         <v>89</v>
       </c>
-      <c r="G160" t="n">
+      <c r="I160" t="n">
         <v>68</v>
       </c>
-      <c r="H160" t="n">
+      <c r="J160" t="n">
         <v>47</v>
-      </c>
-      <c r="I160" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J160" t="n">
-        <v>1.1</v>
       </c>
       <c r="K160" t="n">
         <v>1.9</v>
       </c>
       <c r="L160" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M160" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N160" t="n">
         <v>-42</v>
       </c>
-      <c r="M160" s="11" t="inlineStr">
+      <c r="O160" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8753,27 +9745,33 @@
         </is>
       </c>
       <c r="F161" t="n">
+        <v>364</v>
+      </c>
+      <c r="G161" t="n">
+        <v>328</v>
+      </c>
+      <c r="H161" t="n">
         <v>94</v>
       </c>
-      <c r="G161" t="n">
+      <c r="I161" t="n">
         <v>81</v>
       </c>
-      <c r="H161" t="n">
+      <c r="J161" t="n">
         <v>61</v>
       </c>
-      <c r="I161" t="n">
+      <c r="K161" t="n">
         <v>2</v>
       </c>
-      <c r="J161" t="n">
+      <c r="L161" t="n">
         <v>1.2</v>
       </c>
-      <c r="K161" t="n">
+      <c r="M161" t="n">
         <v>2.5</v>
       </c>
-      <c r="L161" t="n">
+      <c r="N161" t="n">
         <v>-40</v>
       </c>
-      <c r="M161" s="11" t="inlineStr">
+      <c r="O161" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8804,27 +9802,33 @@
         </is>
       </c>
       <c r="F162" t="n">
+        <v>217</v>
+      </c>
+      <c r="G162" t="n">
+        <v>124</v>
+      </c>
+      <c r="H162" t="n">
         <v>60</v>
       </c>
-      <c r="G162" t="n">
+      <c r="I162" t="n">
         <v>33</v>
       </c>
-      <c r="H162" t="n">
+      <c r="J162" t="n">
         <v>18</v>
-      </c>
-      <c r="I162" t="n">
-        <v>5</v>
-      </c>
-      <c r="J162" t="n">
-        <v>1.3</v>
       </c>
       <c r="K162" t="n">
         <v>5</v>
       </c>
       <c r="L162" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M162" t="n">
+        <v>5</v>
+      </c>
+      <c r="N162" t="n">
         <v>-74</v>
       </c>
-      <c r="M162" s="10" t="inlineStr">
+      <c r="O162" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -8855,27 +9859,33 @@
         </is>
       </c>
       <c r="F163" t="n">
+        <v>212</v>
+      </c>
+      <c r="G163" t="n">
+        <v>160</v>
+      </c>
+      <c r="H163" t="n">
         <v>68</v>
       </c>
-      <c r="G163" t="n">
+      <c r="I163" t="n">
         <v>35</v>
       </c>
-      <c r="H163" t="n">
+      <c r="J163" t="n">
         <v>25</v>
-      </c>
-      <c r="I163" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J163" t="n">
-        <v>1.3</v>
       </c>
       <c r="K163" t="n">
         <v>3.2</v>
       </c>
       <c r="L163" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M163" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N163" t="n">
         <v>-59</v>
       </c>
-      <c r="M163" s="10" t="inlineStr">
+      <c r="O163" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -8906,27 +9916,33 @@
         </is>
       </c>
       <c r="F164" t="n">
+        <v>308</v>
+      </c>
+      <c r="G164" t="n">
+        <v>317</v>
+      </c>
+      <c r="H164" t="n">
         <v>89</v>
       </c>
-      <c r="G164" t="n">
+      <c r="I164" t="n">
         <v>67</v>
       </c>
-      <c r="H164" t="n">
+      <c r="J164" t="n">
         <v>48</v>
-      </c>
-      <c r="I164" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J164" t="n">
-        <v>1.2</v>
       </c>
       <c r="K164" t="n">
         <v>3.6</v>
       </c>
       <c r="L164" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M164" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N164" t="n">
         <v>-67</v>
       </c>
-      <c r="M164" s="11" t="inlineStr">
+      <c r="O164" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8957,27 +9973,33 @@
         </is>
       </c>
       <c r="F165" t="n">
+        <v>222</v>
+      </c>
+      <c r="G165" t="n">
+        <v>126</v>
+      </c>
+      <c r="H165" t="n">
         <v>49</v>
       </c>
-      <c r="G165" t="n">
+      <c r="I165" t="n">
         <v>22</v>
       </c>
-      <c r="H165" t="n">
+      <c r="J165" t="n">
         <v>16</v>
-      </c>
-      <c r="I165" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J165" t="n">
-        <v>1.5</v>
       </c>
       <c r="K165" t="n">
         <v>6.2</v>
       </c>
       <c r="L165" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M165" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="N165" t="n">
         <v>-76</v>
       </c>
-      <c r="M165" s="10" t="inlineStr">
+      <c r="O165" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -9008,27 +10030,33 @@
         </is>
       </c>
       <c r="F166" t="n">
+        <v>214</v>
+      </c>
+      <c r="G166" t="n">
+        <v>176</v>
+      </c>
+      <c r="H166" t="n">
         <v>71</v>
       </c>
-      <c r="G166" t="n">
+      <c r="I166" t="n">
         <v>71</v>
       </c>
-      <c r="H166" t="n">
+      <c r="J166" t="n">
         <v>42</v>
-      </c>
-      <c r="I166" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J166" t="n">
-        <v>1.2</v>
       </c>
       <c r="K166" t="n">
         <v>2.3</v>
       </c>
       <c r="L166" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M166" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N166" t="n">
         <v>-48</v>
       </c>
-      <c r="M166" s="11" t="inlineStr">
+      <c r="O166" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9059,27 +10087,33 @@
         </is>
       </c>
       <c r="F167" t="n">
+        <v>242</v>
+      </c>
+      <c r="G167" t="n">
+        <v>211</v>
+      </c>
+      <c r="H167" t="n">
         <v>75</v>
       </c>
-      <c r="G167" t="n">
+      <c r="I167" t="n">
         <v>47</v>
       </c>
-      <c r="H167" t="n">
+      <c r="J167" t="n">
         <v>31</v>
-      </c>
-      <c r="I167" t="n">
-        <v>3</v>
-      </c>
-      <c r="J167" t="n">
-        <v>1.2</v>
       </c>
       <c r="K167" t="n">
         <v>3</v>
       </c>
       <c r="L167" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M167" t="n">
+        <v>3</v>
+      </c>
+      <c r="N167" t="n">
         <v>-60</v>
       </c>
-      <c r="M167" s="10" t="inlineStr">
+      <c r="O167" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -9110,27 +10144,33 @@
         </is>
       </c>
       <c r="F168" t="n">
+        <v>191</v>
+      </c>
+      <c r="G168" t="n">
+        <v>102</v>
+      </c>
+      <c r="H168" t="n">
         <v>53</v>
       </c>
-      <c r="G168" t="n">
+      <c r="I168" t="n">
         <v>23</v>
       </c>
-      <c r="H168" t="n">
+      <c r="J168" t="n">
         <v>12</v>
-      </c>
-      <c r="I168" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J168" t="n">
-        <v>1.4</v>
       </c>
       <c r="K168" t="n">
         <v>4.7</v>
       </c>
       <c r="L168" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M168" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N168" t="n">
         <v>-70</v>
       </c>
-      <c r="M168" s="10" t="inlineStr">
+      <c r="O168" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -9161,27 +10201,33 @@
         </is>
       </c>
       <c r="F169" t="n">
+        <v>281</v>
+      </c>
+      <c r="G169" t="n">
+        <v>246</v>
+      </c>
+      <c r="H169" t="n">
         <v>87</v>
       </c>
-      <c r="G169" t="n">
+      <c r="I169" t="n">
         <v>65</v>
       </c>
-      <c r="H169" t="n">
+      <c r="J169" t="n">
         <v>41</v>
-      </c>
-      <c r="I169" t="n">
-        <v>3</v>
-      </c>
-      <c r="J169" t="n">
-        <v>1.1</v>
       </c>
       <c r="K169" t="n">
         <v>3</v>
       </c>
       <c r="L169" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M169" t="n">
+        <v>3</v>
+      </c>
+      <c r="N169" t="n">
         <v>-63</v>
       </c>
-      <c r="M169" s="13" t="inlineStr">
+      <c r="O169" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -9212,27 +10258,33 @@
         </is>
       </c>
       <c r="F170" t="n">
+        <v>211</v>
+      </c>
+      <c r="G170" t="n">
+        <v>190</v>
+      </c>
+      <c r="H170" t="n">
         <v>79</v>
       </c>
-      <c r="G170" t="n">
+      <c r="I170" t="n">
         <v>54</v>
       </c>
-      <c r="H170" t="n">
+      <c r="J170" t="n">
         <v>37</v>
       </c>
-      <c r="I170" t="n">
+      <c r="K170" t="n">
         <v>1.9</v>
       </c>
-      <c r="J170" t="n">
+      <c r="L170" t="n">
         <v>1.1</v>
       </c>
-      <c r="K170" t="n">
+      <c r="M170" t="n">
         <v>2</v>
       </c>
-      <c r="L170" t="n">
+      <c r="N170" t="n">
         <v>-42</v>
       </c>
-      <c r="M170" s="13" t="inlineStr">
+      <c r="O170" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -9263,27 +10315,33 @@
         </is>
       </c>
       <c r="F171" t="n">
+        <v>223</v>
+      </c>
+      <c r="G171" t="n">
+        <v>216</v>
+      </c>
+      <c r="H171" t="n">
         <v>85</v>
       </c>
-      <c r="G171" t="n">
+      <c r="I171" t="n">
         <v>58</v>
       </c>
-      <c r="H171" t="n">
+      <c r="J171" t="n">
         <v>45</v>
-      </c>
-      <c r="I171" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J171" t="n">
-        <v>1.2</v>
       </c>
       <c r="K171" t="n">
         <v>2.1</v>
       </c>
       <c r="L171" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M171" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N171" t="n">
         <v>-43</v>
       </c>
-      <c r="M171" s="13" t="inlineStr">
+      <c r="O171" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -9314,34 +10372,40 @@
         </is>
       </c>
       <c r="F172" t="n">
+        <v>231</v>
+      </c>
+      <c r="G172" t="n">
+        <v>217</v>
+      </c>
+      <c r="H172" t="n">
         <v>83</v>
       </c>
-      <c r="G172" t="n">
+      <c r="I172" t="n">
         <v>63</v>
       </c>
-      <c r="H172" t="n">
+      <c r="J172" t="n">
         <v>36</v>
-      </c>
-      <c r="I172" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J172" t="n">
-        <v>1.1</v>
       </c>
       <c r="K172" t="n">
         <v>2.4</v>
       </c>
       <c r="L172" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M172" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N172" t="n">
         <v>-54</v>
       </c>
-      <c r="M172" s="13" t="inlineStr">
+      <c r="O172" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="12" t="inlineStr">
+      <c r="A173" s="13" t="inlineStr">
         <is>
           <t>L戦国乙女４戦乱に閃く炯眼の軍師</t>
         </is>
@@ -9365,27 +10429,33 @@
         </is>
       </c>
       <c r="F173" t="n">
+        <v>285</v>
+      </c>
+      <c r="G173" t="n">
+        <v>309</v>
+      </c>
+      <c r="H173" t="n">
         <v>96</v>
       </c>
-      <c r="G173" t="n">
+      <c r="I173" t="n">
         <v>89</v>
       </c>
-      <c r="H173" t="n">
+      <c r="J173" t="n">
         <v>77</v>
       </c>
-      <c r="I173" t="n">
+      <c r="K173" t="n">
         <v>3.3</v>
       </c>
-      <c r="J173" t="n">
+      <c r="L173" t="n">
         <v>2.5</v>
       </c>
-      <c r="K173" t="n">
+      <c r="M173" t="n">
         <v>5</v>
       </c>
-      <c r="L173" t="n">
+      <c r="N173" t="n">
         <v>-24</v>
       </c>
-      <c r="M173" s="11" t="inlineStr">
+      <c r="O173" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9416,27 +10486,33 @@
         </is>
       </c>
       <c r="F174" t="n">
+        <v>158</v>
+      </c>
+      <c r="G174" t="n">
+        <v>169</v>
+      </c>
+      <c r="H174" t="n">
         <v>94</v>
       </c>
-      <c r="G174" t="n">
+      <c r="I174" t="n">
         <v>76</v>
       </c>
-      <c r="H174" t="n">
+      <c r="J174" t="n">
         <v>56</v>
-      </c>
-      <c r="I174" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J174" t="n">
-        <v>1.3</v>
       </c>
       <c r="K174" t="n">
         <v>3.6</v>
       </c>
       <c r="L174" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M174" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N174" t="n">
         <v>-64</v>
       </c>
-      <c r="M174" s="11" t="inlineStr">
+      <c r="O174" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9467,27 +10543,33 @@
         </is>
       </c>
       <c r="F175" t="n">
+        <v>129</v>
+      </c>
+      <c r="G175" t="n">
+        <v>105</v>
+      </c>
+      <c r="H175" t="n">
         <v>71</v>
       </c>
-      <c r="G175" t="n">
+      <c r="I175" t="n">
         <v>34</v>
       </c>
-      <c r="H175" t="n">
+      <c r="J175" t="n">
         <v>19</v>
-      </c>
-      <c r="I175" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J175" t="n">
-        <v>1.4</v>
       </c>
       <c r="K175" t="n">
         <v>4.1</v>
       </c>
       <c r="L175" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M175" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N175" t="n">
         <v>-66</v>
       </c>
-      <c r="M175" s="10" t="inlineStr">
+      <c r="O175" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -9518,27 +10600,33 @@
         </is>
       </c>
       <c r="F176" t="n">
+        <v>165</v>
+      </c>
+      <c r="G176" t="n">
+        <v>174</v>
+      </c>
+      <c r="H176" t="n">
         <v>93</v>
       </c>
-      <c r="G176" t="n">
+      <c r="I176" t="n">
         <v>69</v>
       </c>
-      <c r="H176" t="n">
+      <c r="J176" t="n">
         <v>46</v>
-      </c>
-      <c r="I176" t="n">
-        <v>2</v>
-      </c>
-      <c r="J176" t="n">
-        <v>1.1</v>
       </c>
       <c r="K176" t="n">
         <v>2</v>
       </c>
       <c r="L176" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M176" t="n">
+        <v>2</v>
+      </c>
+      <c r="N176" t="n">
         <v>-45</v>
       </c>
-      <c r="M176" s="11" t="inlineStr">
+      <c r="O176" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9569,27 +10657,33 @@
         </is>
       </c>
       <c r="F177" t="n">
+        <v>168</v>
+      </c>
+      <c r="G177" t="n">
+        <v>177</v>
+      </c>
+      <c r="H177" t="n">
         <v>93</v>
       </c>
-      <c r="G177" t="n">
+      <c r="I177" t="n">
         <v>66</v>
       </c>
-      <c r="H177" t="n">
+      <c r="J177" t="n">
         <v>39</v>
-      </c>
-      <c r="I177" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J177" t="n">
-        <v>1.1</v>
       </c>
       <c r="K177" t="n">
         <v>2.1</v>
       </c>
       <c r="L177" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M177" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N177" t="n">
         <v>-48</v>
       </c>
-      <c r="M177" s="11" t="inlineStr">
+      <c r="O177" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9620,27 +10714,33 @@
         </is>
       </c>
       <c r="F178" t="n">
+        <v>262</v>
+      </c>
+      <c r="G178" t="n">
+        <v>210</v>
+      </c>
+      <c r="H178" t="n">
         <v>77</v>
       </c>
-      <c r="G178" t="n">
+      <c r="I178" t="n">
         <v>52</v>
       </c>
-      <c r="H178" t="n">
+      <c r="J178" t="n">
         <v>23</v>
-      </c>
-      <c r="I178" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J178" t="n">
-        <v>1.3</v>
       </c>
       <c r="K178" t="n">
         <v>7.6</v>
       </c>
       <c r="L178" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M178" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="N178" t="n">
         <v>-83</v>
       </c>
-      <c r="M178" s="13" t="inlineStr">
+      <c r="O178" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -9671,27 +10771,33 @@
         </is>
       </c>
       <c r="F179" t="n">
+        <v>209</v>
+      </c>
+      <c r="G179" t="n">
+        <v>214</v>
+      </c>
+      <c r="H179" t="n">
         <v>88</v>
       </c>
-      <c r="G179" t="n">
+      <c r="I179" t="n">
         <v>67</v>
       </c>
-      <c r="H179" t="n">
+      <c r="J179" t="n">
         <v>56</v>
       </c>
-      <c r="I179" t="n">
+      <c r="K179" t="n">
         <v>4.1</v>
       </c>
-      <c r="J179" t="n">
+      <c r="L179" t="n">
         <v>3.5</v>
       </c>
-      <c r="K179" t="n">
+      <c r="M179" t="n">
         <v>8</v>
       </c>
-      <c r="L179" t="n">
+      <c r="N179" t="n">
         <v>-15</v>
       </c>
-      <c r="M179" s="11" t="inlineStr">
+      <c r="O179" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9722,27 +10828,33 @@
         </is>
       </c>
       <c r="F180" t="n">
+        <v>149</v>
+      </c>
+      <c r="G180" t="n">
+        <v>148</v>
+      </c>
+      <c r="H180" t="n">
         <v>88</v>
       </c>
-      <c r="G180" t="n">
+      <c r="I180" t="n">
         <v>70</v>
       </c>
-      <c r="H180" t="n">
+      <c r="J180" t="n">
         <v>41</v>
       </c>
-      <c r="I180" t="n">
+      <c r="K180" t="n">
         <v>4.3</v>
       </c>
-      <c r="J180" t="n">
+      <c r="L180" t="n">
         <v>1.3</v>
       </c>
-      <c r="K180" t="n">
+      <c r="M180" t="n">
         <v>4.4</v>
       </c>
-      <c r="L180" t="n">
+      <c r="N180" t="n">
         <v>-70</v>
       </c>
-      <c r="M180" s="11" t="inlineStr">
+      <c r="O180" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9773,27 +10885,33 @@
         </is>
       </c>
       <c r="F181" t="n">
+        <v>130</v>
+      </c>
+      <c r="G181" t="n">
+        <v>101</v>
+      </c>
+      <c r="H181" t="n">
         <v>69</v>
       </c>
-      <c r="G181" t="n">
+      <c r="I181" t="n">
         <v>46</v>
       </c>
-      <c r="H181" t="n">
+      <c r="J181" t="n">
         <v>23</v>
-      </c>
-      <c r="I181" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J181" t="n">
-        <v>1.3</v>
       </c>
       <c r="K181" t="n">
         <v>4.2</v>
       </c>
       <c r="L181" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M181" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N181" t="n">
         <v>-69</v>
       </c>
-      <c r="M181" s="10" t="inlineStr">
+      <c r="O181" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -9824,27 +10942,33 @@
         </is>
       </c>
       <c r="F182" t="n">
+        <v>194</v>
+      </c>
+      <c r="G182" t="n">
+        <v>183</v>
+      </c>
+      <c r="H182" t="n">
         <v>88</v>
       </c>
-      <c r="G182" t="n">
+      <c r="I182" t="n">
         <v>62</v>
       </c>
-      <c r="H182" t="n">
+      <c r="J182" t="n">
         <v>49</v>
-      </c>
-      <c r="I182" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J182" t="n">
-        <v>1.5</v>
       </c>
       <c r="K182" t="n">
         <v>5.1</v>
       </c>
       <c r="L182" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M182" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N182" t="n">
         <v>-71</v>
       </c>
-      <c r="M182" s="13" t="inlineStr">
+      <c r="O182" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -9875,27 +10999,33 @@
         </is>
       </c>
       <c r="F183" t="n">
+        <v>274</v>
+      </c>
+      <c r="G183" t="n">
+        <v>151</v>
+      </c>
+      <c r="H183" t="n">
         <v>87</v>
       </c>
-      <c r="G183" t="n">
+      <c r="I183" t="n">
         <v>72</v>
       </c>
-      <c r="H183" t="n">
+      <c r="J183" t="n">
         <v>62</v>
       </c>
-      <c r="I183" t="n">
+      <c r="K183" t="n">
         <v>4</v>
       </c>
-      <c r="J183" t="n">
+      <c r="L183" t="n">
         <v>1.3</v>
       </c>
-      <c r="K183" t="n">
+      <c r="M183" t="n">
         <v>4.1</v>
       </c>
-      <c r="L183" t="n">
+      <c r="N183" t="n">
         <v>-68</v>
       </c>
-      <c r="M183" s="11" t="inlineStr">
+      <c r="O183" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9926,34 +11056,40 @@
         </is>
       </c>
       <c r="F184" t="n">
+        <v>235</v>
+      </c>
+      <c r="G184" t="n">
+        <v>221</v>
+      </c>
+      <c r="H184" t="n">
         <v>94</v>
       </c>
-      <c r="G184" t="n">
+      <c r="I184" t="n">
         <v>65</v>
       </c>
-      <c r="H184" t="n">
+      <c r="J184" t="n">
         <v>52</v>
-      </c>
-      <c r="I184" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J184" t="n">
-        <v>1.6</v>
       </c>
       <c r="K184" t="n">
         <v>5.3</v>
       </c>
       <c r="L184" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M184" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N184" t="n">
         <v>-70</v>
       </c>
-      <c r="M184" s="13" t="inlineStr">
+      <c r="O184" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="12" t="inlineStr">
+      <c r="A185" s="13" t="inlineStr">
         <is>
           <t>Lスマスロ北斗の拳</t>
         </is>
@@ -9977,27 +11113,33 @@
         </is>
       </c>
       <c r="F185" t="n">
+        <v>283</v>
+      </c>
+      <c r="G185" t="n">
+        <v>321</v>
+      </c>
+      <c r="H185" t="n">
         <v>99</v>
       </c>
-      <c r="G185" t="n">
+      <c r="I185" t="n">
         <v>89</v>
       </c>
-      <c r="H185" t="n">
+      <c r="J185" t="n">
         <v>73</v>
       </c>
-      <c r="I185" t="n">
+      <c r="K185" t="n">
         <v>8.9</v>
       </c>
-      <c r="J185" t="n">
+      <c r="L185" t="n">
         <v>7.5</v>
       </c>
-      <c r="K185" t="n">
+      <c r="M185" t="n">
         <v>18.3</v>
       </c>
-      <c r="L185" t="n">
+      <c r="N185" t="n">
         <v>-16</v>
       </c>
-      <c r="M185" s="11" t="inlineStr">
+      <c r="O185" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10028,27 +11170,33 @@
         </is>
       </c>
       <c r="F186" t="n">
+        <v>117</v>
+      </c>
+      <c r="G186" t="n">
+        <v>107</v>
+      </c>
+      <c r="H186" t="n">
         <v>103</v>
       </c>
-      <c r="G186" t="n">
+      <c r="I186" t="n">
         <v>78</v>
       </c>
-      <c r="H186" t="n">
+      <c r="J186" t="n">
         <v>60</v>
       </c>
-      <c r="I186" t="n">
+      <c r="K186" t="n">
         <v>7.1</v>
       </c>
-      <c r="J186" t="n">
+      <c r="L186" t="n">
         <v>1.4</v>
       </c>
-      <c r="K186" t="n">
+      <c r="M186" t="n">
         <v>10.6</v>
       </c>
-      <c r="L186" t="n">
+      <c r="N186" t="n">
         <v>-80</v>
       </c>
-      <c r="M186" s="11" t="inlineStr">
+      <c r="O186" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10079,27 +11227,33 @@
         </is>
       </c>
       <c r="F187" t="n">
+        <v>21</v>
+      </c>
+      <c r="G187" t="n">
+        <v>21</v>
+      </c>
+      <c r="H187" t="n">
         <v>110</v>
       </c>
-      <c r="G187" t="n">
+      <c r="I187" t="n">
         <v>80</v>
       </c>
-      <c r="H187" t="n">
+      <c r="J187" t="n">
         <v>55</v>
-      </c>
-      <c r="I187" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J187" t="n">
-        <v>1.6</v>
       </c>
       <c r="K187" t="n">
         <v>4.1</v>
       </c>
       <c r="L187" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M187" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N187" t="n">
         <v>-61</v>
       </c>
-      <c r="M187" s="11" t="inlineStr">
+      <c r="O187" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10130,27 +11284,33 @@
         </is>
       </c>
       <c r="F188" t="n">
+        <v>73</v>
+      </c>
+      <c r="G188" t="n">
+        <v>68</v>
+      </c>
+      <c r="H188" t="n">
         <v>105</v>
       </c>
-      <c r="G188" t="n">
+      <c r="I188" t="n">
         <v>63</v>
       </c>
-      <c r="H188" t="n">
+      <c r="J188" t="n">
         <v>51</v>
       </c>
-      <c r="I188" t="n">
+      <c r="K188" t="n">
         <v>5.7</v>
       </c>
-      <c r="J188" t="n">
+      <c r="L188" t="n">
         <v>1.3</v>
       </c>
-      <c r="K188" t="n">
+      <c r="M188" t="n">
         <v>5.8</v>
       </c>
-      <c r="L188" t="n">
+      <c r="N188" t="n">
         <v>-77</v>
       </c>
-      <c r="M188" s="13" t="inlineStr">
+      <c r="O188" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -10181,27 +11341,33 @@
         </is>
       </c>
       <c r="F189" t="n">
+        <v>100</v>
+      </c>
+      <c r="G189" t="n">
+        <v>100</v>
+      </c>
+      <c r="H189" t="n">
         <v>113</v>
       </c>
-      <c r="G189" t="n">
+      <c r="I189" t="n">
         <v>82</v>
       </c>
-      <c r="H189" t="n">
+      <c r="J189" t="n">
         <v>72</v>
       </c>
-      <c r="I189" t="n">
+      <c r="K189" t="n">
         <v>6.4</v>
       </c>
-      <c r="J189" t="n">
+      <c r="L189" t="n">
         <v>3.7</v>
       </c>
-      <c r="K189" t="n">
+      <c r="M189" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="L189" t="n">
+      <c r="N189" t="n">
         <v>-42</v>
       </c>
-      <c r="M189" s="11" t="inlineStr">
+      <c r="O189" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10209,7 +11375,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ai収集/分析_新台診断_v0.3.xlsx
+++ b/ai収集/分析_新台診断_v0.3.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,13 +49,17 @@
       <sz val="11"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00333333"/>
-      <sz val="12"/>
+      <color rgb="00D03030"/>
+      <sz val="11"/>
     </font>
     <font>
       <color rgb="00C77B00"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
     </font>
     <font>
       <color rgb="00888888"/>
@@ -69,8 +73,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B00000"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +97,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00ECECEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E3F5E9"/>
       </patternFill>
     </fill>
@@ -100,6 +113,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8C9C9"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -141,14 +159,19 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -514,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="115" customWidth="1" min="1" max="1"/>
@@ -590,55 +613,83 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>● 初月実態 = 初月持続率による生死判定（健全≥66 / 微妙50-66 / 実質死亡&lt;50 / 計測中）。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>【判定ロジック】</t>
+          <t xml:space="preserve">   ⚠重要: 稼働貢献週(設置週数) ≠ 稼働の生死。ホールは筐体代が沈むので死に台でも撤去せず数十週設置する。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・4週が揃う → 初月持続率で確定: 優秀≥66% / 注意≥50% / 危険&lt;50%</t>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   実例: 真・北斗無双=100週設置でも初月持続率47%(実質死に台) / 劇場版まどか=50週設置/22%。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">   → 設置週数が長くても『実質死亡』なら良台ではない。良し悪しは設置週数でなく持続率×稼働値で見る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>【判定ロジック】</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・4週が揃う → 初月持続率で確定: 優秀≥66% / 注意≥50% / 危険&lt;50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  ・4週未到達(新台) → 2週で暫定: 稼働値≥260%かつ持続率≥83%=優秀 / 稼働値&lt;190%または持続率&lt;73%=危険 / 中間=注意</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  ・2週も未到達 → 計測中</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  ・⚠供給過剰 = 大量導入(台数ピーク≥6)なのに判定が注意/危険（戦国乙女型。台数で初動は出るが客が薄まる）</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>【非採用】割数(判別力0.34)・台数初動(0.7)は寿命をほぼ分けず材料にしない。機械割(設定6)は規則で全台115%未満に張付き＝比較情報ゼロ。</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>【データ源】SIS週次(sis_weekly_data)。生成: scripts/misc/build_diagnosis_table.py。週次更新に追従。</t>
         </is>
@@ -655,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O189"/>
+  <dimension ref="A1:P189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -663,97 +714,103 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>※直近導入順。判定/しきい値の意味は『説明』シート参照。稼働値=アウト÷週中央値、持続率=◯週÷初週。</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>機種</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>初週</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>継続表示</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>稼働貢献週</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>状況</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>初月実態</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>初週稼働値</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>2週稼働値</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="I2" s="11" t="inlineStr">
         <is>
           <t>2週持続率</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>初月持続率(4週)</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="K2" s="11" t="inlineStr">
         <is>
           <t>8週持続率</t>
         </is>
       </c>
-      <c r="K2" s="10" t="inlineStr">
+      <c r="L2" s="11" t="inlineStr">
         <is>
           <t>台数初週</t>
         </is>
       </c>
-      <c r="L2" s="10" t="inlineStr">
+      <c r="M2" s="11" t="inlineStr">
         <is>
           <t>台数現在</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr">
+      <c r="N2" s="11" t="inlineStr">
         <is>
           <t>台数ピーク</t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr">
+      <c r="O2" s="11" t="inlineStr">
         <is>
           <t>台数推移%</t>
         </is>
       </c>
-      <c r="O2" s="10" t="inlineStr">
+      <c r="P2" s="11" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
@@ -783,17 +840,19 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>計測中</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>289</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>205</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>72</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>2</v>
@@ -802,9 +861,12 @@
         <v>2</v>
       </c>
       <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t>危険(暫定)</t>
         </is>
@@ -834,17 +896,19 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>計測中</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>484</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>452</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>94</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>4</v>
@@ -853,16 +917,19 @@
         <v>4</v>
       </c>
       <c r="N4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" s="12" t="inlineStr">
+      <c r="P4" s="14" t="inlineStr">
         <is>
           <t>優秀(暫定)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>L戦国乙女5業火を穿つ宿焔の双刃</t>
         </is>
@@ -885,28 +952,33 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>計測中</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>500</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>461</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>93</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>6.5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6.7</v>
       </c>
       <c r="M5" t="n">
         <v>6.7</v>
       </c>
       <c r="N5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O5" t="n">
         <v>3</v>
       </c>
-      <c r="O5" s="12" t="inlineStr">
+      <c r="P5" s="14" t="inlineStr">
         <is>
           <t>優秀(暫定)</t>
         </is>
@@ -936,20 +1008,22 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>302</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>230</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>78</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>53</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.2</v>
@@ -958,9 +1032,12 @@
         <v>1.2</v>
       </c>
       <c r="N6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="14" t="inlineStr">
+      <c r="P6" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -990,31 +1067,36 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>398</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>332</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>83</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>65</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3.1</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>3.1</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>-3</v>
       </c>
-      <c r="O7" s="14" t="inlineStr">
+      <c r="P7" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1044,20 +1126,22 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>388</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>323</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>83</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>66</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.7</v>
       </c>
       <c r="L8" t="n">
         <v>1.7</v>
@@ -1066,9 +1150,12 @@
         <v>1.7</v>
       </c>
       <c r="N8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="12" t="inlineStr">
+      <c r="P8" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1098,31 +1185,36 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>380</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>298</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>78</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>53</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>4.7</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>4.3</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>4.7</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>-9</v>
       </c>
-      <c r="O9" s="14" t="inlineStr">
+      <c r="P9" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1152,31 +1244,36 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>352</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>285</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>80</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>56</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4.1</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>3.9</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4.2</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>-5</v>
       </c>
-      <c r="O10" s="14" t="inlineStr">
+      <c r="P10" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1206,34 +1303,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>278</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>237</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>101</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>71</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>56</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>1.4</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>1.3</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>1.4</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>-7</v>
       </c>
-      <c r="O11" s="12" t="inlineStr">
+      <c r="P11" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1263,34 +1365,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>457</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>371</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>96</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>69</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>53</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>8.4</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>8.5</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>8.6</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="O12" s="12" t="inlineStr">
+      <c r="P12" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1320,34 +1427,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
         <v>318</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>206</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>76</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>33</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>18</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>3.3</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>2.2</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>3.3</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>-33</v>
       </c>
-      <c r="O13" s="11" t="inlineStr">
+      <c r="P13" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -1377,23 +1489,25 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
         <v>343</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>296</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>85</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>75</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>52</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.5</v>
@@ -1402,9 +1516,12 @@
         <v>1.5</v>
       </c>
       <c r="N14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="12" t="inlineStr">
+      <c r="P14" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1434,34 +1551,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
         <v>357</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>289</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>80</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>60</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>33</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>1.7</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>1.4</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>1.7</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>-18</v>
       </c>
-      <c r="O15" s="14" t="inlineStr">
+      <c r="P15" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1491,34 +1613,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
         <v>378</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>299</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>78</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>56</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>27</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>2.4</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>1.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>2.4</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>-21</v>
       </c>
-      <c r="O16" s="14" t="inlineStr">
+      <c r="P16" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1548,23 +1675,25 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
         <v>403</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>380</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>93</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>80</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>66</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.7</v>
       </c>
       <c r="L17" t="n">
         <v>3.7</v>
@@ -1573,9 +1702,12 @@
         <v>3.7</v>
       </c>
       <c r="N17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="12" t="inlineStr">
+      <c r="P17" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1605,34 +1737,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
         <v>406</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>366</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>89</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>76</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>48</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>1.6</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>1.5</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>1.6</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>-6</v>
       </c>
-      <c r="O18" s="12" t="inlineStr">
+      <c r="P18" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1662,34 +1799,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
         <v>315</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>278</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>81</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>67</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>63</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>2.1</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>2</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>2.1</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>-5</v>
       </c>
-      <c r="O19" s="12" t="inlineStr">
+      <c r="P19" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1719,34 +1861,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
         <v>462</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>479</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>95</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>84</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>66</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="L20" t="n">
-        <v>9.9</v>
       </c>
       <c r="M20" t="n">
         <v>9.9</v>
       </c>
       <c r="N20" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="O20" t="n">
         <v>12</v>
       </c>
-      <c r="O20" s="12" t="inlineStr">
+      <c r="P20" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1776,34 +1923,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
         <v>441</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>436</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>101</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>97</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>79</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>1.4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.6</v>
       </c>
       <c r="M21" t="n">
         <v>1.6</v>
       </c>
       <c r="N21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O21" t="n">
         <v>14</v>
       </c>
-      <c r="O21" s="12" t="inlineStr">
+      <c r="P21" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1833,34 +1985,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
         <v>345</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>269</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>80</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>53</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>25</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>3.6</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>1.4</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>3.6</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>-61</v>
       </c>
-      <c r="O22" s="14" t="inlineStr">
+      <c r="P22" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1890,34 +2047,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
         <v>354</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>296</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>86</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>71</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>52</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>3</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>2.9</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>3.1</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>-3</v>
       </c>
-      <c r="O23" s="12" t="inlineStr">
+      <c r="P23" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1947,23 +2109,25 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
         <v>416</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>376</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>93</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>83</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>60</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.7</v>
       </c>
       <c r="L24" t="n">
         <v>2.7</v>
@@ -1972,9 +2136,12 @@
         <v>2.7</v>
       </c>
       <c r="N24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="12" t="inlineStr">
+      <c r="P24" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2004,34 +2171,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
         <v>432</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>394</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>93</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>84</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>59</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>4.2</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>4.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>4.2</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>-2</v>
       </c>
-      <c r="O25" s="12" t="inlineStr">
+      <c r="P25" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2061,34 +2233,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
         <v>350</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>289</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>85</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>63</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>35</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>2.2</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>1.2</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>2.2</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>-45</v>
       </c>
-      <c r="O26" s="14" t="inlineStr">
+      <c r="P26" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -2118,34 +2295,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
         <v>387</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>347</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>86</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>68</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>51</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>4.9</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>2.7</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>4.9</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>-45</v>
       </c>
-      <c r="O27" s="12" t="inlineStr">
+      <c r="P27" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2175,34 +2357,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
         <v>283</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>225</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>77</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>69</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>63</v>
-      </c>
-      <c r="K28" t="n">
-        <v>5.8</v>
       </c>
       <c r="L28" t="n">
         <v>5.8</v>
       </c>
       <c r="M28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N28" t="n">
         <v>5.9</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="12" t="inlineStr">
+      <c r="P28" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2232,34 +2419,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
         <v>421</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>390</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>89</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>71</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>62</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>10.9</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>10.5</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>11.8</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>-4</v>
       </c>
-      <c r="O29" s="12" t="inlineStr">
+      <c r="P29" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2289,34 +2481,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
         <v>375</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>268</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>89</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>71</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>53</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1.5</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>1.4</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>1.5</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>-7</v>
       </c>
-      <c r="O30" s="12" t="inlineStr">
+      <c r="P30" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2346,34 +2543,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
         <v>235</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>193</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>102</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>72</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>62</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>10.7</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>6.3</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>10.8</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>-41</v>
       </c>
-      <c r="O31" s="12" t="inlineStr">
+      <c r="P31" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2403,34 +2605,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
         <v>421</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>304</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>90</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>61</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>45</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>2</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>1.6</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2.2</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>-20</v>
       </c>
-      <c r="O32" s="14" t="inlineStr">
+      <c r="P32" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -2460,34 +2667,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
         <v>366</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>261</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>88</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>54</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>38</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>3.5</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>1.7</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3.5</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>-51</v>
       </c>
-      <c r="O33" s="14" t="inlineStr">
+      <c r="P33" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -2517,34 +2729,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
         <v>400</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>331</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>87</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>68</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>39</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>1.6</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>1.6</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>-38</v>
       </c>
-      <c r="O34" s="12" t="inlineStr">
+      <c r="P34" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2574,34 +2791,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
         <v>390</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>322</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>87</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>77</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>50</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>1.5</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>2</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>-25</v>
       </c>
-      <c r="O35" s="12" t="inlineStr">
+      <c r="P35" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2631,34 +2853,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
         <v>506</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>453</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>94</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>85</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>57</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3.7</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>3.4</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>4</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>-8</v>
       </c>
-      <c r="O36" s="12" t="inlineStr">
+      <c r="P36" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2688,34 +2915,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
         <v>310</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>291</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>99</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>73</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>46</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>1.4</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>1.1</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>1.4</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>-21</v>
       </c>
-      <c r="O37" s="12" t="inlineStr">
+      <c r="P37" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2745,34 +2977,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
         <v>426</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>315</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>86</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>59</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>41</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>2</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>1.3</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>2</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>-35</v>
       </c>
-      <c r="O38" s="14" t="inlineStr">
+      <c r="P38" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -2802,34 +3039,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
         <v>463</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>399</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>84</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>69</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>56</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>6.2</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>9.5</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>-33</v>
       </c>
-      <c r="O39" s="12" t="inlineStr">
+      <c r="P39" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2859,34 +3101,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
         <v>445</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>400</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>88</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>77</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>54</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>2.4</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>1.4</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>2.4</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>-42</v>
       </c>
-      <c r="O40" s="12" t="inlineStr">
+      <c r="P40" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2916,34 +3163,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
         <v>344</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>267</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>76</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>54</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>35</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1.8</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>1.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>1.8</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>-39</v>
       </c>
-      <c r="O41" s="14" t="inlineStr">
+      <c r="P41" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -2973,34 +3225,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
         <v>390</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>339</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>89</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>72</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>63</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>1.5</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>1.4</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>1.5</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>-7</v>
       </c>
-      <c r="O42" s="12" t="inlineStr">
+      <c r="P42" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3030,31 +3287,36 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
         <v>334</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>228</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>70</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>40</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>1.9</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>1.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>1.9</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>-11</v>
       </c>
-      <c r="O43" s="11" t="inlineStr">
+      <c r="P43" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -3084,34 +3346,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
         <v>410</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>365</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>91</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>69</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>49</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>3.7</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>1.7</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>3.7</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>-54</v>
       </c>
-      <c r="O44" s="12" t="inlineStr">
+      <c r="P44" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3141,34 +3408,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
         <v>455</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>397</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>89</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>71</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>52</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>6.1</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>2.9</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>6.1</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>-52</v>
       </c>
-      <c r="O45" s="12" t="inlineStr">
+      <c r="P45" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3190,7 +3462,7 @@
           <t>21週で終了</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="17" t="n">
         <v>21</v>
       </c>
       <c r="E46" t="inlineStr">
@@ -3198,34 +3470,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
         <v>224</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>143</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>65</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>34</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>18</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>1.6</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>1.1</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>1.6</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>-31</v>
       </c>
-      <c r="O46" s="11" t="inlineStr">
+      <c r="P46" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -3255,34 +3532,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
         <v>360</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>314</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>79</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>55</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>36</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>1.6</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>1.1</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>1.6</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>-31</v>
       </c>
-      <c r="O47" s="14" t="inlineStr">
+      <c r="P47" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3312,34 +3594,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
         <v>466</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>414</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>89</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>72</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>54</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>1.9</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>1.6</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>1.9</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>-16</v>
       </c>
-      <c r="O48" s="12" t="inlineStr">
+      <c r="P48" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3369,34 +3656,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
         <v>317</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>251</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>79</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>58</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>40</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>1.5</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>1.1</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>1.5</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>-27</v>
       </c>
-      <c r="O49" s="14" t="inlineStr">
+      <c r="P49" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3426,34 +3718,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
         <v>488</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>427</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>88</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>70</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>48</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>7.2</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>2.6</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>7.2</v>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>-64</v>
       </c>
-      <c r="O50" s="12" t="inlineStr">
+      <c r="P50" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3483,34 +3780,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
         <v>368</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>267</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>95</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>64</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>43</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>2.1</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>1.1</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>2.1</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>-48</v>
       </c>
-      <c r="O51" s="14" t="inlineStr">
+      <c r="P51" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3540,34 +3842,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F52" t="n">
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
         <v>249</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>180</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>94</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>59</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>42</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>1.9</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>1.2</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>1.9</v>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>-37</v>
       </c>
-      <c r="O52" s="14" t="inlineStr">
+      <c r="P52" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3597,34 +3904,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F53" t="n">
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
         <v>409</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>325</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>104</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>86</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>75</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>2.2</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>2</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>2.5</v>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>-9</v>
       </c>
-      <c r="O53" s="12" t="inlineStr">
+      <c r="P53" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3654,34 +3966,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F54" t="n">
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
         <v>360</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>252</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>92</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>60</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>41</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>3.8</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>1.3</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>3.8</v>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>-66</v>
       </c>
-      <c r="O54" s="14" t="inlineStr">
+      <c r="P54" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3711,34 +4028,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F55" t="n">
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
         <v>381</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>266</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>91</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>60</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>40</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>2.2</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>1.1</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>2.2</v>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>-50</v>
       </c>
-      <c r="O55" s="14" t="inlineStr">
+      <c r="P55" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3768,34 +4090,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
         <v>311</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>322</v>
-      </c>
-      <c r="H56" t="n">
-        <v>92</v>
       </c>
       <c r="I56" t="n">
         <v>92</v>
       </c>
       <c r="J56" t="n">
+        <v>92</v>
+      </c>
+      <c r="K56" t="n">
         <v>72</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>1.9</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>1.7</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>1.9</v>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>-11</v>
       </c>
-      <c r="O56" s="12" t="inlineStr">
+      <c r="P56" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3825,34 +4152,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F57" t="n">
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
         <v>292</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>285</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>87</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>82</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>57</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>3.2</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>1.6</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>3.3</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>-50</v>
       </c>
-      <c r="O57" s="12" t="inlineStr">
+      <c r="P57" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3882,34 +4214,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
         <v>254</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>241</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>84</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>76</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>48</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>2</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>1.1</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>2</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>-45</v>
       </c>
-      <c r="O58" s="12" t="inlineStr">
+      <c r="P58" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3939,34 +4276,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
         <v>105</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>100</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>85</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>100</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>72</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>4.9</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>1.5</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>4.9</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>-69</v>
       </c>
-      <c r="O59" s="12" t="inlineStr">
+      <c r="P59" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3988,7 +4330,7 @@
           <t>32週で終了</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="17" t="n">
         <v>32</v>
       </c>
       <c r="E60" t="inlineStr">
@@ -3996,34 +4338,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F60" t="n">
+      <c r="F60" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
         <v>314</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>228</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>72</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>35</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>19</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>1.5</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>1</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>1.5</v>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>-33</v>
       </c>
-      <c r="O60" s="11" t="inlineStr">
+      <c r="P60" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4053,34 +4400,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
         <v>303</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>219</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>73</v>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
         <v>54</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>28</v>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" t="n">
         <v>2.2</v>
       </c>
-      <c r="L61" t="n">
+      <c r="M61" t="n">
         <v>1.2</v>
       </c>
-      <c r="M61" t="n">
+      <c r="N61" t="n">
         <v>2.2</v>
       </c>
-      <c r="N61" t="n">
+      <c r="O61" t="n">
         <v>-45</v>
       </c>
-      <c r="O61" s="14" t="inlineStr">
+      <c r="P61" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4110,34 +4462,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
         <v>346</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>303</v>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>89</v>
       </c>
-      <c r="I62" t="n">
+      <c r="J62" t="n">
         <v>71</v>
       </c>
-      <c r="J62" t="n">
+      <c r="K62" t="n">
         <v>43</v>
       </c>
-      <c r="K62" t="n">
+      <c r="L62" t="n">
         <v>2</v>
       </c>
-      <c r="L62" t="n">
+      <c r="M62" t="n">
         <v>1.1</v>
       </c>
-      <c r="M62" t="n">
+      <c r="N62" t="n">
         <v>2</v>
       </c>
-      <c r="N62" t="n">
+      <c r="O62" t="n">
         <v>-45</v>
       </c>
-      <c r="O62" s="12" t="inlineStr">
+      <c r="P62" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -4167,34 +4524,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F63" t="n">
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
         <v>469</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>446</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>97</v>
       </c>
-      <c r="I63" t="n">
+      <c r="J63" t="n">
         <v>87</v>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" t="n">
         <v>63</v>
       </c>
-      <c r="K63" t="n">
+      <c r="L63" t="n">
         <v>3.3</v>
       </c>
-      <c r="L63" t="n">
+      <c r="M63" t="n">
         <v>2.6</v>
       </c>
-      <c r="M63" t="n">
+      <c r="N63" t="n">
         <v>4.6</v>
       </c>
-      <c r="N63" t="n">
+      <c r="O63" t="n">
         <v>-21</v>
       </c>
-      <c r="O63" s="12" t="inlineStr">
+      <c r="P63" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -4216,7 +4578,7 @@
           <t>53週継続中</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="17" t="n">
         <v>53</v>
       </c>
       <c r="E64" t="inlineStr">
@@ -4224,34 +4586,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F64" t="n">
+      <c r="F64" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
         <v>394</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>294</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>76</v>
       </c>
-      <c r="I64" t="n">
+      <c r="J64" t="n">
         <v>48</v>
       </c>
-      <c r="J64" t="n">
+      <c r="K64" t="n">
         <v>24</v>
       </c>
-      <c r="K64" t="n">
+      <c r="L64" t="n">
         <v>2.4</v>
       </c>
-      <c r="L64" t="n">
+      <c r="M64" t="n">
         <v>1.2</v>
       </c>
-      <c r="M64" t="n">
+      <c r="N64" t="n">
         <v>2.4</v>
       </c>
-      <c r="N64" t="n">
+      <c r="O64" t="n">
         <v>-50</v>
       </c>
-      <c r="O64" s="11" t="inlineStr">
+      <c r="P64" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4281,34 +4648,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F65" t="n">
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
         <v>402</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>321</v>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>81</v>
       </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
         <v>57</v>
       </c>
-      <c r="J65" t="n">
+      <c r="K65" t="n">
         <v>37</v>
       </c>
-      <c r="K65" t="n">
+      <c r="L65" t="n">
         <v>3.3</v>
       </c>
-      <c r="L65" t="n">
+      <c r="M65" t="n">
         <v>1.3</v>
       </c>
-      <c r="M65" t="n">
+      <c r="N65" t="n">
         <v>3.3</v>
       </c>
-      <c r="N65" t="n">
+      <c r="O65" t="n">
         <v>-61</v>
       </c>
-      <c r="O65" s="14" t="inlineStr">
+      <c r="P65" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4338,34 +4710,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F66" t="n">
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
         <v>321</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>245</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>77</v>
       </c>
-      <c r="I66" t="n">
+      <c r="J66" t="n">
         <v>59</v>
       </c>
-      <c r="J66" t="n">
+      <c r="K66" t="n">
         <v>29</v>
       </c>
-      <c r="K66" t="n">
+      <c r="L66" t="n">
         <v>1.2</v>
       </c>
-      <c r="L66" t="n">
+      <c r="M66" t="n">
         <v>1.1</v>
       </c>
-      <c r="M66" t="n">
+      <c r="N66" t="n">
         <v>1.2</v>
       </c>
-      <c r="N66" t="n">
+      <c r="O66" t="n">
         <v>-8</v>
       </c>
-      <c r="O66" s="14" t="inlineStr">
+      <c r="P66" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4395,34 +4772,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F67" t="n">
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
         <v>306</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>217</v>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>72</v>
       </c>
-      <c r="I67" t="n">
+      <c r="J67" t="n">
         <v>50</v>
       </c>
-      <c r="J67" t="n">
+      <c r="K67" t="n">
         <v>33</v>
       </c>
-      <c r="K67" t="n">
+      <c r="L67" t="n">
         <v>1.3</v>
       </c>
-      <c r="L67" t="n">
+      <c r="M67" t="n">
         <v>1.1</v>
       </c>
-      <c r="M67" t="n">
+      <c r="N67" t="n">
         <v>1.3</v>
       </c>
-      <c r="N67" t="n">
+      <c r="O67" t="n">
         <v>-15</v>
       </c>
-      <c r="O67" s="14" t="inlineStr">
+      <c r="P67" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4444,7 +4826,7 @@
           <t>21週で終了</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="17" t="n">
         <v>21</v>
       </c>
       <c r="E68" t="inlineStr">
@@ -4452,34 +4834,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F68" t="n">
+      <c r="F68" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
         <v>241</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>157</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>66</v>
       </c>
-      <c r="I68" t="n">
+      <c r="J68" t="n">
         <v>40</v>
       </c>
-      <c r="J68" t="n">
+      <c r="K68" t="n">
         <v>23</v>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" t="n">
         <v>1.4</v>
       </c>
-      <c r="L68" t="n">
+      <c r="M68" t="n">
         <v>1.1</v>
       </c>
-      <c r="M68" t="n">
+      <c r="N68" t="n">
         <v>1.4</v>
       </c>
-      <c r="N68" t="n">
+      <c r="O68" t="n">
         <v>-21</v>
       </c>
-      <c r="O68" s="11" t="inlineStr">
+      <c r="P68" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4509,34 +4896,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
         <v>422</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>365</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>84</v>
       </c>
-      <c r="I69" t="n">
+      <c r="J69" t="n">
         <v>60</v>
       </c>
-      <c r="J69" t="n">
+      <c r="K69" t="n">
         <v>61</v>
       </c>
-      <c r="K69" t="n">
+      <c r="L69" t="n">
         <v>3.4</v>
       </c>
-      <c r="L69" t="n">
+      <c r="M69" t="n">
         <v>2</v>
       </c>
-      <c r="M69" t="n">
+      <c r="N69" t="n">
         <v>3.4</v>
       </c>
-      <c r="N69" t="n">
+      <c r="O69" t="n">
         <v>-41</v>
       </c>
-      <c r="O69" s="14" t="inlineStr">
+      <c r="P69" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4566,34 +4958,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F70" t="n">
+      <c r="F70" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
         <v>351</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>244</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>67</v>
       </c>
-      <c r="I70" t="n">
+      <c r="J70" t="n">
         <v>37</v>
       </c>
-      <c r="J70" t="n">
+      <c r="K70" t="n">
         <v>31</v>
       </c>
-      <c r="K70" t="n">
+      <c r="L70" t="n">
         <v>11.3</v>
       </c>
-      <c r="L70" t="n">
+      <c r="M70" t="n">
         <v>3.3</v>
       </c>
-      <c r="M70" t="n">
+      <c r="N70" t="n">
         <v>11.3</v>
       </c>
-      <c r="N70" t="n">
+      <c r="O70" t="n">
         <v>-71</v>
       </c>
-      <c r="O70" s="11" t="inlineStr">
+      <c r="P70" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4615,7 +5012,7 @@
           <t>46週で終了</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="17" t="n">
         <v>46</v>
       </c>
       <c r="E71" t="inlineStr">
@@ -4623,34 +5020,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F71" t="n">
+      <c r="F71" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
         <v>353</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>339</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I71" t="n">
         <v>72</v>
       </c>
-      <c r="I71" t="n">
+      <c r="J71" t="n">
         <v>48</v>
       </c>
-      <c r="J71" t="n">
+      <c r="K71" t="n">
         <v>24</v>
       </c>
-      <c r="K71" t="n">
+      <c r="L71" t="n">
         <v>2</v>
       </c>
-      <c r="L71" t="n">
+      <c r="M71" t="n">
         <v>1.1</v>
       </c>
-      <c r="M71" t="n">
+      <c r="N71" t="n">
         <v>2</v>
       </c>
-      <c r="N71" t="n">
+      <c r="O71" t="n">
         <v>-45</v>
       </c>
-      <c r="O71" s="11" t="inlineStr">
+      <c r="P71" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4672,7 +5074,7 @@
           <t>53週で終了</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="17" t="n">
         <v>53</v>
       </c>
       <c r="E72" t="inlineStr">
@@ -4680,34 +5082,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
         <v>313</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>292</v>
       </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
         <v>70</v>
       </c>
-      <c r="I72" t="n">
+      <c r="J72" t="n">
         <v>45</v>
       </c>
-      <c r="J72" t="n">
+      <c r="K72" t="n">
         <v>29</v>
       </c>
-      <c r="K72" t="n">
+      <c r="L72" t="n">
         <v>5.2</v>
       </c>
-      <c r="L72" t="n">
+      <c r="M72" t="n">
         <v>1.2</v>
       </c>
-      <c r="M72" t="n">
+      <c r="N72" t="n">
         <v>5.2</v>
       </c>
-      <c r="N72" t="n">
+      <c r="O72" t="n">
         <v>-77</v>
       </c>
-      <c r="O72" s="11" t="inlineStr">
+      <c r="P72" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4737,34 +5144,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F73" t="n">
+      <c r="F73" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
         <v>362</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>384</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I73" t="n">
         <v>80</v>
       </c>
-      <c r="I73" t="n">
+      <c r="J73" t="n">
         <v>57</v>
       </c>
-      <c r="J73" t="n">
+      <c r="K73" t="n">
         <v>35</v>
       </c>
-      <c r="K73" t="n">
+      <c r="L73" t="n">
         <v>3.8</v>
       </c>
-      <c r="L73" t="n">
+      <c r="M73" t="n">
         <v>1.1</v>
       </c>
-      <c r="M73" t="n">
+      <c r="N73" t="n">
         <v>3.8</v>
       </c>
-      <c r="N73" t="n">
+      <c r="O73" t="n">
         <v>-71</v>
       </c>
-      <c r="O73" s="14" t="inlineStr">
+      <c r="P73" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4794,34 +5206,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F74" t="n">
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
         <v>412</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>338</v>
       </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
         <v>95</v>
       </c>
-      <c r="I74" t="n">
+      <c r="J74" t="n">
         <v>53</v>
       </c>
-      <c r="J74" t="n">
+      <c r="K74" t="n">
         <v>35</v>
       </c>
-      <c r="K74" t="n">
+      <c r="L74" t="n">
         <v>3</v>
       </c>
-      <c r="L74" t="n">
+      <c r="M74" t="n">
         <v>1.1</v>
       </c>
-      <c r="M74" t="n">
+      <c r="N74" t="n">
         <v>3</v>
       </c>
-      <c r="N74" t="n">
+      <c r="O74" t="n">
         <v>-63</v>
       </c>
-      <c r="O74" s="14" t="inlineStr">
+      <c r="P74" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4851,34 +5268,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
         <v>442</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>384</v>
       </c>
-      <c r="H75" t="n">
+      <c r="I75" t="n">
         <v>101</v>
       </c>
-      <c r="I75" t="n">
+      <c r="J75" t="n">
         <v>77</v>
       </c>
-      <c r="J75" t="n">
+      <c r="K75" t="n">
         <v>66</v>
       </c>
-      <c r="K75" t="n">
+      <c r="L75" t="n">
         <v>4</v>
       </c>
-      <c r="L75" t="n">
+      <c r="M75" t="n">
         <v>2.2</v>
       </c>
-      <c r="M75" t="n">
+      <c r="N75" t="n">
         <v>4.4</v>
       </c>
-      <c r="N75" t="n">
+      <c r="O75" t="n">
         <v>-45</v>
       </c>
-      <c r="O75" s="12" t="inlineStr">
+      <c r="P75" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -4900,7 +5322,7 @@
           <t>36週で終了</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="17" t="n">
         <v>36</v>
       </c>
       <c r="E76" t="inlineStr">
@@ -4908,34 +5330,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F76" t="n">
+      <c r="F76" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
         <v>317</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>218</v>
       </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
         <v>80</v>
       </c>
-      <c r="I76" t="n">
+      <c r="J76" t="n">
         <v>35</v>
       </c>
-      <c r="J76" t="n">
+      <c r="K76" t="n">
         <v>20</v>
       </c>
-      <c r="K76" t="n">
+      <c r="L76" t="n">
         <v>2.7</v>
       </c>
-      <c r="L76" t="n">
+      <c r="M76" t="n">
         <v>1.1</v>
       </c>
-      <c r="M76" t="n">
+      <c r="N76" t="n">
         <v>2.7</v>
       </c>
-      <c r="N76" t="n">
+      <c r="O76" t="n">
         <v>-59</v>
       </c>
-      <c r="O76" s="11" t="inlineStr">
+      <c r="P76" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4965,34 +5392,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F77" t="n">
+      <c r="F77" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
         <v>376</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>324</v>
       </c>
-      <c r="H77" t="n">
+      <c r="I77" t="n">
         <v>86</v>
       </c>
-      <c r="I77" t="n">
+      <c r="J77" t="n">
         <v>66</v>
       </c>
-      <c r="J77" t="n">
+      <c r="K77" t="n">
         <v>38</v>
       </c>
-      <c r="K77" t="n">
+      <c r="L77" t="n">
         <v>2.3</v>
       </c>
-      <c r="L77" t="n">
+      <c r="M77" t="n">
         <v>1.2</v>
       </c>
-      <c r="M77" t="n">
+      <c r="N77" t="n">
         <v>2.4</v>
       </c>
-      <c r="N77" t="n">
+      <c r="O77" t="n">
         <v>-48</v>
       </c>
-      <c r="O77" s="12" t="inlineStr">
+      <c r="P77" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5022,34 +5454,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F78" t="n">
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
         <v>504</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>479</v>
       </c>
-      <c r="H78" t="n">
+      <c r="I78" t="n">
         <v>95</v>
       </c>
-      <c r="I78" t="n">
+      <c r="J78" t="n">
         <v>87</v>
       </c>
-      <c r="J78" t="n">
+      <c r="K78" t="n">
         <v>62</v>
       </c>
-      <c r="K78" t="n">
+      <c r="L78" t="n">
         <v>3.9</v>
       </c>
-      <c r="L78" t="n">
+      <c r="M78" t="n">
         <v>3.5</v>
       </c>
-      <c r="M78" t="n">
+      <c r="N78" t="n">
         <v>4.5</v>
       </c>
-      <c r="N78" t="n">
+      <c r="O78" t="n">
         <v>-10</v>
       </c>
-      <c r="O78" s="12" t="inlineStr">
+      <c r="P78" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5079,31 +5516,36 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F79" t="n">
+      <c r="F79" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
         <v>247</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>168</v>
       </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
         <v>68</v>
       </c>
-      <c r="I79" t="n">
+      <c r="J79" t="n">
         <v>46</v>
       </c>
-      <c r="K79" t="n">
+      <c r="L79" t="n">
         <v>2.7</v>
       </c>
-      <c r="L79" t="n">
+      <c r="M79" t="n">
         <v>2.4</v>
       </c>
-      <c r="M79" t="n">
+      <c r="N79" t="n">
         <v>2.7</v>
       </c>
-      <c r="N79" t="n">
+      <c r="O79" t="n">
         <v>-11</v>
       </c>
-      <c r="O79" s="11" t="inlineStr">
+      <c r="P79" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -5125,7 +5567,7 @@
           <t>29週で終了</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="17" t="n">
         <v>29</v>
       </c>
       <c r="E80" t="inlineStr">
@@ -5133,34 +5575,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F80" t="n">
+      <c r="F80" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
         <v>307</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>201</v>
       </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
         <v>66</v>
       </c>
-      <c r="I80" t="n">
+      <c r="J80" t="n">
         <v>40</v>
       </c>
-      <c r="J80" t="n">
+      <c r="K80" t="n">
         <v>17</v>
       </c>
-      <c r="K80" t="n">
+      <c r="L80" t="n">
         <v>2.6</v>
       </c>
-      <c r="L80" t="n">
+      <c r="M80" t="n">
         <v>1.1</v>
       </c>
-      <c r="M80" t="n">
+      <c r="N80" t="n">
         <v>2.6</v>
       </c>
-      <c r="N80" t="n">
+      <c r="O80" t="n">
         <v>-58</v>
       </c>
-      <c r="O80" s="11" t="inlineStr">
+      <c r="P80" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -5182,7 +5629,7 @@
           <t>28週で終了</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="17" t="n">
         <v>28</v>
       </c>
       <c r="E81" t="inlineStr">
@@ -5190,34 +5637,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F81" t="n">
+      <c r="F81" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
         <v>249</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>191</v>
       </c>
-      <c r="H81" t="n">
+      <c r="I81" t="n">
         <v>71</v>
       </c>
-      <c r="I81" t="n">
+      <c r="J81" t="n">
         <v>42</v>
       </c>
-      <c r="J81" t="n">
+      <c r="K81" t="n">
         <v>28</v>
       </c>
-      <c r="K81" t="n">
+      <c r="L81" t="n">
         <v>1.5</v>
       </c>
-      <c r="L81" t="n">
+      <c r="M81" t="n">
         <v>1.1</v>
       </c>
-      <c r="M81" t="n">
+      <c r="N81" t="n">
         <v>1.5</v>
       </c>
-      <c r="N81" t="n">
+      <c r="O81" t="n">
         <v>-27</v>
       </c>
-      <c r="O81" s="11" t="inlineStr">
+      <c r="P81" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -5247,34 +5699,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F82" t="n">
+      <c r="F82" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
         <v>361</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>315</v>
       </c>
-      <c r="H82" t="n">
+      <c r="I82" t="n">
         <v>77</v>
       </c>
-      <c r="I82" t="n">
+      <c r="J82" t="n">
         <v>56</v>
       </c>
-      <c r="J82" t="n">
+      <c r="K82" t="n">
         <v>34</v>
       </c>
-      <c r="K82" t="n">
+      <c r="L82" t="n">
         <v>2.4</v>
       </c>
-      <c r="L82" t="n">
+      <c r="M82" t="n">
         <v>1.1</v>
       </c>
-      <c r="M82" t="n">
+      <c r="N82" t="n">
         <v>2.4</v>
       </c>
-      <c r="N82" t="n">
+      <c r="O82" t="n">
         <v>-54</v>
       </c>
-      <c r="O82" s="14" t="inlineStr">
+      <c r="P82" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5304,34 +5761,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F83" t="n">
+      <c r="F83" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
         <v>432</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>430</v>
       </c>
-      <c r="H83" t="n">
+      <c r="I83" t="n">
         <v>88</v>
       </c>
-      <c r="I83" t="n">
+      <c r="J83" t="n">
         <v>69</v>
       </c>
-      <c r="J83" t="n">
+      <c r="K83" t="n">
         <v>49</v>
       </c>
-      <c r="K83" t="n">
+      <c r="L83" t="n">
         <v>3.6</v>
       </c>
-      <c r="L83" t="n">
+      <c r="M83" t="n">
         <v>1.5</v>
       </c>
-      <c r="M83" t="n">
+      <c r="N83" t="n">
         <v>4.1</v>
       </c>
-      <c r="N83" t="n">
+      <c r="O83" t="n">
         <v>-58</v>
       </c>
-      <c r="O83" s="12" t="inlineStr">
+      <c r="P83" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5361,34 +5823,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F84" t="n">
+      <c r="F84" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
         <v>381</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>360</v>
       </c>
-      <c r="H84" t="n">
+      <c r="I84" t="n">
         <v>84</v>
       </c>
-      <c r="I84" t="n">
+      <c r="J84" t="n">
         <v>58</v>
       </c>
-      <c r="J84" t="n">
+      <c r="K84" t="n">
         <v>38</v>
       </c>
-      <c r="K84" t="n">
+      <c r="L84" t="n">
         <v>2.6</v>
       </c>
-      <c r="L84" t="n">
+      <c r="M84" t="n">
         <v>1.1</v>
       </c>
-      <c r="M84" t="n">
+      <c r="N84" t="n">
         <v>2.6</v>
       </c>
-      <c r="N84" t="n">
+      <c r="O84" t="n">
         <v>-58</v>
       </c>
-      <c r="O84" s="14" t="inlineStr">
+      <c r="P84" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5418,34 +5885,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F85" t="n">
+      <c r="F85" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
         <v>415</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>436</v>
       </c>
-      <c r="H85" t="n">
+      <c r="I85" t="n">
         <v>93</v>
       </c>
-      <c r="I85" t="n">
+      <c r="J85" t="n">
         <v>85</v>
       </c>
-      <c r="J85" t="n">
+      <c r="K85" t="n">
         <v>70</v>
       </c>
-      <c r="K85" t="n">
+      <c r="L85" t="n">
         <v>1.5</v>
       </c>
-      <c r="L85" t="n">
+      <c r="M85" t="n">
         <v>1.3</v>
       </c>
-      <c r="M85" t="n">
+      <c r="N85" t="n">
         <v>1.7</v>
       </c>
-      <c r="N85" t="n">
+      <c r="O85" t="n">
         <v>-13</v>
       </c>
-      <c r="O85" s="12" t="inlineStr">
+      <c r="P85" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5475,34 +5947,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F86" t="n">
+      <c r="F86" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
         <v>145</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>115</v>
       </c>
-      <c r="H86" t="n">
+      <c r="I86" t="n">
         <v>70</v>
       </c>
-      <c r="I86" t="n">
+      <c r="J86" t="n">
         <v>48</v>
       </c>
-      <c r="J86" t="n">
+      <c r="K86" t="n">
         <v>49</v>
       </c>
-      <c r="K86" t="n">
+      <c r="L86" t="n">
         <v>5.6</v>
       </c>
-      <c r="L86" t="n">
+      <c r="M86" t="n">
         <v>2.3</v>
       </c>
-      <c r="M86" t="n">
+      <c r="N86" t="n">
         <v>5.6</v>
       </c>
-      <c r="N86" t="n">
+      <c r="O86" t="n">
         <v>-59</v>
       </c>
-      <c r="O86" s="11" t="inlineStr">
+      <c r="P86" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -5532,34 +6009,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F87" t="n">
+      <c r="F87" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
         <v>357</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>278</v>
       </c>
-      <c r="H87" t="n">
+      <c r="I87" t="n">
         <v>86</v>
       </c>
-      <c r="I87" t="n">
+      <c r="J87" t="n">
         <v>64</v>
       </c>
-      <c r="J87" t="n">
+      <c r="K87" t="n">
         <v>38</v>
       </c>
-      <c r="K87" t="n">
+      <c r="L87" t="n">
         <v>3</v>
       </c>
-      <c r="L87" t="n">
+      <c r="M87" t="n">
         <v>1.1</v>
       </c>
-      <c r="M87" t="n">
+      <c r="N87" t="n">
         <v>3</v>
       </c>
-      <c r="N87" t="n">
+      <c r="O87" t="n">
         <v>-63</v>
       </c>
-      <c r="O87" s="14" t="inlineStr">
+      <c r="P87" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5589,34 +6071,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F88" t="n">
+      <c r="F88" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
         <v>391</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>314</v>
       </c>
-      <c r="H88" t="n">
+      <c r="I88" t="n">
         <v>89</v>
       </c>
-      <c r="I88" t="n">
+      <c r="J88" t="n">
         <v>70</v>
       </c>
-      <c r="J88" t="n">
+      <c r="K88" t="n">
         <v>45</v>
       </c>
-      <c r="K88" t="n">
+      <c r="L88" t="n">
         <v>2.5</v>
       </c>
-      <c r="L88" t="n">
+      <c r="M88" t="n">
         <v>1.5</v>
       </c>
-      <c r="M88" t="n">
+      <c r="N88" t="n">
         <v>2.5</v>
       </c>
-      <c r="N88" t="n">
+      <c r="O88" t="n">
         <v>-40</v>
       </c>
-      <c r="O88" s="12" t="inlineStr">
+      <c r="P88" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5646,34 +6133,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F89" t="n">
+      <c r="F89" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
         <v>426</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>352</v>
       </c>
-      <c r="H89" t="n">
+      <c r="I89" t="n">
         <v>91</v>
       </c>
-      <c r="I89" t="n">
+      <c r="J89" t="n">
         <v>80</v>
       </c>
-      <c r="J89" t="n">
+      <c r="K89" t="n">
         <v>63</v>
       </c>
-      <c r="K89" t="n">
+      <c r="L89" t="n">
         <v>3.7</v>
       </c>
-      <c r="L89" t="n">
+      <c r="M89" t="n">
         <v>2.1</v>
       </c>
-      <c r="M89" t="n">
+      <c r="N89" t="n">
         <v>3.7</v>
       </c>
-      <c r="N89" t="n">
+      <c r="O89" t="n">
         <v>-43</v>
       </c>
-      <c r="O89" s="12" t="inlineStr">
+      <c r="P89" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5703,34 +6195,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F90" t="n">
+      <c r="F90" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
         <v>471</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>417</v>
       </c>
-      <c r="H90" t="n">
+      <c r="I90" t="n">
         <v>98</v>
       </c>
-      <c r="I90" t="n">
+      <c r="J90" t="n">
         <v>91</v>
       </c>
-      <c r="J90" t="n">
+      <c r="K90" t="n">
         <v>78</v>
       </c>
-      <c r="K90" t="n">
+      <c r="L90" t="n">
         <v>4.6</v>
       </c>
-      <c r="L90" t="n">
+      <c r="M90" t="n">
         <v>11.2</v>
       </c>
-      <c r="M90" t="n">
+      <c r="N90" t="n">
         <v>11.3</v>
       </c>
-      <c r="N90" t="n">
+      <c r="O90" t="n">
         <v>143</v>
       </c>
-      <c r="O90" s="12" t="inlineStr">
+      <c r="P90" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5760,34 +6257,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F91" t="n">
+      <c r="F91" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
         <v>328</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>247</v>
       </c>
-      <c r="H91" t="n">
+      <c r="I91" t="n">
         <v>75</v>
       </c>
-      <c r="I91" t="n">
+      <c r="J91" t="n">
         <v>64</v>
       </c>
-      <c r="J91" t="n">
+      <c r="K91" t="n">
         <v>48</v>
       </c>
-      <c r="K91" t="n">
+      <c r="L91" t="n">
         <v>5.6</v>
       </c>
-      <c r="L91" t="n">
+      <c r="M91" t="n">
         <v>3.2</v>
       </c>
-      <c r="M91" t="n">
+      <c r="N91" t="n">
         <v>6.3</v>
       </c>
-      <c r="N91" t="n">
+      <c r="O91" t="n">
         <v>-43</v>
       </c>
-      <c r="O91" s="14" t="inlineStr">
+      <c r="P91" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5817,34 +6319,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F92" t="n">
+      <c r="F92" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
         <v>428</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>408</v>
       </c>
-      <c r="H92" t="n">
+      <c r="I92" t="n">
         <v>95</v>
       </c>
-      <c r="I92" t="n">
+      <c r="J92" t="n">
         <v>87</v>
       </c>
-      <c r="J92" t="n">
+      <c r="K92" t="n">
         <v>71</v>
       </c>
-      <c r="K92" t="n">
+      <c r="L92" t="n">
         <v>1.9</v>
       </c>
-      <c r="L92" t="n">
+      <c r="M92" t="n">
         <v>2</v>
       </c>
-      <c r="M92" t="n">
+      <c r="N92" t="n">
         <v>2.3</v>
       </c>
-      <c r="N92" t="n">
+      <c r="O92" t="n">
         <v>5</v>
       </c>
-      <c r="O92" s="12" t="inlineStr">
+      <c r="P92" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5874,34 +6381,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F93" t="n">
+      <c r="F93" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
         <v>437</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>411</v>
       </c>
-      <c r="H93" t="n">
+      <c r="I93" t="n">
         <v>94</v>
       </c>
-      <c r="I93" t="n">
+      <c r="J93" t="n">
         <v>70</v>
       </c>
-      <c r="J93" t="n">
+      <c r="K93" t="n">
         <v>54</v>
       </c>
-      <c r="K93" t="n">
+      <c r="L93" t="n">
         <v>1.5</v>
       </c>
-      <c r="L93" t="n">
+      <c r="M93" t="n">
         <v>1.2</v>
       </c>
-      <c r="M93" t="n">
+      <c r="N93" t="n">
         <v>1.8</v>
       </c>
-      <c r="N93" t="n">
+      <c r="O93" t="n">
         <v>-20</v>
       </c>
-      <c r="O93" s="12" t="inlineStr">
+      <c r="P93" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5923,7 +6435,7 @@
           <t>51週で終了</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="17" t="n">
         <v>51</v>
       </c>
       <c r="E94" t="inlineStr">
@@ -5931,34 +6443,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F94" t="n">
+      <c r="F94" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
         <v>380</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>288</v>
       </c>
-      <c r="H94" t="n">
+      <c r="I94" t="n">
         <v>76</v>
       </c>
-      <c r="I94" t="n">
+      <c r="J94" t="n">
         <v>42</v>
       </c>
-      <c r="J94" t="n">
+      <c r="K94" t="n">
         <v>24</v>
       </c>
-      <c r="K94" t="n">
+      <c r="L94" t="n">
         <v>3.2</v>
       </c>
-      <c r="L94" t="n">
+      <c r="M94" t="n">
         <v>1.2</v>
       </c>
-      <c r="M94" t="n">
+      <c r="N94" t="n">
         <v>3.2</v>
       </c>
-      <c r="N94" t="n">
+      <c r="O94" t="n">
         <v>-62</v>
       </c>
-      <c r="O94" s="11" t="inlineStr">
+      <c r="P94" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -5980,7 +6497,7 @@
           <t>49週で終了</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="17" t="n">
         <v>49</v>
       </c>
       <c r="E95" t="inlineStr">
@@ -5988,34 +6505,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F95" t="n">
+      <c r="F95" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
         <v>364</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>298</v>
       </c>
-      <c r="H95" t="n">
+      <c r="I95" t="n">
         <v>82</v>
       </c>
-      <c r="I95" t="n">
+      <c r="J95" t="n">
         <v>47</v>
       </c>
-      <c r="J95" t="n">
+      <c r="K95" t="n">
         <v>25</v>
       </c>
-      <c r="K95" t="n">
+      <c r="L95" t="n">
         <v>2.2</v>
       </c>
-      <c r="L95" t="n">
+      <c r="M95" t="n">
         <v>1.1</v>
       </c>
-      <c r="M95" t="n">
+      <c r="N95" t="n">
         <v>2.2</v>
       </c>
-      <c r="N95" t="n">
+      <c r="O95" t="n">
         <v>-50</v>
       </c>
-      <c r="O95" s="11" t="inlineStr">
+      <c r="P95" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -6045,34 +6567,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F96" t="n">
+      <c r="F96" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
         <v>254</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>200</v>
       </c>
-      <c r="H96" t="n">
+      <c r="I96" t="n">
         <v>79</v>
       </c>
-      <c r="I96" t="n">
+      <c r="J96" t="n">
         <v>59</v>
       </c>
-      <c r="J96" t="n">
+      <c r="K96" t="n">
         <v>45</v>
       </c>
-      <c r="K96" t="n">
+      <c r="L96" t="n">
         <v>10.7</v>
       </c>
-      <c r="L96" t="n">
+      <c r="M96" t="n">
         <v>1.6</v>
       </c>
-      <c r="M96" t="n">
+      <c r="N96" t="n">
         <v>10.7</v>
       </c>
-      <c r="N96" t="n">
+      <c r="O96" t="n">
         <v>-85</v>
       </c>
-      <c r="O96" s="14" t="inlineStr">
+      <c r="P96" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6102,34 +6629,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F97" t="n">
+      <c r="F97" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
         <v>424</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>335</v>
       </c>
-      <c r="H97" t="n">
+      <c r="I97" t="n">
         <v>83</v>
       </c>
-      <c r="I97" t="n">
+      <c r="J97" t="n">
         <v>57</v>
       </c>
-      <c r="J97" t="n">
+      <c r="K97" t="n">
         <v>39</v>
       </c>
-      <c r="K97" t="n">
+      <c r="L97" t="n">
         <v>2.3</v>
       </c>
-      <c r="L97" t="n">
+      <c r="M97" t="n">
         <v>1.1</v>
       </c>
-      <c r="M97" t="n">
+      <c r="N97" t="n">
         <v>2.3</v>
       </c>
-      <c r="N97" t="n">
+      <c r="O97" t="n">
         <v>-52</v>
       </c>
-      <c r="O97" s="14" t="inlineStr">
+      <c r="P97" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6159,34 +6691,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F98" t="n">
+      <c r="F98" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
         <v>240</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>173</v>
       </c>
-      <c r="H98" t="n">
+      <c r="I98" t="n">
         <v>76</v>
       </c>
-      <c r="I98" t="n">
+      <c r="J98" t="n">
         <v>61</v>
       </c>
-      <c r="J98" t="n">
+      <c r="K98" t="n">
         <v>51</v>
       </c>
-      <c r="K98" t="n">
+      <c r="L98" t="n">
         <v>4.8</v>
       </c>
-      <c r="L98" t="n">
+      <c r="M98" t="n">
         <v>2.5</v>
       </c>
-      <c r="M98" t="n">
+      <c r="N98" t="n">
         <v>4.9</v>
       </c>
-      <c r="N98" t="n">
+      <c r="O98" t="n">
         <v>-48</v>
       </c>
-      <c r="O98" s="14" t="inlineStr">
+      <c r="P98" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6216,34 +6753,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F99" t="n">
+      <c r="F99" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
         <v>378</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>293</v>
       </c>
-      <c r="H99" t="n">
+      <c r="I99" t="n">
         <v>89</v>
       </c>
-      <c r="I99" t="n">
+      <c r="J99" t="n">
         <v>74</v>
       </c>
-      <c r="J99" t="n">
+      <c r="K99" t="n">
         <v>65</v>
       </c>
-      <c r="K99" t="n">
+      <c r="L99" t="n">
         <v>2.8</v>
       </c>
-      <c r="L99" t="n">
+      <c r="M99" t="n">
         <v>1.8</v>
       </c>
-      <c r="M99" t="n">
+      <c r="N99" t="n">
         <v>3.1</v>
       </c>
-      <c r="N99" t="n">
+      <c r="O99" t="n">
         <v>-36</v>
       </c>
-      <c r="O99" s="12" t="inlineStr">
+      <c r="P99" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -6273,34 +6815,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F100" t="n">
+      <c r="F100" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
         <v>395</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>285</v>
       </c>
-      <c r="H100" t="n">
+      <c r="I100" t="n">
         <v>83</v>
       </c>
-      <c r="I100" t="n">
+      <c r="J100" t="n">
         <v>54</v>
       </c>
-      <c r="J100" t="n">
+      <c r="K100" t="n">
         <v>42</v>
       </c>
-      <c r="K100" t="n">
+      <c r="L100" t="n">
         <v>6</v>
       </c>
-      <c r="L100" t="n">
+      <c r="M100" t="n">
         <v>1.3</v>
       </c>
-      <c r="M100" t="n">
+      <c r="N100" t="n">
         <v>6.1</v>
       </c>
-      <c r="N100" t="n">
+      <c r="O100" t="n">
         <v>-78</v>
       </c>
-      <c r="O100" s="14" t="inlineStr">
+      <c r="P100" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6322,7 +6869,7 @@
           <t>69週で終了</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="17" t="n">
         <v>69</v>
       </c>
       <c r="E101" t="inlineStr">
@@ -6330,34 +6877,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F101" t="n">
+      <c r="F101" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
         <v>403</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>271</v>
       </c>
-      <c r="H101" t="n">
+      <c r="I101" t="n">
         <v>77</v>
       </c>
-      <c r="I101" t="n">
+      <c r="J101" t="n">
         <v>45</v>
       </c>
-      <c r="J101" t="n">
+      <c r="K101" t="n">
         <v>26</v>
       </c>
-      <c r="K101" t="n">
+      <c r="L101" t="n">
         <v>2.9</v>
       </c>
-      <c r="L101" t="n">
+      <c r="M101" t="n">
         <v>1.2</v>
       </c>
-      <c r="M101" t="n">
+      <c r="N101" t="n">
         <v>3</v>
       </c>
-      <c r="N101" t="n">
+      <c r="O101" t="n">
         <v>-59</v>
       </c>
-      <c r="O101" s="11" t="inlineStr">
+      <c r="P101" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -6387,34 +6939,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F102" t="n">
+      <c r="F102" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
         <v>469</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>398</v>
       </c>
-      <c r="H102" t="n">
+      <c r="I102" t="n">
         <v>89</v>
       </c>
-      <c r="I102" t="n">
+      <c r="J102" t="n">
         <v>61</v>
       </c>
-      <c r="J102" t="n">
+      <c r="K102" t="n">
         <v>40</v>
       </c>
-      <c r="K102" t="n">
+      <c r="L102" t="n">
         <v>2.3</v>
       </c>
-      <c r="L102" t="n">
+      <c r="M102" t="n">
         <v>1</v>
       </c>
-      <c r="M102" t="n">
+      <c r="N102" t="n">
         <v>2.3</v>
       </c>
-      <c r="N102" t="n">
+      <c r="O102" t="n">
         <v>-57</v>
       </c>
-      <c r="O102" s="14" t="inlineStr">
+      <c r="P102" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6444,34 +7001,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F103" t="n">
+      <c r="F103" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
         <v>466</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>403</v>
       </c>
-      <c r="H103" t="n">
+      <c r="I103" t="n">
         <v>91</v>
       </c>
-      <c r="I103" t="n">
+      <c r="J103" t="n">
         <v>67</v>
       </c>
-      <c r="J103" t="n">
+      <c r="K103" t="n">
         <v>53</v>
       </c>
-      <c r="K103" t="n">
+      <c r="L103" t="n">
         <v>3.2</v>
       </c>
-      <c r="L103" t="n">
+      <c r="M103" t="n">
         <v>1.2</v>
       </c>
-      <c r="M103" t="n">
+      <c r="N103" t="n">
         <v>3.2</v>
       </c>
-      <c r="N103" t="n">
+      <c r="O103" t="n">
         <v>-62</v>
       </c>
-      <c r="O103" s="12" t="inlineStr">
+      <c r="P103" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -6501,34 +7063,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F104" t="n">
+      <c r="F104" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
         <v>453</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>366</v>
       </c>
-      <c r="H104" t="n">
+      <c r="I104" t="n">
         <v>85</v>
       </c>
-      <c r="I104" t="n">
+      <c r="J104" t="n">
         <v>59</v>
       </c>
-      <c r="J104" t="n">
+      <c r="K104" t="n">
         <v>42</v>
       </c>
-      <c r="K104" t="n">
+      <c r="L104" t="n">
         <v>1.6</v>
       </c>
-      <c r="L104" t="n">
+      <c r="M104" t="n">
         <v>1</v>
       </c>
-      <c r="M104" t="n">
+      <c r="N104" t="n">
         <v>1.6</v>
       </c>
-      <c r="N104" t="n">
+      <c r="O104" t="n">
         <v>-38</v>
       </c>
-      <c r="O104" s="14" t="inlineStr">
+      <c r="P104" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6558,34 +7125,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F105" t="n">
+      <c r="F105" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
         <v>411</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>337</v>
       </c>
-      <c r="H105" t="n">
+      <c r="I105" t="n">
         <v>86</v>
       </c>
-      <c r="I105" t="n">
+      <c r="J105" t="n">
         <v>51</v>
       </c>
-      <c r="J105" t="n">
+      <c r="K105" t="n">
         <v>29</v>
       </c>
-      <c r="K105" t="n">
+      <c r="L105" t="n">
         <v>2.9</v>
       </c>
-      <c r="L105" t="n">
+      <c r="M105" t="n">
         <v>1.1</v>
       </c>
-      <c r="M105" t="n">
+      <c r="N105" t="n">
         <v>2.9</v>
       </c>
-      <c r="N105" t="n">
+      <c r="O105" t="n">
         <v>-62</v>
       </c>
-      <c r="O105" s="14" t="inlineStr">
+      <c r="P105" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6615,34 +7187,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F106" t="n">
+      <c r="F106" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
         <v>533</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>497</v>
       </c>
-      <c r="H106" t="n">
+      <c r="I106" t="n">
         <v>97</v>
       </c>
-      <c r="I106" t="n">
+      <c r="J106" t="n">
         <v>77</v>
       </c>
-      <c r="J106" t="n">
+      <c r="K106" t="n">
         <v>70</v>
       </c>
-      <c r="K106" t="n">
+      <c r="L106" t="n">
         <v>5.1</v>
       </c>
-      <c r="L106" t="n">
+      <c r="M106" t="n">
         <v>3</v>
       </c>
-      <c r="M106" t="n">
+      <c r="N106" t="n">
         <v>6</v>
       </c>
-      <c r="N106" t="n">
+      <c r="O106" t="n">
         <v>-41</v>
       </c>
-      <c r="O106" s="12" t="inlineStr">
+      <c r="P106" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -6672,17 +7249,19 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F107" t="n">
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>計測中</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
         <v>260</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>172</v>
       </c>
-      <c r="H107" t="n">
+      <c r="I107" t="n">
         <v>69</v>
-      </c>
-      <c r="K107" t="n">
-        <v>1.2</v>
       </c>
       <c r="L107" t="n">
         <v>1.2</v>
@@ -6691,9 +7270,12 @@
         <v>1.2</v>
       </c>
       <c r="N107" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="O107" s="11" t="inlineStr">
+      <c r="P107" s="13" t="inlineStr">
         <is>
           <t>危険(暫定)</t>
         </is>
@@ -6723,34 +7305,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F108" t="n">
+      <c r="F108" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
         <v>334</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>246</v>
       </c>
-      <c r="H108" t="n">
+      <c r="I108" t="n">
         <v>76</v>
       </c>
-      <c r="I108" t="n">
+      <c r="J108" t="n">
         <v>43</v>
       </c>
-      <c r="J108" t="n">
+      <c r="K108" t="n">
         <v>30</v>
       </c>
-      <c r="K108" t="n">
+      <c r="L108" t="n">
         <v>1.9</v>
       </c>
-      <c r="L108" t="n">
+      <c r="M108" t="n">
         <v>1.5</v>
       </c>
-      <c r="M108" t="n">
+      <c r="N108" t="n">
         <v>1.9</v>
       </c>
-      <c r="N108" t="n">
+      <c r="O108" t="n">
         <v>-21</v>
       </c>
-      <c r="O108" s="11" t="inlineStr">
+      <c r="P108" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -6772,7 +7359,7 @@
           <t>83週継続中</t>
         </is>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" s="17" t="n">
         <v>83</v>
       </c>
       <c r="E109" t="inlineStr">
@@ -6780,34 +7367,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F109" t="n">
+      <c r="F109" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
         <v>391</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>299</v>
       </c>
-      <c r="H109" t="n">
+      <c r="I109" t="n">
         <v>71</v>
       </c>
-      <c r="I109" t="n">
+      <c r="J109" t="n">
         <v>48</v>
       </c>
-      <c r="J109" t="n">
+      <c r="K109" t="n">
         <v>33</v>
       </c>
-      <c r="K109" t="n">
+      <c r="L109" t="n">
         <v>3.4</v>
       </c>
-      <c r="L109" t="n">
+      <c r="M109" t="n">
         <v>1.6</v>
       </c>
-      <c r="M109" t="n">
+      <c r="N109" t="n">
         <v>3.4</v>
       </c>
-      <c r="N109" t="n">
+      <c r="O109" t="n">
         <v>-53</v>
       </c>
-      <c r="O109" s="11" t="inlineStr">
+      <c r="P109" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -6837,34 +7429,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F110" t="n">
+      <c r="F110" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
         <v>351</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>297</v>
       </c>
-      <c r="H110" t="n">
+      <c r="I110" t="n">
         <v>79</v>
       </c>
-      <c r="I110" t="n">
+      <c r="J110" t="n">
         <v>52</v>
       </c>
-      <c r="J110" t="n">
+      <c r="K110" t="n">
         <v>33</v>
       </c>
-      <c r="K110" t="n">
+      <c r="L110" t="n">
         <v>1.6</v>
       </c>
-      <c r="L110" t="n">
+      <c r="M110" t="n">
         <v>1</v>
       </c>
-      <c r="M110" t="n">
+      <c r="N110" t="n">
         <v>1.6</v>
       </c>
-      <c r="N110" t="n">
+      <c r="O110" t="n">
         <v>-38</v>
       </c>
-      <c r="O110" s="14" t="inlineStr">
+      <c r="P110" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6886,7 +7483,7 @@
           <t>83週継続中</t>
         </is>
       </c>
-      <c r="D111" t="n">
+      <c r="D111" s="17" t="n">
         <v>83</v>
       </c>
       <c r="E111" t="inlineStr">
@@ -6894,34 +7491,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F111" t="n">
+      <c r="F111" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
         <v>468</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>372</v>
       </c>
-      <c r="H111" t="n">
+      <c r="I111" t="n">
         <v>79</v>
       </c>
-      <c r="I111" t="n">
+      <c r="J111" t="n">
         <v>47</v>
       </c>
-      <c r="J111" t="n">
+      <c r="K111" t="n">
         <v>31</v>
       </c>
-      <c r="K111" t="n">
+      <c r="L111" t="n">
         <v>7.5</v>
       </c>
-      <c r="L111" t="n">
+      <c r="M111" t="n">
         <v>1.3</v>
       </c>
-      <c r="M111" t="n">
+      <c r="N111" t="n">
         <v>7.5</v>
       </c>
-      <c r="N111" t="n">
+      <c r="O111" t="n">
         <v>-83</v>
       </c>
-      <c r="O111" s="11" t="inlineStr">
+      <c r="P111" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -6951,34 +7553,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F112" t="n">
+      <c r="F112" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
         <v>417</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>356</v>
       </c>
-      <c r="H112" t="n">
+      <c r="I112" t="n">
         <v>85</v>
       </c>
-      <c r="I112" t="n">
+      <c r="J112" t="n">
         <v>58</v>
       </c>
-      <c r="J112" t="n">
+      <c r="K112" t="n">
         <v>44</v>
       </c>
-      <c r="K112" t="n">
+      <c r="L112" t="n">
         <v>2.5</v>
       </c>
-      <c r="L112" t="n">
+      <c r="M112" t="n">
         <v>1.2</v>
       </c>
-      <c r="M112" t="n">
+      <c r="N112" t="n">
         <v>2.5</v>
       </c>
-      <c r="N112" t="n">
+      <c r="O112" t="n">
         <v>-52</v>
       </c>
-      <c r="O112" s="14" t="inlineStr">
+      <c r="P112" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7008,34 +7615,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F113" t="n">
+      <c r="F113" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
         <v>438</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>381</v>
       </c>
-      <c r="H113" t="n">
+      <c r="I113" t="n">
         <v>87</v>
       </c>
-      <c r="I113" t="n">
+      <c r="J113" t="n">
         <v>61</v>
       </c>
-      <c r="J113" t="n">
+      <c r="K113" t="n">
         <v>43</v>
       </c>
-      <c r="K113" t="n">
+      <c r="L113" t="n">
         <v>1.7</v>
       </c>
-      <c r="L113" t="n">
+      <c r="M113" t="n">
         <v>1.1</v>
       </c>
-      <c r="M113" t="n">
+      <c r="N113" t="n">
         <v>1.7</v>
       </c>
-      <c r="N113" t="n">
+      <c r="O113" t="n">
         <v>-35</v>
       </c>
-      <c r="O113" s="14" t="inlineStr">
+      <c r="P113" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7065,34 +7677,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F114" t="n">
+      <c r="F114" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
         <v>446</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>410</v>
       </c>
-      <c r="H114" t="n">
+      <c r="I114" t="n">
         <v>92</v>
       </c>
-      <c r="I114" t="n">
+      <c r="J114" t="n">
         <v>70</v>
       </c>
-      <c r="J114" t="n">
+      <c r="K114" t="n">
         <v>53</v>
       </c>
-      <c r="K114" t="n">
+      <c r="L114" t="n">
         <v>1.9</v>
       </c>
-      <c r="L114" t="n">
+      <c r="M114" t="n">
         <v>1.2</v>
       </c>
-      <c r="M114" t="n">
+      <c r="N114" t="n">
         <v>1.9</v>
       </c>
-      <c r="N114" t="n">
+      <c r="O114" t="n">
         <v>-37</v>
       </c>
-      <c r="O114" s="12" t="inlineStr">
+      <c r="P114" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7114,7 +7731,7 @@
           <t>70週で終了</t>
         </is>
       </c>
-      <c r="D115" t="n">
+      <c r="D115" s="17" t="n">
         <v>70</v>
       </c>
       <c r="E115" t="inlineStr">
@@ -7122,34 +7739,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F115" t="n">
+      <c r="F115" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
         <v>415</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>305</v>
       </c>
-      <c r="H115" t="n">
+      <c r="I115" t="n">
         <v>73</v>
       </c>
-      <c r="I115" t="n">
+      <c r="J115" t="n">
         <v>41</v>
       </c>
-      <c r="J115" t="n">
+      <c r="K115" t="n">
         <v>26</v>
       </c>
-      <c r="K115" t="n">
+      <c r="L115" t="n">
         <v>3.3</v>
       </c>
-      <c r="L115" t="n">
+      <c r="M115" t="n">
         <v>1.4</v>
       </c>
-      <c r="M115" t="n">
+      <c r="N115" t="n">
         <v>3.3</v>
       </c>
-      <c r="N115" t="n">
+      <c r="O115" t="n">
         <v>-58</v>
       </c>
-      <c r="O115" s="11" t="inlineStr">
+      <c r="P115" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -7179,34 +7801,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F116" t="n">
+      <c r="F116" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
         <v>401</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>348</v>
       </c>
-      <c r="H116" t="n">
+      <c r="I116" t="n">
         <v>87</v>
       </c>
-      <c r="I116" t="n">
+      <c r="J116" t="n">
         <v>71</v>
       </c>
-      <c r="J116" t="n">
+      <c r="K116" t="n">
         <v>46</v>
       </c>
-      <c r="K116" t="n">
+      <c r="L116" t="n">
         <v>1.7</v>
       </c>
-      <c r="L116" t="n">
+      <c r="M116" t="n">
         <v>1.1</v>
       </c>
-      <c r="M116" t="n">
+      <c r="N116" t="n">
         <v>1.7</v>
       </c>
-      <c r="N116" t="n">
+      <c r="O116" t="n">
         <v>-35</v>
       </c>
-      <c r="O116" s="12" t="inlineStr">
+      <c r="P116" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7236,34 +7863,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F117" t="n">
+      <c r="F117" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
         <v>374</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>299</v>
       </c>
-      <c r="H117" t="n">
+      <c r="I117" t="n">
         <v>80</v>
       </c>
-      <c r="I117" t="n">
+      <c r="J117" t="n">
         <v>61</v>
       </c>
-      <c r="J117" t="n">
+      <c r="K117" t="n">
         <v>43</v>
       </c>
-      <c r="K117" t="n">
+      <c r="L117" t="n">
         <v>1.7</v>
       </c>
-      <c r="L117" t="n">
+      <c r="M117" t="n">
         <v>1.1</v>
       </c>
-      <c r="M117" t="n">
+      <c r="N117" t="n">
         <v>1.7</v>
       </c>
-      <c r="N117" t="n">
+      <c r="O117" t="n">
         <v>-35</v>
       </c>
-      <c r="O117" s="14" t="inlineStr">
+      <c r="P117" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7293,34 +7925,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F118" t="n">
+      <c r="F118" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
         <v>449</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>412</v>
       </c>
-      <c r="H118" t="n">
+      <c r="I118" t="n">
         <v>92</v>
       </c>
-      <c r="I118" t="n">
+      <c r="J118" t="n">
         <v>84</v>
       </c>
-      <c r="J118" t="n">
+      <c r="K118" t="n">
         <v>66</v>
       </c>
-      <c r="K118" t="n">
+      <c r="L118" t="n">
         <v>6.7</v>
       </c>
-      <c r="L118" t="n">
+      <c r="M118" t="n">
         <v>3.6</v>
       </c>
-      <c r="M118" t="n">
+      <c r="N118" t="n">
         <v>6.7</v>
       </c>
-      <c r="N118" t="n">
+      <c r="O118" t="n">
         <v>-46</v>
       </c>
-      <c r="O118" s="12" t="inlineStr">
+      <c r="P118" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7342,7 +7979,7 @@
           <t>45週で終了</t>
         </is>
       </c>
-      <c r="D119" t="n">
+      <c r="D119" s="17" t="n">
         <v>45</v>
       </c>
       <c r="E119" t="inlineStr">
@@ -7350,34 +7987,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F119" t="n">
+      <c r="F119" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
         <v>323</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>246</v>
       </c>
-      <c r="H119" t="n">
+      <c r="I119" t="n">
         <v>76</v>
       </c>
-      <c r="I119" t="n">
+      <c r="J119" t="n">
         <v>49</v>
       </c>
-      <c r="J119" t="n">
+      <c r="K119" t="n">
         <v>25</v>
       </c>
-      <c r="K119" t="n">
+      <c r="L119" t="n">
         <v>2.8</v>
       </c>
-      <c r="L119" t="n">
+      <c r="M119" t="n">
         <v>1.2</v>
       </c>
-      <c r="M119" t="n">
+      <c r="N119" t="n">
         <v>2.8</v>
       </c>
-      <c r="N119" t="n">
+      <c r="O119" t="n">
         <v>-57</v>
       </c>
-      <c r="O119" s="11" t="inlineStr">
+      <c r="P119" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -7407,34 +8049,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F120" t="n">
+      <c r="F120" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
         <v>246</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>163</v>
       </c>
-      <c r="H120" t="n">
+      <c r="I120" t="n">
         <v>83</v>
       </c>
-      <c r="I120" t="n">
+      <c r="J120" t="n">
         <v>58</v>
       </c>
-      <c r="J120" t="n">
+      <c r="K120" t="n">
         <v>34</v>
       </c>
-      <c r="K120" t="n">
+      <c r="L120" t="n">
         <v>2.5</v>
       </c>
-      <c r="L120" t="n">
+      <c r="M120" t="n">
         <v>1.1</v>
       </c>
-      <c r="M120" t="n">
+      <c r="N120" t="n">
         <v>2.5</v>
       </c>
-      <c r="N120" t="n">
+      <c r="O120" t="n">
         <v>-56</v>
       </c>
-      <c r="O120" s="14" t="inlineStr">
+      <c r="P120" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7464,34 +8111,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F121" t="n">
+      <c r="F121" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
         <v>341</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>249</v>
       </c>
-      <c r="H121" t="n">
+      <c r="I121" t="n">
         <v>91</v>
       </c>
-      <c r="I121" t="n">
+      <c r="J121" t="n">
         <v>62</v>
       </c>
-      <c r="J121" t="n">
+      <c r="K121" t="n">
         <v>37</v>
       </c>
-      <c r="K121" t="n">
+      <c r="L121" t="n">
         <v>3.4</v>
       </c>
-      <c r="L121" t="n">
+      <c r="M121" t="n">
         <v>1</v>
       </c>
-      <c r="M121" t="n">
+      <c r="N121" t="n">
         <v>3.4</v>
       </c>
-      <c r="N121" t="n">
+      <c r="O121" t="n">
         <v>-71</v>
       </c>
-      <c r="O121" s="14" t="inlineStr">
+      <c r="P121" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7521,34 +8173,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F122" t="n">
+      <c r="F122" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
         <v>152</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>107</v>
       </c>
-      <c r="H122" t="n">
+      <c r="I122" t="n">
         <v>88</v>
       </c>
-      <c r="I122" t="n">
+      <c r="J122" t="n">
         <v>56</v>
       </c>
-      <c r="J122" t="n">
+      <c r="K122" t="n">
         <v>39</v>
       </c>
-      <c r="K122" t="n">
+      <c r="L122" t="n">
         <v>3</v>
       </c>
-      <c r="L122" t="n">
+      <c r="M122" t="n">
         <v>1.4</v>
       </c>
-      <c r="M122" t="n">
+      <c r="N122" t="n">
         <v>3</v>
       </c>
-      <c r="N122" t="n">
+      <c r="O122" t="n">
         <v>-53</v>
       </c>
-      <c r="O122" s="14" t="inlineStr">
+      <c r="P122" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7578,34 +8235,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F123" t="n">
+      <c r="F123" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
         <v>359</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>272</v>
       </c>
-      <c r="H123" t="n">
+      <c r="I123" t="n">
         <v>95</v>
       </c>
-      <c r="I123" t="n">
+      <c r="J123" t="n">
         <v>63</v>
       </c>
-      <c r="J123" t="n">
+      <c r="K123" t="n">
         <v>32</v>
       </c>
-      <c r="K123" t="n">
+      <c r="L123" t="n">
         <v>2.3</v>
       </c>
-      <c r="L123" t="n">
+      <c r="M123" t="n">
         <v>1.1</v>
       </c>
-      <c r="M123" t="n">
+      <c r="N123" t="n">
         <v>2.3</v>
       </c>
-      <c r="N123" t="n">
+      <c r="O123" t="n">
         <v>-52</v>
       </c>
-      <c r="O123" s="14" t="inlineStr">
+      <c r="P123" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7635,34 +8297,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F124" t="n">
+      <c r="F124" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
         <v>419</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>417</v>
       </c>
-      <c r="H124" t="n">
+      <c r="I124" t="n">
         <v>95</v>
       </c>
-      <c r="I124" t="n">
+      <c r="J124" t="n">
         <v>88</v>
       </c>
-      <c r="J124" t="n">
+      <c r="K124" t="n">
         <v>66</v>
       </c>
-      <c r="K124" t="n">
+      <c r="L124" t="n">
         <v>4.3</v>
       </c>
-      <c r="L124" t="n">
+      <c r="M124" t="n">
         <v>3.4</v>
       </c>
-      <c r="M124" t="n">
+      <c r="N124" t="n">
         <v>5.9</v>
       </c>
-      <c r="N124" t="n">
+      <c r="O124" t="n">
         <v>-21</v>
       </c>
-      <c r="O124" s="12" t="inlineStr">
+      <c r="P124" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7692,34 +8359,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F125" t="n">
+      <c r="F125" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
         <v>394</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>349</v>
       </c>
-      <c r="H125" t="n">
+      <c r="I125" t="n">
         <v>84</v>
       </c>
-      <c r="I125" t="n">
+      <c r="J125" t="n">
         <v>75</v>
       </c>
-      <c r="J125" t="n">
+      <c r="K125" t="n">
         <v>48</v>
       </c>
-      <c r="K125" t="n">
+      <c r="L125" t="n">
         <v>1.7</v>
       </c>
-      <c r="L125" t="n">
+      <c r="M125" t="n">
         <v>1.2</v>
       </c>
-      <c r="M125" t="n">
+      <c r="N125" t="n">
         <v>1.7</v>
       </c>
-      <c r="N125" t="n">
+      <c r="O125" t="n">
         <v>-29</v>
       </c>
-      <c r="O125" s="12" t="inlineStr">
+      <c r="P125" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7741,7 +8413,7 @@
           <t>20週で終了</t>
         </is>
       </c>
-      <c r="D126" t="n">
+      <c r="D126" s="17" t="n">
         <v>20</v>
       </c>
       <c r="E126" t="inlineStr">
@@ -7749,34 +8421,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F126" t="n">
+      <c r="F126" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
         <v>253</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>177</v>
       </c>
-      <c r="H126" t="n">
+      <c r="I126" t="n">
         <v>66</v>
       </c>
-      <c r="I126" t="n">
+      <c r="J126" t="n">
         <v>47</v>
       </c>
-      <c r="J126" t="n">
+      <c r="K126" t="n">
         <v>24</v>
       </c>
-      <c r="K126" t="n">
+      <c r="L126" t="n">
         <v>2.8</v>
       </c>
-      <c r="L126" t="n">
+      <c r="M126" t="n">
         <v>1.2</v>
       </c>
-      <c r="M126" t="n">
+      <c r="N126" t="n">
         <v>2.8</v>
       </c>
-      <c r="N126" t="n">
+      <c r="O126" t="n">
         <v>-57</v>
       </c>
-      <c r="O126" s="11" t="inlineStr">
+      <c r="P126" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -7798,7 +8475,7 @@
           <t>30週で終了</t>
         </is>
       </c>
-      <c r="D127" t="n">
+      <c r="D127" s="17" t="n">
         <v>30</v>
       </c>
       <c r="E127" t="inlineStr">
@@ -7806,34 +8483,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F127" t="n">
+      <c r="F127" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
         <v>258</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>175</v>
       </c>
-      <c r="H127" t="n">
+      <c r="I127" t="n">
         <v>68</v>
       </c>
-      <c r="I127" t="n">
+      <c r="J127" t="n">
         <v>35</v>
       </c>
-      <c r="J127" t="n">
+      <c r="K127" t="n">
         <v>21</v>
       </c>
-      <c r="K127" t="n">
+      <c r="L127" t="n">
         <v>2.1</v>
       </c>
-      <c r="L127" t="n">
+      <c r="M127" t="n">
         <v>1.1</v>
       </c>
-      <c r="M127" t="n">
+      <c r="N127" t="n">
         <v>2.2</v>
       </c>
-      <c r="N127" t="n">
+      <c r="O127" t="n">
         <v>-48</v>
       </c>
-      <c r="O127" s="11" t="inlineStr">
+      <c r="P127" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -7855,7 +8537,7 @@
           <t>100週継続中</t>
         </is>
       </c>
-      <c r="D128" t="n">
+      <c r="D128" s="17" t="n">
         <v>100</v>
       </c>
       <c r="E128" t="inlineStr">
@@ -7863,34 +8545,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F128" t="n">
+      <c r="F128" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
         <v>333</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>262</v>
       </c>
-      <c r="H128" t="n">
+      <c r="I128" t="n">
         <v>78</v>
       </c>
-      <c r="I128" t="n">
+      <c r="J128" t="n">
         <v>47</v>
       </c>
-      <c r="J128" t="n">
+      <c r="K128" t="n">
         <v>36</v>
       </c>
-      <c r="K128" t="n">
+      <c r="L128" t="n">
         <v>4.4</v>
       </c>
-      <c r="L128" t="n">
+      <c r="M128" t="n">
         <v>1.2</v>
       </c>
-      <c r="M128" t="n">
+      <c r="N128" t="n">
         <v>4.4</v>
       </c>
-      <c r="N128" t="n">
+      <c r="O128" t="n">
         <v>-73</v>
       </c>
-      <c r="O128" s="11" t="inlineStr">
+      <c r="P128" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -7920,34 +8607,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F129" t="n">
+      <c r="F129" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
         <v>369</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>311</v>
       </c>
-      <c r="H129" t="n">
+      <c r="I129" t="n">
         <v>84</v>
       </c>
-      <c r="I129" t="n">
+      <c r="J129" t="n">
         <v>55</v>
       </c>
-      <c r="J129" t="n">
+      <c r="K129" t="n">
         <v>37</v>
       </c>
-      <c r="K129" t="n">
+      <c r="L129" t="n">
         <v>5.4</v>
       </c>
-      <c r="L129" t="n">
+      <c r="M129" t="n">
         <v>1.2</v>
       </c>
-      <c r="M129" t="n">
+      <c r="N129" t="n">
         <v>5.4</v>
       </c>
-      <c r="N129" t="n">
+      <c r="O129" t="n">
         <v>-78</v>
       </c>
-      <c r="O129" s="14" t="inlineStr">
+      <c r="P129" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7977,34 +8669,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F130" t="n">
+      <c r="F130" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
         <v>353</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>358</v>
       </c>
-      <c r="H130" t="n">
+      <c r="I130" t="n">
         <v>92</v>
       </c>
-      <c r="I130" t="n">
+      <c r="J130" t="n">
         <v>88</v>
       </c>
-      <c r="J130" t="n">
+      <c r="K130" t="n">
         <v>77</v>
       </c>
-      <c r="K130" t="n">
+      <c r="L130" t="n">
         <v>2.9</v>
       </c>
-      <c r="L130" t="n">
+      <c r="M130" t="n">
         <v>1.8</v>
       </c>
-      <c r="M130" t="n">
+      <c r="N130" t="n">
         <v>4.2</v>
       </c>
-      <c r="N130" t="n">
+      <c r="O130" t="n">
         <v>-38</v>
       </c>
-      <c r="O130" s="12" t="inlineStr">
+      <c r="P130" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8034,34 +8731,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F131" t="n">
+      <c r="F131" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
         <v>239</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>191</v>
       </c>
-      <c r="H131" t="n">
+      <c r="I131" t="n">
         <v>72</v>
       </c>
-      <c r="I131" t="n">
+      <c r="J131" t="n">
         <v>56</v>
       </c>
-      <c r="J131" t="n">
+      <c r="K131" t="n">
         <v>41</v>
       </c>
-      <c r="K131" t="n">
+      <c r="L131" t="n">
         <v>2.1</v>
       </c>
-      <c r="L131" t="n">
+      <c r="M131" t="n">
         <v>1.2</v>
       </c>
-      <c r="M131" t="n">
+      <c r="N131" t="n">
         <v>2.1</v>
       </c>
-      <c r="N131" t="n">
+      <c r="O131" t="n">
         <v>-43</v>
       </c>
-      <c r="O131" s="14" t="inlineStr">
+      <c r="P131" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8091,34 +8793,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F132" t="n">
+      <c r="F132" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
         <v>323</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>322</v>
       </c>
-      <c r="H132" t="n">
+      <c r="I132" t="n">
         <v>90</v>
       </c>
-      <c r="I132" t="n">
+      <c r="J132" t="n">
         <v>77</v>
       </c>
-      <c r="J132" t="n">
+      <c r="K132" t="n">
         <v>60</v>
       </c>
-      <c r="K132" t="n">
+      <c r="L132" t="n">
         <v>2.7</v>
       </c>
-      <c r="L132" t="n">
+      <c r="M132" t="n">
         <v>1.6</v>
       </c>
-      <c r="M132" t="n">
+      <c r="N132" t="n">
         <v>2.7</v>
       </c>
-      <c r="N132" t="n">
+      <c r="O132" t="n">
         <v>-41</v>
       </c>
-      <c r="O132" s="12" t="inlineStr">
+      <c r="P132" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8148,34 +8855,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F133" t="n">
+      <c r="F133" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
         <v>367</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>368</v>
       </c>
-      <c r="H133" t="n">
+      <c r="I133" t="n">
         <v>91</v>
       </c>
-      <c r="I133" t="n">
+      <c r="J133" t="n">
         <v>77</v>
       </c>
-      <c r="J133" t="n">
+      <c r="K133" t="n">
         <v>51</v>
       </c>
-      <c r="K133" t="n">
+      <c r="L133" t="n">
         <v>5.1</v>
       </c>
-      <c r="L133" t="n">
+      <c r="M133" t="n">
         <v>1.4</v>
       </c>
-      <c r="M133" t="n">
+      <c r="N133" t="n">
         <v>5.8</v>
       </c>
-      <c r="N133" t="n">
+      <c r="O133" t="n">
         <v>-73</v>
       </c>
-      <c r="O133" s="12" t="inlineStr">
+      <c r="P133" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8205,34 +8917,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F134" t="n">
+      <c r="F134" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
         <v>282</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>233</v>
       </c>
-      <c r="H134" t="n">
+      <c r="I134" t="n">
         <v>72</v>
       </c>
-      <c r="I134" t="n">
+      <c r="J134" t="n">
         <v>51</v>
       </c>
-      <c r="J134" t="n">
+      <c r="K134" t="n">
         <v>34</v>
       </c>
-      <c r="K134" t="n">
+      <c r="L134" t="n">
         <v>1.9</v>
       </c>
-      <c r="L134" t="n">
+      <c r="M134" t="n">
         <v>1.1</v>
       </c>
-      <c r="M134" t="n">
+      <c r="N134" t="n">
         <v>1.9</v>
       </c>
-      <c r="N134" t="n">
+      <c r="O134" t="n">
         <v>-42</v>
       </c>
-      <c r="O134" s="14" t="inlineStr">
+      <c r="P134" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8254,7 +8971,7 @@
           <t>61週で終了</t>
         </is>
       </c>
-      <c r="D135" t="n">
+      <c r="D135" s="17" t="n">
         <v>61</v>
       </c>
       <c r="E135" t="inlineStr">
@@ -8262,34 +8979,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F135" t="n">
+      <c r="F135" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
         <v>325</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>258</v>
       </c>
-      <c r="H135" t="n">
+      <c r="I135" t="n">
         <v>69</v>
       </c>
-      <c r="I135" t="n">
+      <c r="J135" t="n">
         <v>42</v>
       </c>
-      <c r="J135" t="n">
+      <c r="K135" t="n">
         <v>22</v>
       </c>
-      <c r="K135" t="n">
+      <c r="L135" t="n">
         <v>3.6</v>
       </c>
-      <c r="L135" t="n">
+      <c r="M135" t="n">
         <v>1.2</v>
       </c>
-      <c r="M135" t="n">
+      <c r="N135" t="n">
         <v>3.6</v>
       </c>
-      <c r="N135" t="n">
+      <c r="O135" t="n">
         <v>-67</v>
       </c>
-      <c r="O135" s="11" t="inlineStr">
+      <c r="P135" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -8319,34 +9041,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F136" t="n">
+      <c r="F136" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
         <v>397</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>411</v>
       </c>
-      <c r="H136" t="n">
+      <c r="I136" t="n">
         <v>90</v>
       </c>
-      <c r="I136" t="n">
+      <c r="J136" t="n">
         <v>74</v>
       </c>
-      <c r="J136" t="n">
+      <c r="K136" t="n">
         <v>58</v>
       </c>
-      <c r="K136" t="n">
+      <c r="L136" t="n">
         <v>3.4</v>
       </c>
-      <c r="L136" t="n">
+      <c r="M136" t="n">
         <v>1.5</v>
       </c>
-      <c r="M136" t="n">
+      <c r="N136" t="n">
         <v>4.2</v>
       </c>
-      <c r="N136" t="n">
+      <c r="O136" t="n">
         <v>-56</v>
       </c>
-      <c r="O136" s="12" t="inlineStr">
+      <c r="P136" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8376,34 +9103,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F137" t="n">
+      <c r="F137" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
         <v>383</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>297</v>
       </c>
-      <c r="H137" t="n">
+      <c r="I137" t="n">
         <v>96</v>
       </c>
-      <c r="I137" t="n">
+      <c r="J137" t="n">
         <v>71</v>
       </c>
-      <c r="J137" t="n">
+      <c r="K137" t="n">
         <v>53</v>
       </c>
-      <c r="K137" t="n">
+      <c r="L137" t="n">
         <v>6</v>
       </c>
-      <c r="L137" t="n">
+      <c r="M137" t="n">
         <v>1.5</v>
       </c>
-      <c r="M137" t="n">
+      <c r="N137" t="n">
         <v>7</v>
       </c>
-      <c r="N137" t="n">
+      <c r="O137" t="n">
         <v>-75</v>
       </c>
-      <c r="O137" s="12" t="inlineStr">
+      <c r="P137" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8433,34 +9165,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F138" t="n">
+      <c r="F138" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
         <v>298</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>242</v>
       </c>
-      <c r="H138" t="n">
+      <c r="I138" t="n">
         <v>79</v>
       </c>
-      <c r="I138" t="n">
+      <c r="J138" t="n">
         <v>66</v>
       </c>
-      <c r="J138" t="n">
+      <c r="K138" t="n">
         <v>36</v>
       </c>
-      <c r="K138" t="n">
+      <c r="L138" t="n">
         <v>1.8</v>
       </c>
-      <c r="L138" t="n">
+      <c r="M138" t="n">
         <v>1.1</v>
       </c>
-      <c r="M138" t="n">
+      <c r="N138" t="n">
         <v>1.8</v>
       </c>
-      <c r="N138" t="n">
+      <c r="O138" t="n">
         <v>-39</v>
       </c>
-      <c r="O138" s="12" t="inlineStr">
+      <c r="P138" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8490,34 +9227,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F139" t="n">
+      <c r="F139" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
         <v>359</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>308</v>
       </c>
-      <c r="H139" t="n">
+      <c r="I139" t="n">
         <v>84</v>
       </c>
-      <c r="I139" t="n">
+      <c r="J139" t="n">
         <v>66</v>
       </c>
-      <c r="J139" t="n">
+      <c r="K139" t="n">
         <v>33</v>
       </c>
-      <c r="K139" t="n">
+      <c r="L139" t="n">
         <v>3.8</v>
       </c>
-      <c r="L139" t="n">
+      <c r="M139" t="n">
         <v>1.1</v>
       </c>
-      <c r="M139" t="n">
+      <c r="N139" t="n">
         <v>3.8</v>
       </c>
-      <c r="N139" t="n">
+      <c r="O139" t="n">
         <v>-71</v>
       </c>
-      <c r="O139" s="12" t="inlineStr">
+      <c r="P139" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8547,34 +9289,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F140" t="n">
+      <c r="F140" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
         <v>332</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>294</v>
       </c>
-      <c r="H140" t="n">
+      <c r="I140" t="n">
         <v>86</v>
       </c>
-      <c r="I140" t="n">
+      <c r="J140" t="n">
         <v>72</v>
       </c>
-      <c r="J140" t="n">
+      <c r="K140" t="n">
         <v>44</v>
       </c>
-      <c r="K140" t="n">
+      <c r="L140" t="n">
         <v>1.4</v>
       </c>
-      <c r="L140" t="n">
+      <c r="M140" t="n">
         <v>1</v>
       </c>
-      <c r="M140" t="n">
+      <c r="N140" t="n">
         <v>1.4</v>
       </c>
-      <c r="N140" t="n">
+      <c r="O140" t="n">
         <v>-29</v>
       </c>
-      <c r="O140" s="12" t="inlineStr">
+      <c r="P140" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8604,34 +9351,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F141" t="n">
+      <c r="F141" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
         <v>289</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>257</v>
       </c>
-      <c r="H141" t="n">
+      <c r="I141" t="n">
         <v>84</v>
       </c>
-      <c r="I141" t="n">
+      <c r="J141" t="n">
         <v>61</v>
       </c>
-      <c r="J141" t="n">
+      <c r="K141" t="n">
         <v>35</v>
       </c>
-      <c r="K141" t="n">
+      <c r="L141" t="n">
         <v>2.9</v>
       </c>
-      <c r="L141" t="n">
+      <c r="M141" t="n">
         <v>1.2</v>
       </c>
-      <c r="M141" t="n">
+      <c r="N141" t="n">
         <v>2.9</v>
       </c>
-      <c r="N141" t="n">
+      <c r="O141" t="n">
         <v>-59</v>
       </c>
-      <c r="O141" s="14" t="inlineStr">
+      <c r="P141" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8661,34 +9413,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F142" t="n">
+      <c r="F142" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
         <v>228</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>166</v>
       </c>
-      <c r="H142" t="n">
+      <c r="I142" t="n">
         <v>77</v>
       </c>
-      <c r="I142" t="n">
+      <c r="J142" t="n">
         <v>60</v>
       </c>
-      <c r="J142" t="n">
+      <c r="K142" t="n">
         <v>54</v>
       </c>
-      <c r="K142" t="n">
+      <c r="L142" t="n">
         <v>4.4</v>
       </c>
-      <c r="L142" t="n">
+      <c r="M142" t="n">
         <v>3.3</v>
       </c>
-      <c r="M142" t="n">
+      <c r="N142" t="n">
         <v>4.7</v>
       </c>
-      <c r="N142" t="n">
+      <c r="O142" t="n">
         <v>-25</v>
       </c>
-      <c r="O142" s="14" t="inlineStr">
+      <c r="P142" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8718,34 +9475,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F143" t="n">
+      <c r="F143" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
         <v>291</v>
       </c>
-      <c r="G143" t="n">
+      <c r="H143" t="n">
         <v>280</v>
       </c>
-      <c r="H143" t="n">
+      <c r="I143" t="n">
         <v>82</v>
       </c>
-      <c r="I143" t="n">
+      <c r="J143" t="n">
         <v>62</v>
       </c>
-      <c r="J143" t="n">
+      <c r="K143" t="n">
         <v>45</v>
       </c>
-      <c r="K143" t="n">
+      <c r="L143" t="n">
         <v>2.6</v>
       </c>
-      <c r="L143" t="n">
+      <c r="M143" t="n">
         <v>1.2</v>
       </c>
-      <c r="M143" t="n">
+      <c r="N143" t="n">
         <v>2.6</v>
       </c>
-      <c r="N143" t="n">
+      <c r="O143" t="n">
         <v>-54</v>
       </c>
-      <c r="O143" s="14" t="inlineStr">
+      <c r="P143" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8775,34 +9537,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F144" t="n">
+      <c r="F144" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
         <v>264</v>
       </c>
-      <c r="G144" t="n">
+      <c r="H144" t="n">
         <v>315</v>
       </c>
-      <c r="H144" t="n">
+      <c r="I144" t="n">
         <v>102</v>
       </c>
-      <c r="I144" t="n">
+      <c r="J144" t="n">
         <v>98</v>
       </c>
-      <c r="J144" t="n">
+      <c r="K144" t="n">
         <v>92</v>
       </c>
-      <c r="K144" t="n">
+      <c r="L144" t="n">
         <v>12.1</v>
       </c>
-      <c r="L144" t="n">
+      <c r="M144" t="n">
         <v>4.1</v>
       </c>
-      <c r="M144" t="n">
+      <c r="N144" t="n">
         <v>12.2</v>
       </c>
-      <c r="N144" t="n">
+      <c r="O144" t="n">
         <v>-66</v>
       </c>
-      <c r="O144" s="12" t="inlineStr">
+      <c r="P144" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8832,34 +9599,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F145" t="n">
+      <c r="F145" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
         <v>270</v>
       </c>
-      <c r="G145" t="n">
+      <c r="H145" t="n">
         <v>264</v>
       </c>
-      <c r="H145" t="n">
+      <c r="I145" t="n">
         <v>84</v>
       </c>
-      <c r="I145" t="n">
+      <c r="J145" t="n">
         <v>65</v>
       </c>
-      <c r="J145" t="n">
+      <c r="K145" t="n">
         <v>50</v>
       </c>
-      <c r="K145" t="n">
+      <c r="L145" t="n">
         <v>5.5</v>
       </c>
-      <c r="L145" t="n">
+      <c r="M145" t="n">
         <v>1.5</v>
       </c>
-      <c r="M145" t="n">
+      <c r="N145" t="n">
         <v>5.5</v>
       </c>
-      <c r="N145" t="n">
+      <c r="O145" t="n">
         <v>-73</v>
       </c>
-      <c r="O145" s="14" t="inlineStr">
+      <c r="P145" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8889,34 +9661,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F146" t="n">
+      <c r="F146" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
         <v>246</v>
       </c>
-      <c r="G146" t="n">
+      <c r="H146" t="n">
         <v>224</v>
       </c>
-      <c r="H146" t="n">
+      <c r="I146" t="n">
         <v>88</v>
       </c>
-      <c r="I146" t="n">
+      <c r="J146" t="n">
         <v>73</v>
       </c>
-      <c r="J146" t="n">
+      <c r="K146" t="n">
         <v>55</v>
       </c>
-      <c r="K146" t="n">
+      <c r="L146" t="n">
         <v>1.5</v>
       </c>
-      <c r="L146" t="n">
+      <c r="M146" t="n">
         <v>1.1</v>
       </c>
-      <c r="M146" t="n">
+      <c r="N146" t="n">
         <v>1.5</v>
       </c>
-      <c r="N146" t="n">
+      <c r="O146" t="n">
         <v>-27</v>
       </c>
-      <c r="O146" s="12" t="inlineStr">
+      <c r="P146" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8946,34 +9723,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F147" t="n">
+      <c r="F147" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
         <v>274</v>
       </c>
-      <c r="G147" t="n">
+      <c r="H147" t="n">
         <v>235</v>
       </c>
-      <c r="H147" t="n">
+      <c r="I147" t="n">
         <v>83</v>
       </c>
-      <c r="I147" t="n">
+      <c r="J147" t="n">
         <v>59</v>
       </c>
-      <c r="J147" t="n">
+      <c r="K147" t="n">
         <v>40</v>
       </c>
-      <c r="K147" t="n">
+      <c r="L147" t="n">
         <v>3.8</v>
       </c>
-      <c r="L147" t="n">
+      <c r="M147" t="n">
         <v>1.2</v>
       </c>
-      <c r="M147" t="n">
+      <c r="N147" t="n">
         <v>3.8</v>
       </c>
-      <c r="N147" t="n">
+      <c r="O147" t="n">
         <v>-68</v>
       </c>
-      <c r="O147" s="14" t="inlineStr">
+      <c r="P147" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -9003,34 +9785,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F148" t="n">
+      <c r="F148" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
         <v>267</v>
       </c>
-      <c r="G148" t="n">
+      <c r="H148" t="n">
         <v>277</v>
       </c>
-      <c r="H148" t="n">
+      <c r="I148" t="n">
         <v>100</v>
       </c>
-      <c r="I148" t="n">
+      <c r="J148" t="n">
         <v>90</v>
       </c>
-      <c r="J148" t="n">
+      <c r="K148" t="n">
         <v>72</v>
       </c>
-      <c r="K148" t="n">
+      <c r="L148" t="n">
         <v>2.3</v>
       </c>
-      <c r="L148" t="n">
+      <c r="M148" t="n">
         <v>1.4</v>
       </c>
-      <c r="M148" t="n">
+      <c r="N148" t="n">
         <v>3.8</v>
       </c>
-      <c r="N148" t="n">
+      <c r="O148" t="n">
         <v>-39</v>
       </c>
-      <c r="O148" s="12" t="inlineStr">
+      <c r="P148" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9052,7 +9839,7 @@
           <t>27週で終了</t>
         </is>
       </c>
-      <c r="D149" t="n">
+      <c r="D149" s="17" t="n">
         <v>27</v>
       </c>
       <c r="E149" t="inlineStr">
@@ -9060,34 +9847,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F149" t="n">
+      <c r="F149" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
         <v>189</v>
       </c>
-      <c r="G149" t="n">
+      <c r="H149" t="n">
         <v>136</v>
       </c>
-      <c r="H149" t="n">
+      <c r="I149" t="n">
         <v>70</v>
       </c>
-      <c r="I149" t="n">
+      <c r="J149" t="n">
         <v>46</v>
       </c>
-      <c r="J149" t="n">
+      <c r="K149" t="n">
         <v>28</v>
       </c>
-      <c r="K149" t="n">
+      <c r="L149" t="n">
         <v>2.5</v>
       </c>
-      <c r="L149" t="n">
+      <c r="M149" t="n">
         <v>1.2</v>
       </c>
-      <c r="M149" t="n">
+      <c r="N149" t="n">
         <v>2.5</v>
       </c>
-      <c r="N149" t="n">
+      <c r="O149" t="n">
         <v>-52</v>
       </c>
-      <c r="O149" s="11" t="inlineStr">
+      <c r="P149" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -9117,34 +9909,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F150" t="n">
+      <c r="F150" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
         <v>217</v>
       </c>
-      <c r="G150" t="n">
+      <c r="H150" t="n">
         <v>188</v>
       </c>
-      <c r="H150" t="n">
+      <c r="I150" t="n">
         <v>84</v>
       </c>
-      <c r="I150" t="n">
+      <c r="J150" t="n">
         <v>68</v>
       </c>
-      <c r="J150" t="n">
+      <c r="K150" t="n">
         <v>47</v>
       </c>
-      <c r="K150" t="n">
+      <c r="L150" t="n">
         <v>1.7</v>
       </c>
-      <c r="L150" t="n">
+      <c r="M150" t="n">
         <v>1</v>
       </c>
-      <c r="M150" t="n">
+      <c r="N150" t="n">
         <v>1.7</v>
       </c>
-      <c r="N150" t="n">
+      <c r="O150" t="n">
         <v>-41</v>
       </c>
-      <c r="O150" s="12" t="inlineStr">
+      <c r="P150" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9174,34 +9971,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F151" t="n">
+      <c r="F151" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
         <v>262</v>
       </c>
-      <c r="G151" t="n">
+      <c r="H151" t="n">
         <v>218</v>
       </c>
-      <c r="H151" t="n">
+      <c r="I151" t="n">
         <v>81</v>
       </c>
-      <c r="I151" t="n">
+      <c r="J151" t="n">
         <v>60</v>
       </c>
-      <c r="J151" t="n">
+      <c r="K151" t="n">
         <v>41</v>
       </c>
-      <c r="K151" t="n">
+      <c r="L151" t="n">
         <v>4.1</v>
       </c>
-      <c r="L151" t="n">
+      <c r="M151" t="n">
         <v>1.3</v>
       </c>
-      <c r="M151" t="n">
+      <c r="N151" t="n">
         <v>4.1</v>
       </c>
-      <c r="N151" t="n">
+      <c r="O151" t="n">
         <v>-68</v>
       </c>
-      <c r="O151" s="14" t="inlineStr">
+      <c r="P151" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -9223,7 +10025,7 @@
           <t>30週で終了</t>
         </is>
       </c>
-      <c r="D152" t="n">
+      <c r="D152" s="17" t="n">
         <v>30</v>
       </c>
       <c r="E152" t="inlineStr">
@@ -9231,34 +10033,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F152" t="n">
+      <c r="F152" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
         <v>149</v>
       </c>
-      <c r="G152" t="n">
+      <c r="H152" t="n">
         <v>88</v>
       </c>
-      <c r="H152" t="n">
+      <c r="I152" t="n">
         <v>57</v>
       </c>
-      <c r="I152" t="n">
+      <c r="J152" t="n">
         <v>33</v>
       </c>
-      <c r="J152" t="n">
+      <c r="K152" t="n">
         <v>19</v>
       </c>
-      <c r="K152" t="n">
+      <c r="L152" t="n">
         <v>2</v>
       </c>
-      <c r="L152" t="n">
+      <c r="M152" t="n">
         <v>1.1</v>
       </c>
-      <c r="M152" t="n">
+      <c r="N152" t="n">
         <v>2</v>
       </c>
-      <c r="N152" t="n">
+      <c r="O152" t="n">
         <v>-45</v>
       </c>
-      <c r="O152" s="11" t="inlineStr">
+      <c r="P152" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -9288,34 +10095,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F153" t="n">
+      <c r="F153" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
         <v>297</v>
       </c>
-      <c r="G153" t="n">
+      <c r="H153" t="n">
         <v>242</v>
       </c>
-      <c r="H153" t="n">
+      <c r="I153" t="n">
         <v>76</v>
       </c>
-      <c r="I153" t="n">
+      <c r="J153" t="n">
         <v>50</v>
       </c>
-      <c r="J153" t="n">
+      <c r="K153" t="n">
         <v>35</v>
       </c>
-      <c r="K153" t="n">
+      <c r="L153" t="n">
         <v>3.2</v>
       </c>
-      <c r="L153" t="n">
+      <c r="M153" t="n">
         <v>1.2</v>
       </c>
-      <c r="M153" t="n">
+      <c r="N153" t="n">
         <v>3.2</v>
       </c>
-      <c r="N153" t="n">
+      <c r="O153" t="n">
         <v>-62</v>
       </c>
-      <c r="O153" s="14" t="inlineStr">
+      <c r="P153" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -9345,34 +10157,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F154" t="n">
+      <c r="F154" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
         <v>305</v>
       </c>
-      <c r="G154" t="n">
+      <c r="H154" t="n">
         <v>279</v>
       </c>
-      <c r="H154" t="n">
+      <c r="I154" t="n">
         <v>85</v>
       </c>
-      <c r="I154" t="n">
+      <c r="J154" t="n">
         <v>66</v>
       </c>
-      <c r="J154" t="n">
+      <c r="K154" t="n">
         <v>47</v>
       </c>
-      <c r="K154" t="n">
+      <c r="L154" t="n">
         <v>1.4</v>
       </c>
-      <c r="L154" t="n">
+      <c r="M154" t="n">
         <v>1.1</v>
       </c>
-      <c r="M154" t="n">
+      <c r="N154" t="n">
         <v>1.4</v>
       </c>
-      <c r="N154" t="n">
+      <c r="O154" t="n">
         <v>-21</v>
       </c>
-      <c r="O154" s="12" t="inlineStr">
+      <c r="P154" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9402,34 +10219,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F155" t="n">
+      <c r="F155" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
         <v>322</v>
       </c>
-      <c r="G155" t="n">
+      <c r="H155" t="n">
         <v>291</v>
       </c>
-      <c r="H155" t="n">
+      <c r="I155" t="n">
         <v>84</v>
       </c>
-      <c r="I155" t="n">
+      <c r="J155" t="n">
         <v>63</v>
       </c>
-      <c r="J155" t="n">
+      <c r="K155" t="n">
         <v>41</v>
       </c>
-      <c r="K155" t="n">
+      <c r="L155" t="n">
         <v>3.4</v>
       </c>
-      <c r="L155" t="n">
+      <c r="M155" t="n">
         <v>1.1</v>
       </c>
-      <c r="M155" t="n">
+      <c r="N155" t="n">
         <v>3.4</v>
       </c>
-      <c r="N155" t="n">
+      <c r="O155" t="n">
         <v>-68</v>
       </c>
-      <c r="O155" s="14" t="inlineStr">
+      <c r="P155" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -9459,34 +10281,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F156" t="n">
+      <c r="F156" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
         <v>305</v>
       </c>
-      <c r="G156" t="n">
+      <c r="H156" t="n">
         <v>267</v>
       </c>
-      <c r="H156" t="n">
+      <c r="I156" t="n">
         <v>81</v>
       </c>
-      <c r="I156" t="n">
+      <c r="J156" t="n">
         <v>53</v>
       </c>
-      <c r="J156" t="n">
+      <c r="K156" t="n">
         <v>30</v>
       </c>
-      <c r="K156" t="n">
+      <c r="L156" t="n">
         <v>4.2</v>
       </c>
-      <c r="L156" t="n">
+      <c r="M156" t="n">
         <v>1.2</v>
       </c>
-      <c r="M156" t="n">
+      <c r="N156" t="n">
         <v>4.2</v>
       </c>
-      <c r="N156" t="n">
+      <c r="O156" t="n">
         <v>-71</v>
       </c>
-      <c r="O156" s="14" t="inlineStr">
+      <c r="P156" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -9516,41 +10343,46 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F157" t="n">
+      <c r="F157" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
         <v>423</v>
       </c>
-      <c r="G157" t="n">
+      <c r="H157" t="n">
         <v>325</v>
       </c>
-      <c r="H157" t="n">
+      <c r="I157" t="n">
         <v>94</v>
       </c>
-      <c r="I157" t="n">
+      <c r="J157" t="n">
         <v>76</v>
       </c>
-      <c r="J157" t="n">
+      <c r="K157" t="n">
         <v>55</v>
       </c>
-      <c r="K157" t="n">
+      <c r="L157" t="n">
         <v>7.2</v>
       </c>
-      <c r="L157" t="n">
+      <c r="M157" t="n">
         <v>2.1</v>
       </c>
-      <c r="M157" t="n">
+      <c r="N157" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="N157" t="n">
+      <c r="O157" t="n">
         <v>-71</v>
       </c>
-      <c r="O157" s="12" t="inlineStr">
+      <c r="P157" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="13" t="inlineStr">
+      <c r="A158" s="15" t="inlineStr">
         <is>
           <t>LスマスロモンキーターンＶ</t>
         </is>
@@ -9573,34 +10405,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F158" t="n">
+      <c r="F158" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
         <v>338</v>
       </c>
-      <c r="G158" t="n">
+      <c r="H158" t="n">
         <v>309</v>
       </c>
-      <c r="H158" t="n">
+      <c r="I158" t="n">
         <v>95</v>
       </c>
-      <c r="I158" t="n">
+      <c r="J158" t="n">
         <v>83</v>
       </c>
-      <c r="J158" t="n">
+      <c r="K158" t="n">
         <v>77</v>
       </c>
-      <c r="K158" t="n">
+      <c r="L158" t="n">
         <v>4.2</v>
       </c>
-      <c r="L158" t="n">
+      <c r="M158" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M158" t="n">
+      <c r="N158" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="N158" t="n">
+      <c r="O158" t="n">
         <v>95</v>
       </c>
-      <c r="O158" s="12" t="inlineStr">
+      <c r="P158" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9630,34 +10467,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F159" t="n">
+      <c r="F159" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
         <v>295</v>
       </c>
-      <c r="G159" t="n">
+      <c r="H159" t="n">
         <v>243</v>
       </c>
-      <c r="H159" t="n">
+      <c r="I159" t="n">
         <v>86</v>
       </c>
-      <c r="I159" t="n">
+      <c r="J159" t="n">
         <v>71</v>
       </c>
-      <c r="J159" t="n">
+      <c r="K159" t="n">
         <v>51</v>
       </c>
-      <c r="K159" t="n">
+      <c r="L159" t="n">
         <v>2</v>
       </c>
-      <c r="L159" t="n">
+      <c r="M159" t="n">
         <v>1.3</v>
       </c>
-      <c r="M159" t="n">
+      <c r="N159" t="n">
         <v>2.1</v>
       </c>
-      <c r="N159" t="n">
+      <c r="O159" t="n">
         <v>-35</v>
       </c>
-      <c r="O159" s="12" t="inlineStr">
+      <c r="P159" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9687,34 +10529,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F160" t="n">
+      <c r="F160" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
         <v>298</v>
       </c>
-      <c r="G160" t="n">
+      <c r="H160" t="n">
         <v>255</v>
       </c>
-      <c r="H160" t="n">
+      <c r="I160" t="n">
         <v>89</v>
       </c>
-      <c r="I160" t="n">
+      <c r="J160" t="n">
         <v>68</v>
       </c>
-      <c r="J160" t="n">
+      <c r="K160" t="n">
         <v>47</v>
       </c>
-      <c r="K160" t="n">
+      <c r="L160" t="n">
         <v>1.9</v>
       </c>
-      <c r="L160" t="n">
+      <c r="M160" t="n">
         <v>1.1</v>
       </c>
-      <c r="M160" t="n">
+      <c r="N160" t="n">
         <v>1.9</v>
       </c>
-      <c r="N160" t="n">
+      <c r="O160" t="n">
         <v>-42</v>
       </c>
-      <c r="O160" s="12" t="inlineStr">
+      <c r="P160" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9744,34 +10591,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F161" t="n">
+      <c r="F161" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
         <v>364</v>
       </c>
-      <c r="G161" t="n">
+      <c r="H161" t="n">
         <v>328</v>
       </c>
-      <c r="H161" t="n">
+      <c r="I161" t="n">
         <v>94</v>
       </c>
-      <c r="I161" t="n">
+      <c r="J161" t="n">
         <v>81</v>
       </c>
-      <c r="J161" t="n">
+      <c r="K161" t="n">
         <v>61</v>
       </c>
-      <c r="K161" t="n">
+      <c r="L161" t="n">
         <v>2</v>
       </c>
-      <c r="L161" t="n">
+      <c r="M161" t="n">
         <v>1.2</v>
       </c>
-      <c r="M161" t="n">
+      <c r="N161" t="n">
         <v>2.5</v>
       </c>
-      <c r="N161" t="n">
+      <c r="O161" t="n">
         <v>-40</v>
       </c>
-      <c r="O161" s="12" t="inlineStr">
+      <c r="P161" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9793,7 +10645,7 @@
           <t>36週で終了</t>
         </is>
       </c>
-      <c r="D162" t="n">
+      <c r="D162" s="17" t="n">
         <v>36</v>
       </c>
       <c r="E162" t="inlineStr">
@@ -9801,34 +10653,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F162" t="n">
+      <c r="F162" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
         <v>217</v>
       </c>
-      <c r="G162" t="n">
+      <c r="H162" t="n">
         <v>124</v>
       </c>
-      <c r="H162" t="n">
+      <c r="I162" t="n">
         <v>60</v>
       </c>
-      <c r="I162" t="n">
+      <c r="J162" t="n">
         <v>33</v>
       </c>
-      <c r="J162" t="n">
+      <c r="K162" t="n">
         <v>18</v>
       </c>
-      <c r="K162" t="n">
+      <c r="L162" t="n">
         <v>5</v>
       </c>
-      <c r="L162" t="n">
+      <c r="M162" t="n">
         <v>1.3</v>
       </c>
-      <c r="M162" t="n">
+      <c r="N162" t="n">
         <v>5</v>
       </c>
-      <c r="N162" t="n">
+      <c r="O162" t="n">
         <v>-74</v>
       </c>
-      <c r="O162" s="11" t="inlineStr">
+      <c r="P162" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -9850,7 +10707,7 @@
           <t>23週で終了</t>
         </is>
       </c>
-      <c r="D163" t="n">
+      <c r="D163" s="17" t="n">
         <v>23</v>
       </c>
       <c r="E163" t="inlineStr">
@@ -9858,34 +10715,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F163" t="n">
+      <c r="F163" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
         <v>212</v>
       </c>
-      <c r="G163" t="n">
+      <c r="H163" t="n">
         <v>160</v>
       </c>
-      <c r="H163" t="n">
+      <c r="I163" t="n">
         <v>68</v>
       </c>
-      <c r="I163" t="n">
+      <c r="J163" t="n">
         <v>35</v>
       </c>
-      <c r="J163" t="n">
+      <c r="K163" t="n">
         <v>25</v>
       </c>
-      <c r="K163" t="n">
+      <c r="L163" t="n">
         <v>3.2</v>
       </c>
-      <c r="L163" t="n">
+      <c r="M163" t="n">
         <v>1.3</v>
       </c>
-      <c r="M163" t="n">
+      <c r="N163" t="n">
         <v>3.2</v>
       </c>
-      <c r="N163" t="n">
+      <c r="O163" t="n">
         <v>-59</v>
       </c>
-      <c r="O163" s="11" t="inlineStr">
+      <c r="P163" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -9915,34 +10777,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F164" t="n">
+      <c r="F164" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
         <v>308</v>
       </c>
-      <c r="G164" t="n">
+      <c r="H164" t="n">
         <v>317</v>
       </c>
-      <c r="H164" t="n">
+      <c r="I164" t="n">
         <v>89</v>
       </c>
-      <c r="I164" t="n">
+      <c r="J164" t="n">
         <v>67</v>
       </c>
-      <c r="J164" t="n">
+      <c r="K164" t="n">
         <v>48</v>
       </c>
-      <c r="K164" t="n">
+      <c r="L164" t="n">
         <v>3.6</v>
       </c>
-      <c r="L164" t="n">
+      <c r="M164" t="n">
         <v>1.2</v>
       </c>
-      <c r="M164" t="n">
+      <c r="N164" t="n">
         <v>3.6</v>
       </c>
-      <c r="N164" t="n">
+      <c r="O164" t="n">
         <v>-67</v>
       </c>
-      <c r="O164" s="12" t="inlineStr">
+      <c r="P164" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9964,7 +10831,7 @@
           <t>50週で終了</t>
         </is>
       </c>
-      <c r="D165" t="n">
+      <c r="D165" s="17" t="n">
         <v>50</v>
       </c>
       <c r="E165" t="inlineStr">
@@ -9972,34 +10839,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F165" t="n">
+      <c r="F165" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
         <v>222</v>
       </c>
-      <c r="G165" t="n">
+      <c r="H165" t="n">
         <v>126</v>
       </c>
-      <c r="H165" t="n">
+      <c r="I165" t="n">
         <v>49</v>
       </c>
-      <c r="I165" t="n">
+      <c r="J165" t="n">
         <v>22</v>
       </c>
-      <c r="J165" t="n">
+      <c r="K165" t="n">
         <v>16</v>
       </c>
-      <c r="K165" t="n">
+      <c r="L165" t="n">
         <v>6.2</v>
       </c>
-      <c r="L165" t="n">
+      <c r="M165" t="n">
         <v>1.5</v>
       </c>
-      <c r="M165" t="n">
+      <c r="N165" t="n">
         <v>6.2</v>
       </c>
-      <c r="N165" t="n">
+      <c r="O165" t="n">
         <v>-76</v>
       </c>
-      <c r="O165" s="11" t="inlineStr">
+      <c r="P165" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -10029,34 +10901,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F166" t="n">
+      <c r="F166" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
         <v>214</v>
       </c>
-      <c r="G166" t="n">
+      <c r="H166" t="n">
         <v>176</v>
-      </c>
-      <c r="H166" t="n">
-        <v>71</v>
       </c>
       <c r="I166" t="n">
         <v>71</v>
       </c>
       <c r="J166" t="n">
+        <v>71</v>
+      </c>
+      <c r="K166" t="n">
         <v>42</v>
       </c>
-      <c r="K166" t="n">
+      <c r="L166" t="n">
         <v>2.3</v>
       </c>
-      <c r="L166" t="n">
+      <c r="M166" t="n">
         <v>1.2</v>
       </c>
-      <c r="M166" t="n">
+      <c r="N166" t="n">
         <v>2.3</v>
       </c>
-      <c r="N166" t="n">
+      <c r="O166" t="n">
         <v>-48</v>
       </c>
-      <c r="O166" s="12" t="inlineStr">
+      <c r="P166" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10078,7 +10955,7 @@
           <t>57週で終了</t>
         </is>
       </c>
-      <c r="D167" t="n">
+      <c r="D167" s="17" t="n">
         <v>57</v>
       </c>
       <c r="E167" t="inlineStr">
@@ -10086,34 +10963,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F167" t="n">
+      <c r="F167" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
         <v>242</v>
       </c>
-      <c r="G167" t="n">
+      <c r="H167" t="n">
         <v>211</v>
       </c>
-      <c r="H167" t="n">
+      <c r="I167" t="n">
         <v>75</v>
       </c>
-      <c r="I167" t="n">
+      <c r="J167" t="n">
         <v>47</v>
       </c>
-      <c r="J167" t="n">
+      <c r="K167" t="n">
         <v>31</v>
       </c>
-      <c r="K167" t="n">
+      <c r="L167" t="n">
         <v>3</v>
       </c>
-      <c r="L167" t="n">
+      <c r="M167" t="n">
         <v>1.2</v>
       </c>
-      <c r="M167" t="n">
+      <c r="N167" t="n">
         <v>3</v>
       </c>
-      <c r="N167" t="n">
+      <c r="O167" t="n">
         <v>-60</v>
       </c>
-      <c r="O167" s="11" t="inlineStr">
+      <c r="P167" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -10135,7 +11017,7 @@
           <t>36週で終了</t>
         </is>
       </c>
-      <c r="D168" t="n">
+      <c r="D168" s="17" t="n">
         <v>36</v>
       </c>
       <c r="E168" t="inlineStr">
@@ -10143,34 +11025,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F168" t="n">
+      <c r="F168" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
         <v>191</v>
       </c>
-      <c r="G168" t="n">
+      <c r="H168" t="n">
         <v>102</v>
       </c>
-      <c r="H168" t="n">
+      <c r="I168" t="n">
         <v>53</v>
       </c>
-      <c r="I168" t="n">
+      <c r="J168" t="n">
         <v>23</v>
       </c>
-      <c r="J168" t="n">
+      <c r="K168" t="n">
         <v>12</v>
       </c>
-      <c r="K168" t="n">
+      <c r="L168" t="n">
         <v>4.7</v>
       </c>
-      <c r="L168" t="n">
+      <c r="M168" t="n">
         <v>1.4</v>
       </c>
-      <c r="M168" t="n">
+      <c r="N168" t="n">
         <v>4.7</v>
       </c>
-      <c r="N168" t="n">
+      <c r="O168" t="n">
         <v>-70</v>
       </c>
-      <c r="O168" s="11" t="inlineStr">
+      <c r="P168" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -10200,34 +11087,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F169" t="n">
+      <c r="F169" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
         <v>281</v>
       </c>
-      <c r="G169" t="n">
+      <c r="H169" t="n">
         <v>246</v>
       </c>
-      <c r="H169" t="n">
+      <c r="I169" t="n">
         <v>87</v>
       </c>
-      <c r="I169" t="n">
+      <c r="J169" t="n">
         <v>65</v>
       </c>
-      <c r="J169" t="n">
+      <c r="K169" t="n">
         <v>41</v>
       </c>
-      <c r="K169" t="n">
+      <c r="L169" t="n">
         <v>3</v>
       </c>
-      <c r="L169" t="n">
+      <c r="M169" t="n">
         <v>1.1</v>
       </c>
-      <c r="M169" t="n">
+      <c r="N169" t="n">
         <v>3</v>
       </c>
-      <c r="N169" t="n">
+      <c r="O169" t="n">
         <v>-63</v>
       </c>
-      <c r="O169" s="14" t="inlineStr">
+      <c r="P169" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -10257,34 +11149,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F170" t="n">
+      <c r="F170" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
         <v>211</v>
       </c>
-      <c r="G170" t="n">
+      <c r="H170" t="n">
         <v>190</v>
       </c>
-      <c r="H170" t="n">
+      <c r="I170" t="n">
         <v>79</v>
       </c>
-      <c r="I170" t="n">
+      <c r="J170" t="n">
         <v>54</v>
       </c>
-      <c r="J170" t="n">
+      <c r="K170" t="n">
         <v>37</v>
       </c>
-      <c r="K170" t="n">
+      <c r="L170" t="n">
         <v>1.9</v>
       </c>
-      <c r="L170" t="n">
+      <c r="M170" t="n">
         <v>1.1</v>
       </c>
-      <c r="M170" t="n">
+      <c r="N170" t="n">
         <v>2</v>
       </c>
-      <c r="N170" t="n">
+      <c r="O170" t="n">
         <v>-42</v>
       </c>
-      <c r="O170" s="14" t="inlineStr">
+      <c r="P170" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -10314,34 +11211,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F171" t="n">
+      <c r="F171" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
         <v>223</v>
       </c>
-      <c r="G171" t="n">
+      <c r="H171" t="n">
         <v>216</v>
       </c>
-      <c r="H171" t="n">
+      <c r="I171" t="n">
         <v>85</v>
       </c>
-      <c r="I171" t="n">
+      <c r="J171" t="n">
         <v>58</v>
       </c>
-      <c r="J171" t="n">
+      <c r="K171" t="n">
         <v>45</v>
       </c>
-      <c r="K171" t="n">
+      <c r="L171" t="n">
         <v>2.1</v>
       </c>
-      <c r="L171" t="n">
+      <c r="M171" t="n">
         <v>1.2</v>
       </c>
-      <c r="M171" t="n">
+      <c r="N171" t="n">
         <v>2.1</v>
       </c>
-      <c r="N171" t="n">
+      <c r="O171" t="n">
         <v>-43</v>
       </c>
-      <c r="O171" s="14" t="inlineStr">
+      <c r="P171" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -10371,41 +11273,46 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F172" t="n">
+      <c r="F172" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
         <v>231</v>
       </c>
-      <c r="G172" t="n">
+      <c r="H172" t="n">
         <v>217</v>
       </c>
-      <c r="H172" t="n">
+      <c r="I172" t="n">
         <v>83</v>
       </c>
-      <c r="I172" t="n">
+      <c r="J172" t="n">
         <v>63</v>
       </c>
-      <c r="J172" t="n">
+      <c r="K172" t="n">
         <v>36</v>
       </c>
-      <c r="K172" t="n">
+      <c r="L172" t="n">
         <v>2.4</v>
       </c>
-      <c r="L172" t="n">
+      <c r="M172" t="n">
         <v>1.1</v>
       </c>
-      <c r="M172" t="n">
+      <c r="N172" t="n">
         <v>2.4</v>
       </c>
-      <c r="N172" t="n">
+      <c r="O172" t="n">
         <v>-54</v>
       </c>
-      <c r="O172" s="14" t="inlineStr">
+      <c r="P172" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="13" t="inlineStr">
+      <c r="A173" s="15" t="inlineStr">
         <is>
           <t>L戦国乙女４戦乱に閃く炯眼の軍師</t>
         </is>
@@ -10428,34 +11335,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F173" t="n">
+      <c r="F173" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
         <v>285</v>
       </c>
-      <c r="G173" t="n">
+      <c r="H173" t="n">
         <v>309</v>
       </c>
-      <c r="H173" t="n">
+      <c r="I173" t="n">
         <v>96</v>
       </c>
-      <c r="I173" t="n">
+      <c r="J173" t="n">
         <v>89</v>
       </c>
-      <c r="J173" t="n">
+      <c r="K173" t="n">
         <v>77</v>
       </c>
-      <c r="K173" t="n">
+      <c r="L173" t="n">
         <v>3.3</v>
       </c>
-      <c r="L173" t="n">
+      <c r="M173" t="n">
         <v>2.5</v>
       </c>
-      <c r="M173" t="n">
+      <c r="N173" t="n">
         <v>5</v>
       </c>
-      <c r="N173" t="n">
+      <c r="O173" t="n">
         <v>-24</v>
       </c>
-      <c r="O173" s="12" t="inlineStr">
+      <c r="P173" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10485,34 +11397,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F174" t="n">
+      <c r="F174" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
         <v>158</v>
       </c>
-      <c r="G174" t="n">
+      <c r="H174" t="n">
         <v>169</v>
       </c>
-      <c r="H174" t="n">
+      <c r="I174" t="n">
         <v>94</v>
       </c>
-      <c r="I174" t="n">
+      <c r="J174" t="n">
         <v>76</v>
       </c>
-      <c r="J174" t="n">
+      <c r="K174" t="n">
         <v>56</v>
       </c>
-      <c r="K174" t="n">
+      <c r="L174" t="n">
         <v>3.6</v>
       </c>
-      <c r="L174" t="n">
+      <c r="M174" t="n">
         <v>1.3</v>
       </c>
-      <c r="M174" t="n">
+      <c r="N174" t="n">
         <v>3.6</v>
       </c>
-      <c r="N174" t="n">
+      <c r="O174" t="n">
         <v>-64</v>
       </c>
-      <c r="O174" s="12" t="inlineStr">
+      <c r="P174" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10534,7 +11451,7 @@
           <t>44週で終了</t>
         </is>
       </c>
-      <c r="D175" t="n">
+      <c r="D175" s="17" t="n">
         <v>44</v>
       </c>
       <c r="E175" t="inlineStr">
@@ -10542,34 +11459,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F175" t="n">
+      <c r="F175" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
         <v>129</v>
       </c>
-      <c r="G175" t="n">
+      <c r="H175" t="n">
         <v>105</v>
       </c>
-      <c r="H175" t="n">
+      <c r="I175" t="n">
         <v>71</v>
       </c>
-      <c r="I175" t="n">
+      <c r="J175" t="n">
         <v>34</v>
       </c>
-      <c r="J175" t="n">
+      <c r="K175" t="n">
         <v>19</v>
       </c>
-      <c r="K175" t="n">
+      <c r="L175" t="n">
         <v>4.1</v>
       </c>
-      <c r="L175" t="n">
+      <c r="M175" t="n">
         <v>1.4</v>
       </c>
-      <c r="M175" t="n">
+      <c r="N175" t="n">
         <v>4.1</v>
       </c>
-      <c r="N175" t="n">
+      <c r="O175" t="n">
         <v>-66</v>
       </c>
-      <c r="O175" s="11" t="inlineStr">
+      <c r="P175" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -10599,34 +11521,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F176" t="n">
+      <c r="F176" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
         <v>165</v>
       </c>
-      <c r="G176" t="n">
+      <c r="H176" t="n">
         <v>174</v>
       </c>
-      <c r="H176" t="n">
+      <c r="I176" t="n">
         <v>93</v>
       </c>
-      <c r="I176" t="n">
+      <c r="J176" t="n">
         <v>69</v>
       </c>
-      <c r="J176" t="n">
+      <c r="K176" t="n">
         <v>46</v>
       </c>
-      <c r="K176" t="n">
+      <c r="L176" t="n">
         <v>2</v>
       </c>
-      <c r="L176" t="n">
+      <c r="M176" t="n">
         <v>1.1</v>
       </c>
-      <c r="M176" t="n">
+      <c r="N176" t="n">
         <v>2</v>
       </c>
-      <c r="N176" t="n">
+      <c r="O176" t="n">
         <v>-45</v>
       </c>
-      <c r="O176" s="12" t="inlineStr">
+      <c r="P176" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10656,34 +11583,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F177" t="n">
+      <c r="F177" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
         <v>168</v>
       </c>
-      <c r="G177" t="n">
+      <c r="H177" t="n">
         <v>177</v>
       </c>
-      <c r="H177" t="n">
+      <c r="I177" t="n">
         <v>93</v>
       </c>
-      <c r="I177" t="n">
+      <c r="J177" t="n">
         <v>66</v>
       </c>
-      <c r="J177" t="n">
+      <c r="K177" t="n">
         <v>39</v>
       </c>
-      <c r="K177" t="n">
+      <c r="L177" t="n">
         <v>2.1</v>
       </c>
-      <c r="L177" t="n">
+      <c r="M177" t="n">
         <v>1.1</v>
       </c>
-      <c r="M177" t="n">
+      <c r="N177" t="n">
         <v>2.1</v>
       </c>
-      <c r="N177" t="n">
+      <c r="O177" t="n">
         <v>-48</v>
       </c>
-      <c r="O177" s="12" t="inlineStr">
+      <c r="P177" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10713,34 +11645,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F178" t="n">
+      <c r="F178" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
         <v>262</v>
       </c>
-      <c r="G178" t="n">
+      <c r="H178" t="n">
         <v>210</v>
       </c>
-      <c r="H178" t="n">
+      <c r="I178" t="n">
         <v>77</v>
       </c>
-      <c r="I178" t="n">
+      <c r="J178" t="n">
         <v>52</v>
       </c>
-      <c r="J178" t="n">
+      <c r="K178" t="n">
         <v>23</v>
       </c>
-      <c r="K178" t="n">
+      <c r="L178" t="n">
         <v>7.6</v>
       </c>
-      <c r="L178" t="n">
+      <c r="M178" t="n">
         <v>1.3</v>
       </c>
-      <c r="M178" t="n">
+      <c r="N178" t="n">
         <v>7.6</v>
       </c>
-      <c r="N178" t="n">
+      <c r="O178" t="n">
         <v>-83</v>
       </c>
-      <c r="O178" s="14" t="inlineStr">
+      <c r="P178" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -10770,34 +11707,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F179" t="n">
+      <c r="F179" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
         <v>209</v>
       </c>
-      <c r="G179" t="n">
+      <c r="H179" t="n">
         <v>214</v>
       </c>
-      <c r="H179" t="n">
+      <c r="I179" t="n">
         <v>88</v>
       </c>
-      <c r="I179" t="n">
+      <c r="J179" t="n">
         <v>67</v>
       </c>
-      <c r="J179" t="n">
+      <c r="K179" t="n">
         <v>56</v>
       </c>
-      <c r="K179" t="n">
+      <c r="L179" t="n">
         <v>4.1</v>
       </c>
-      <c r="L179" t="n">
+      <c r="M179" t="n">
         <v>3.5</v>
       </c>
-      <c r="M179" t="n">
+      <c r="N179" t="n">
         <v>8</v>
       </c>
-      <c r="N179" t="n">
+      <c r="O179" t="n">
         <v>-15</v>
       </c>
-      <c r="O179" s="12" t="inlineStr">
+      <c r="P179" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10827,34 +11769,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F180" t="n">
+      <c r="F180" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
         <v>149</v>
       </c>
-      <c r="G180" t="n">
+      <c r="H180" t="n">
         <v>148</v>
       </c>
-      <c r="H180" t="n">
+      <c r="I180" t="n">
         <v>88</v>
       </c>
-      <c r="I180" t="n">
+      <c r="J180" t="n">
         <v>70</v>
       </c>
-      <c r="J180" t="n">
+      <c r="K180" t="n">
         <v>41</v>
       </c>
-      <c r="K180" t="n">
+      <c r="L180" t="n">
         <v>4.3</v>
       </c>
-      <c r="L180" t="n">
+      <c r="M180" t="n">
         <v>1.3</v>
       </c>
-      <c r="M180" t="n">
+      <c r="N180" t="n">
         <v>4.4</v>
       </c>
-      <c r="N180" t="n">
+      <c r="O180" t="n">
         <v>-70</v>
       </c>
-      <c r="O180" s="12" t="inlineStr">
+      <c r="P180" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10876,7 +11823,7 @@
           <t>60週で終了</t>
         </is>
       </c>
-      <c r="D181" t="n">
+      <c r="D181" s="17" t="n">
         <v>60</v>
       </c>
       <c r="E181" t="inlineStr">
@@ -10884,34 +11831,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F181" t="n">
+      <c r="F181" s="13" t="inlineStr">
+        <is>
+          <t>実質死亡(設置のみ)</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
         <v>130</v>
       </c>
-      <c r="G181" t="n">
+      <c r="H181" t="n">
         <v>101</v>
       </c>
-      <c r="H181" t="n">
+      <c r="I181" t="n">
         <v>69</v>
       </c>
-      <c r="I181" t="n">
+      <c r="J181" t="n">
         <v>46</v>
       </c>
-      <c r="J181" t="n">
+      <c r="K181" t="n">
         <v>23</v>
       </c>
-      <c r="K181" t="n">
+      <c r="L181" t="n">
         <v>4.2</v>
       </c>
-      <c r="L181" t="n">
+      <c r="M181" t="n">
         <v>1.3</v>
       </c>
-      <c r="M181" t="n">
+      <c r="N181" t="n">
         <v>4.2</v>
       </c>
-      <c r="N181" t="n">
+      <c r="O181" t="n">
         <v>-69</v>
       </c>
-      <c r="O181" s="11" t="inlineStr">
+      <c r="P181" s="13" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -10941,34 +11893,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F182" t="n">
+      <c r="F182" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
         <v>194</v>
       </c>
-      <c r="G182" t="n">
+      <c r="H182" t="n">
         <v>183</v>
       </c>
-      <c r="H182" t="n">
+      <c r="I182" t="n">
         <v>88</v>
       </c>
-      <c r="I182" t="n">
+      <c r="J182" t="n">
         <v>62</v>
       </c>
-      <c r="J182" t="n">
+      <c r="K182" t="n">
         <v>49</v>
       </c>
-      <c r="K182" t="n">
+      <c r="L182" t="n">
         <v>5.1</v>
       </c>
-      <c r="L182" t="n">
+      <c r="M182" t="n">
         <v>1.5</v>
       </c>
-      <c r="M182" t="n">
+      <c r="N182" t="n">
         <v>5.1</v>
       </c>
-      <c r="N182" t="n">
+      <c r="O182" t="n">
         <v>-71</v>
       </c>
-      <c r="O182" s="14" t="inlineStr">
+      <c r="P182" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -10998,34 +11955,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F183" t="n">
+      <c r="F183" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
         <v>274</v>
       </c>
-      <c r="G183" t="n">
+      <c r="H183" t="n">
         <v>151</v>
       </c>
-      <c r="H183" t="n">
+      <c r="I183" t="n">
         <v>87</v>
       </c>
-      <c r="I183" t="n">
+      <c r="J183" t="n">
         <v>72</v>
       </c>
-      <c r="J183" t="n">
+      <c r="K183" t="n">
         <v>62</v>
       </c>
-      <c r="K183" t="n">
+      <c r="L183" t="n">
         <v>4</v>
       </c>
-      <c r="L183" t="n">
+      <c r="M183" t="n">
         <v>1.3</v>
       </c>
-      <c r="M183" t="n">
+      <c r="N183" t="n">
         <v>4.1</v>
       </c>
-      <c r="N183" t="n">
+      <c r="O183" t="n">
         <v>-68</v>
       </c>
-      <c r="O183" s="12" t="inlineStr">
+      <c r="P183" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -11055,41 +12017,46 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F184" t="n">
+      <c r="F184" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
         <v>235</v>
       </c>
-      <c r="G184" t="n">
+      <c r="H184" t="n">
         <v>221</v>
       </c>
-      <c r="H184" t="n">
+      <c r="I184" t="n">
         <v>94</v>
       </c>
-      <c r="I184" t="n">
+      <c r="J184" t="n">
         <v>65</v>
       </c>
-      <c r="J184" t="n">
+      <c r="K184" t="n">
         <v>52</v>
       </c>
-      <c r="K184" t="n">
+      <c r="L184" t="n">
         <v>5.3</v>
       </c>
-      <c r="L184" t="n">
+      <c r="M184" t="n">
         <v>1.6</v>
       </c>
-      <c r="M184" t="n">
+      <c r="N184" t="n">
         <v>5.3</v>
       </c>
-      <c r="N184" t="n">
+      <c r="O184" t="n">
         <v>-70</v>
       </c>
-      <c r="O184" s="14" t="inlineStr">
+      <c r="P184" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="13" t="inlineStr">
+      <c r="A185" s="15" t="inlineStr">
         <is>
           <t>Lスマスロ北斗の拳</t>
         </is>
@@ -11112,34 +12079,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F185" t="n">
+      <c r="F185" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
         <v>283</v>
       </c>
-      <c r="G185" t="n">
+      <c r="H185" t="n">
         <v>321</v>
       </c>
-      <c r="H185" t="n">
+      <c r="I185" t="n">
         <v>99</v>
       </c>
-      <c r="I185" t="n">
+      <c r="J185" t="n">
         <v>89</v>
       </c>
-      <c r="J185" t="n">
+      <c r="K185" t="n">
         <v>73</v>
       </c>
-      <c r="K185" t="n">
+      <c r="L185" t="n">
         <v>8.9</v>
       </c>
-      <c r="L185" t="n">
+      <c r="M185" t="n">
         <v>7.5</v>
       </c>
-      <c r="M185" t="n">
+      <c r="N185" t="n">
         <v>18.3</v>
       </c>
-      <c r="N185" t="n">
+      <c r="O185" t="n">
         <v>-16</v>
       </c>
-      <c r="O185" s="12" t="inlineStr">
+      <c r="P185" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -11169,34 +12141,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F186" t="n">
+      <c r="F186" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
         <v>117</v>
       </c>
-      <c r="G186" t="n">
+      <c r="H186" t="n">
         <v>107</v>
       </c>
-      <c r="H186" t="n">
+      <c r="I186" t="n">
         <v>103</v>
       </c>
-      <c r="I186" t="n">
+      <c r="J186" t="n">
         <v>78</v>
       </c>
-      <c r="J186" t="n">
+      <c r="K186" t="n">
         <v>60</v>
       </c>
-      <c r="K186" t="n">
+      <c r="L186" t="n">
         <v>7.1</v>
       </c>
-      <c r="L186" t="n">
+      <c r="M186" t="n">
         <v>1.4</v>
       </c>
-      <c r="M186" t="n">
+      <c r="N186" t="n">
         <v>10.6</v>
       </c>
-      <c r="N186" t="n">
+      <c r="O186" t="n">
         <v>-80</v>
       </c>
-      <c r="O186" s="12" t="inlineStr">
+      <c r="P186" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -11226,34 +12203,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F187" t="n">
-        <v>21</v>
+      <c r="F187" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
       </c>
       <c r="G187" t="n">
         <v>21</v>
       </c>
       <c r="H187" t="n">
+        <v>21</v>
+      </c>
+      <c r="I187" t="n">
         <v>110</v>
       </c>
-      <c r="I187" t="n">
+      <c r="J187" t="n">
         <v>80</v>
       </c>
-      <c r="J187" t="n">
+      <c r="K187" t="n">
         <v>55</v>
       </c>
-      <c r="K187" t="n">
+      <c r="L187" t="n">
         <v>4.1</v>
       </c>
-      <c r="L187" t="n">
+      <c r="M187" t="n">
         <v>1.6</v>
       </c>
-      <c r="M187" t="n">
+      <c r="N187" t="n">
         <v>4.1</v>
       </c>
-      <c r="N187" t="n">
+      <c r="O187" t="n">
         <v>-61</v>
       </c>
-      <c r="O187" s="12" t="inlineStr">
+      <c r="P187" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -11283,34 +12265,39 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="F188" t="n">
+      <c r="F188" s="16" t="inlineStr">
+        <is>
+          <t>微妙</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
         <v>73</v>
       </c>
-      <c r="G188" t="n">
+      <c r="H188" t="n">
         <v>68</v>
       </c>
-      <c r="H188" t="n">
+      <c r="I188" t="n">
         <v>105</v>
       </c>
-      <c r="I188" t="n">
+      <c r="J188" t="n">
         <v>63</v>
       </c>
-      <c r="J188" t="n">
+      <c r="K188" t="n">
         <v>51</v>
       </c>
-      <c r="K188" t="n">
+      <c r="L188" t="n">
         <v>5.7</v>
       </c>
-      <c r="L188" t="n">
+      <c r="M188" t="n">
         <v>1.3</v>
       </c>
-      <c r="M188" t="n">
+      <c r="N188" t="n">
         <v>5.8</v>
       </c>
-      <c r="N188" t="n">
+      <c r="O188" t="n">
         <v>-77</v>
       </c>
-      <c r="O188" s="14" t="inlineStr">
+      <c r="P188" s="16" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -11340,34 +12327,39 @@
           <t>継続中</t>
         </is>
       </c>
-      <c r="F189" t="n">
-        <v>100</v>
+      <c r="F189" s="14" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
       </c>
       <c r="G189" t="n">
         <v>100</v>
       </c>
       <c r="H189" t="n">
+        <v>100</v>
+      </c>
+      <c r="I189" t="n">
         <v>113</v>
       </c>
-      <c r="I189" t="n">
+      <c r="J189" t="n">
         <v>82</v>
       </c>
-      <c r="J189" t="n">
+      <c r="K189" t="n">
         <v>72</v>
       </c>
-      <c r="K189" t="n">
+      <c r="L189" t="n">
         <v>6.4</v>
       </c>
-      <c r="L189" t="n">
+      <c r="M189" t="n">
         <v>3.7</v>
       </c>
-      <c r="M189" t="n">
+      <c r="N189" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="N189" t="n">
+      <c r="O189" t="n">
         <v>-42</v>
       </c>
-      <c r="O189" s="12" t="inlineStr">
+      <c r="P189" s="14" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -11375,7 +12367,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ai収集/分析_新台診断_v0.3.xlsx
+++ b/ai収集/分析_新台診断_v0.3.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,7 +36,7 @@
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="00333333"/>
+      <color rgb="00D03030"/>
       <sz val="11"/>
     </font>
     <font>
@@ -49,17 +49,8 @@
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="00D03030"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <color rgb="00C77B00"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00333333"/>
-      <sz val="12"/>
     </font>
     <font>
       <color rgb="00888888"/>
@@ -133,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -156,14 +147,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -171,7 +156,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -537,16 +522,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="115" customWidth="1" min="1" max="1"/>
+    <col width="118" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>新台診断テーブル ― 指標の説明（2軸: 稼働値×持続率）</t>
+          <t>新台診断テーブル v0.5（稼働貢献週=SIS公式値に修正）</t>
         </is>
       </c>
     </row>
@@ -556,7 +541,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>【考え方】台数やIPは“入口”でしかない。台の生死は『人気(稼働値)』と『定着(持続率)』の2軸で決まる。2週で仮説→4週/8週で検証。</t>
+          <t>【重大修正 2026-06-29】旧版は週次データの行数を『稼働貢献週』として誤用していた。死に台でも設置されてる限り週次行が残るため大幅に水増しされていた(例:真北斗無双 誤100週→正5週)。</t>
         </is>
       </c>
     </row>
@@ -566,132 +551,55 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>● 稼働値 = アウト ÷ その週の全機種アウト中央値 ×100（人気・絶対需要。市場が来たか）</t>
+          <t>● 稼働貢献週(公式) = sis_machine_stats のSIS公式値。SISが『○週稼動貢献中』と認めた週数(稼働が一定水準を満たした週)。これが正。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   寿命別平均: 長寿 初週335%/2週291% ・ 短命 初週262%/2週190%。判別力1.0前後で有効。</t>
+          <t>● 設置週数 = 週次データに行がある週数(参考)。死に台でも設置され続ければ伸びる。設置週数≠生死。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>● 持続率 = ◯週目アウト ÷ 初週アウト ×100（定着・減衰）</t>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>● 死に台期間 = 設置週数 − 公式稼働貢献週。大きいほど『貢献しなくなった後も惰性で設置された』台。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   初月(4週): 優秀≥66/注意≥50/危険&lt;50（長寿66 vs 短命47）。2週: 長寿86 vs 短命72。判別力最強(1.31)。</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>● 8週持続率 … 中期の定着度。</t>
+          <t>● 稼働値 = アウト ÷ その週の全機種中央値(人気/需要)。持続率 = ◯週目アウト ÷ 初週アウト(定着)。※週次outは『平均IN』=1台平均値で総量ではない。比率なので診断は有効。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>● 台数(初週→現在 / 推移% / ピーク) = 1店あたり平均設置台数の変化。減少=店が撤去。</t>
+          <t>● 初月実態 = 初月持続率による生死(健全≥66/微妙50-66/実質死亡&lt;50/計測中)。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>● 稼働貢献週 / 状況 = SISで稼働を計上した週数と継続中/終了（『◯週継続中』『◯週で終了』）。</t>
+          <t>● 判定 = 4週揃えば持続率4週(優秀≥66/注意≥50/危険&lt;50)、新台は2週暫定(稼働値≥260かつ持続率≥83で優秀)。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>● 初月実態 = 初月持続率による生死判定（健全≥66 / 微妙50-66 / 実質死亡&lt;50 / 計測中）。</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ⚠重要: 稼働貢献週(設置週数) ≠ 稼働の生死。ホールは筐体代が沈むので死に台でも撤去せず数十週設置する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   実例: 真・北斗無双=100週設置でも初月持続率47%(実質死に台) / 劇場版まどか=50週設置/22%。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   → 設置週数が長くても『実質死亡』なら良台ではない。良し悪しは設置週数でなく持続率×稼働値で見る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>【判定ロジック】</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・4週が揃う → 初月持続率で確定: 優秀≥66% / 注意≥50% / 危険&lt;50%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・4週未到達(新台) → 2週で暫定: 稼働値≥260%かつ持続率≥83%=優秀 / 稼働値&lt;190%または持続率&lt;73%=危険 / 中間=注意</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・2週も未到達 → 計測中</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・⚠供給過剰 = 大量導入(台数ピーク≥6)なのに判定が注意/危険（戦国乙女型。台数で初動は出るが客が薄まる）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>【非採用】割数(判別力0.34)・台数初動(0.7)は寿命をほぼ分けず材料にしない。機械割(設定6)は規則で全台115%未満に張付き＝比較情報ゼロ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>【データ源】SIS週次(sis_weekly_data)。生成: scripts/misc/build_diagnosis_table.py。週次更新に追従。</t>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>【データ源】SIS週次(sis_weekly_data)+稼働貢献週(sis_machine_stats)。元はZ:/01_SISデータ/PS/週毎SISデータ一覧_2026.xlsm。生成: scripts/misc/build_diagnosis_table.py。</t>
         </is>
       </c>
     </row>
@@ -711,10 +619,10 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
@@ -728,89 +636,89 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>※直近導入順。判定/しきい値の意味は『説明』シート参照。稼働値=アウト÷週中央値、持続率=◯週÷初週。</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>※直近導入順。稼働貢献週=SIS公式値(これが正)。設置週数は参考。意味は『説明』シート参照。</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>機種</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>初週</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>継続表示</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
-        <is>
-          <t>稼働貢献週</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>状況</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>稼働貢献週(公式)</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>設置週数</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>死に台期間</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>初月実態</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>初週稼働値</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>2週稼働値</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>2週持続率</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>初月持続率(4週)</t>
         </is>
       </c>
-      <c r="K2" s="11" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>8週持続率</t>
         </is>
       </c>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>台数初週</t>
         </is>
       </c>
-      <c r="M2" s="11" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>台数現在</t>
         </is>
       </c>
-      <c r="N2" s="11" t="inlineStr">
+      <c r="N2" s="9" t="inlineStr">
         <is>
           <t>台数ピーク</t>
         </is>
       </c>
-      <c r="O2" s="11" t="inlineStr">
+      <c r="O2" s="9" t="inlineStr">
         <is>
           <t>台数推移%</t>
         </is>
       </c>
-      <c r="P2" s="11" t="inlineStr">
+      <c r="P2" s="9" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
@@ -827,20 +735,16 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2週継続中</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>計測中</t>
         </is>
@@ -866,7 +770,7 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" s="13" t="inlineStr">
+      <c r="P3" s="11" t="inlineStr">
         <is>
           <t>危険(暫定)</t>
         </is>
@@ -883,20 +787,16 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2週継続中</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>計測中</t>
         </is>
@@ -922,14 +822,14 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t>優秀(暫定)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>L戦国乙女5業火を穿つ宿焔の双刃</t>
         </is>
@@ -939,20 +839,16 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2週継続中</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>計測中</t>
         </is>
@@ -978,7 +874,7 @@
       <c r="O5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="14" t="inlineStr">
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t>優秀(暫定)</t>
         </is>
@@ -995,20 +891,16 @@
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4週継続中</t>
-        </is>
+      <c r="C6" t="n">
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -1037,7 +929,7 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="16" t="inlineStr">
+      <c r="P6" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1054,20 +946,16 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>6週継続中</t>
-        </is>
+      <c r="C7" t="n">
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -1096,7 +984,7 @@
       <c r="O7" t="n">
         <v>-3</v>
       </c>
-      <c r="P7" s="16" t="inlineStr">
+      <c r="P7" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1113,20 +1001,16 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>6週継続中</t>
-        </is>
+      <c r="C8" t="n">
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -1155,7 +1039,7 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="14" t="inlineStr">
+      <c r="P8" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1172,20 +1056,16 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>6週継続中</t>
-        </is>
+      <c r="C9" t="n">
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -1214,7 +1094,7 @@
       <c r="O9" t="n">
         <v>-9</v>
       </c>
-      <c r="P9" s="16" t="inlineStr">
+      <c r="P9" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1231,20 +1111,16 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>6週継続中</t>
-        </is>
+      <c r="C10" t="n">
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -1273,7 +1149,7 @@
       <c r="O10" t="n">
         <v>-5</v>
       </c>
-      <c r="P10" s="16" t="inlineStr">
+      <c r="P10" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1290,20 +1166,16 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>9週継続中</t>
-        </is>
+      <c r="C11" t="n">
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -1335,7 +1207,7 @@
       <c r="O11" t="n">
         <v>-7</v>
       </c>
-      <c r="P11" s="14" t="inlineStr">
+      <c r="P11" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1352,20 +1224,16 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>9週継続中</t>
-        </is>
+      <c r="C12" t="n">
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -1397,7 +1265,7 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="P12" s="14" t="inlineStr">
+      <c r="P12" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1414,22 +1282,18 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>9週継続中</t>
-        </is>
+      <c r="C13" t="n">
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1459,7 +1323,7 @@
       <c r="O13" t="n">
         <v>-33</v>
       </c>
-      <c r="P13" s="13" t="inlineStr">
+      <c r="P13" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -1476,20 +1340,16 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>11週継続中</t>
-        </is>
+      <c r="C14" t="n">
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -1521,7 +1381,7 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" s="14" t="inlineStr">
+      <c r="P14" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1538,20 +1398,16 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>11週継続中</t>
-        </is>
+      <c r="C15" t="n">
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -1583,7 +1439,7 @@
       <c r="O15" t="n">
         <v>-18</v>
       </c>
-      <c r="P15" s="16" t="inlineStr">
+      <c r="P15" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1600,20 +1456,16 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>11週継続中</t>
-        </is>
+      <c r="C16" t="n">
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -1645,7 +1497,7 @@
       <c r="O16" t="n">
         <v>-21</v>
       </c>
-      <c r="P16" s="16" t="inlineStr">
+      <c r="P16" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1662,20 +1514,16 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>11週継続中</t>
-        </is>
+      <c r="C17" t="n">
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -1707,7 +1555,7 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="P17" s="14" t="inlineStr">
+      <c r="P17" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1724,20 +1572,16 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>11週継続中</t>
-        </is>
+      <c r="C18" t="n">
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>11</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -1769,7 +1613,7 @@
       <c r="O18" t="n">
         <v>-6</v>
       </c>
-      <c r="P18" s="14" t="inlineStr">
+      <c r="P18" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1786,20 +1630,16 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>16週継続中</t>
-        </is>
+      <c r="C19" t="n">
+        <v>15</v>
       </c>
       <c r="D19" t="n">
         <v>16</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -1831,7 +1671,7 @@
       <c r="O19" t="n">
         <v>-5</v>
       </c>
-      <c r="P19" s="14" t="inlineStr">
+      <c r="P19" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1848,20 +1688,16 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>16週継続中</t>
-        </is>
+      <c r="C20" t="n">
+        <v>15</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -1893,7 +1729,7 @@
       <c r="O20" t="n">
         <v>12</v>
       </c>
-      <c r="P20" s="14" t="inlineStr">
+      <c r="P20" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1910,20 +1746,16 @@
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>20週継続中</t>
-        </is>
+      <c r="C21" t="n">
+        <v>19</v>
       </c>
       <c r="D21" t="n">
         <v>20</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -1955,7 +1787,7 @@
       <c r="O21" t="n">
         <v>14</v>
       </c>
-      <c r="P21" s="14" t="inlineStr">
+      <c r="P21" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -1972,20 +1804,16 @@
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>20週継続中</t>
-        </is>
+      <c r="C22" t="n">
+        <v>5</v>
       </c>
       <c r="D22" t="n">
         <v>20</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="E22" t="n">
+        <v>15</v>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -2017,7 +1845,7 @@
       <c r="O22" t="n">
         <v>-61</v>
       </c>
-      <c r="P22" s="16" t="inlineStr">
+      <c r="P22" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -2034,20 +1862,16 @@
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>20週継続中</t>
-        </is>
+      <c r="C23" t="n">
+        <v>15</v>
       </c>
       <c r="D23" t="n">
         <v>20</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -2079,7 +1903,7 @@
       <c r="O23" t="n">
         <v>-3</v>
       </c>
-      <c r="P23" s="14" t="inlineStr">
+      <c r="P23" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2096,20 +1920,16 @@
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>20週継続中</t>
-        </is>
+      <c r="C24" t="n">
+        <v>19</v>
       </c>
       <c r="D24" t="n">
         <v>20</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -2141,7 +1961,7 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="P24" s="14" t="inlineStr">
+      <c r="P24" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2158,20 +1978,16 @@
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>20週継続中</t>
-        </is>
+      <c r="C25" t="n">
+        <v>19</v>
       </c>
       <c r="D25" t="n">
         <v>20</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -2203,7 +2019,7 @@
       <c r="O25" t="n">
         <v>-2</v>
       </c>
-      <c r="P25" s="14" t="inlineStr">
+      <c r="P25" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2220,20 +2036,16 @@
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>20週継続中</t>
-        </is>
+      <c r="C26" t="n">
+        <v>5</v>
       </c>
       <c r="D26" t="n">
         <v>20</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="E26" t="n">
+        <v>15</v>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -2265,7 +2077,7 @@
       <c r="O26" t="n">
         <v>-45</v>
       </c>
-      <c r="P26" s="16" t="inlineStr">
+      <c r="P26" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -2282,20 +2094,16 @@
           <t>2026-01-05</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>24週継続中</t>
-        </is>
+      <c r="C27" t="n">
+        <v>10</v>
       </c>
       <c r="D27" t="n">
         <v>24</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="E27" t="n">
+        <v>14</v>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -2327,7 +2135,7 @@
       <c r="O27" t="n">
         <v>-45</v>
       </c>
-      <c r="P27" s="14" t="inlineStr">
+      <c r="P27" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2344,20 +2152,16 @@
           <t>2026-01-05</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>24週継続中</t>
-        </is>
+      <c r="C28" t="n">
+        <v>10</v>
       </c>
       <c r="D28" t="n">
         <v>24</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
+      <c r="E28" t="n">
+        <v>14</v>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -2389,7 +2193,7 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="P28" s="14" t="inlineStr">
+      <c r="P28" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2406,20 +2210,16 @@
           <t>2026-01-05</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>24週継続中</t>
-        </is>
+      <c r="C29" t="n">
+        <v>23</v>
       </c>
       <c r="D29" t="n">
         <v>24</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -2451,7 +2251,7 @@
       <c r="O29" t="n">
         <v>-4</v>
       </c>
-      <c r="P29" s="14" t="inlineStr">
+      <c r="P29" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2468,20 +2268,16 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>26週継続中</t>
-        </is>
+      <c r="C30" t="n">
+        <v>14</v>
       </c>
       <c r="D30" t="n">
         <v>26</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
+      <c r="E30" t="n">
+        <v>12</v>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -2513,7 +2309,7 @@
       <c r="O30" t="n">
         <v>-7</v>
       </c>
-      <c r="P30" s="14" t="inlineStr">
+      <c r="P30" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2530,20 +2326,16 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>26週継続中</t>
-        </is>
+      <c r="C31" t="n">
+        <v>5</v>
       </c>
       <c r="D31" t="n">
         <v>26</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="E31" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -2575,7 +2367,7 @@
       <c r="O31" t="n">
         <v>-41</v>
       </c>
-      <c r="P31" s="14" t="inlineStr">
+      <c r="P31" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2592,20 +2384,16 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>26週継続中</t>
-        </is>
+      <c r="C32" t="n">
+        <v>11</v>
       </c>
       <c r="D32" t="n">
         <v>26</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="E32" t="n">
+        <v>15</v>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -2637,7 +2425,7 @@
       <c r="O32" t="n">
         <v>-20</v>
       </c>
-      <c r="P32" s="16" t="inlineStr">
+      <c r="P32" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -2654,20 +2442,16 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>26週継続中</t>
-        </is>
+      <c r="C33" t="n">
+        <v>7</v>
       </c>
       <c r="D33" t="n">
         <v>26</v>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="E33" t="n">
+        <v>19</v>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -2699,7 +2483,7 @@
       <c r="O33" t="n">
         <v>-51</v>
       </c>
-      <c r="P33" s="16" t="inlineStr">
+      <c r="P33" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -2716,20 +2500,16 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>28週継続中</t>
-        </is>
+      <c r="C34" t="n">
+        <v>6</v>
       </c>
       <c r="D34" t="n">
         <v>28</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
+      <c r="E34" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -2761,7 +2541,7 @@
       <c r="O34" t="n">
         <v>-38</v>
       </c>
-      <c r="P34" s="14" t="inlineStr">
+      <c r="P34" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2778,20 +2558,16 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>28週継続中</t>
-        </is>
+      <c r="C35" t="n">
+        <v>9</v>
       </c>
       <c r="D35" t="n">
         <v>28</v>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="E35" t="n">
+        <v>19</v>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -2823,7 +2599,7 @@
       <c r="O35" t="n">
         <v>-25</v>
       </c>
-      <c r="P35" s="14" t="inlineStr">
+      <c r="P35" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2840,20 +2616,16 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>28週継続中</t>
-        </is>
+      <c r="C36" t="n">
+        <v>14</v>
       </c>
       <c r="D36" t="n">
         <v>28</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
+      <c r="E36" t="n">
+        <v>14</v>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -2885,7 +2657,7 @@
       <c r="O36" t="n">
         <v>-8</v>
       </c>
-      <c r="P36" s="14" t="inlineStr">
+      <c r="P36" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2902,20 +2674,16 @@
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>29週継続中</t>
-        </is>
+      <c r="C37" t="n">
+        <v>5</v>
       </c>
       <c r="D37" t="n">
         <v>29</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="E37" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -2947,7 +2715,7 @@
       <c r="O37" t="n">
         <v>-21</v>
       </c>
-      <c r="P37" s="14" t="inlineStr">
+      <c r="P37" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -2964,20 +2732,16 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>31週継続中</t>
-        </is>
+      <c r="C38" t="n">
+        <v>8</v>
       </c>
       <c r="D38" t="n">
         <v>31</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="E38" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -3009,7 +2773,7 @@
       <c r="O38" t="n">
         <v>-35</v>
       </c>
-      <c r="P38" s="16" t="inlineStr">
+      <c r="P38" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3026,20 +2790,16 @@
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>33週継続中</t>
-        </is>
+      <c r="C39" t="n">
+        <v>18</v>
       </c>
       <c r="D39" t="n">
         <v>33</v>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="E39" t="n">
+        <v>15</v>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -3071,7 +2831,7 @@
       <c r="O39" t="n">
         <v>-33</v>
       </c>
-      <c r="P39" s="14" t="inlineStr">
+      <c r="P39" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3088,20 +2848,16 @@
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>33週継続中</t>
-        </is>
+      <c r="C40" t="n">
+        <v>11</v>
       </c>
       <c r="D40" t="n">
         <v>33</v>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="inlineStr">
+      <c r="E40" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -3133,7 +2889,7 @@
       <c r="O40" t="n">
         <v>-42</v>
       </c>
-      <c r="P40" s="14" t="inlineStr">
+      <c r="P40" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3150,20 +2906,16 @@
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>33週継続中</t>
-        </is>
+      <c r="C41" t="n">
+        <v>4</v>
       </c>
       <c r="D41" t="n">
         <v>33</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="inlineStr">
+      <c r="E41" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -3195,7 +2947,7 @@
       <c r="O41" t="n">
         <v>-39</v>
       </c>
-      <c r="P41" s="16" t="inlineStr">
+      <c r="P41" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3212,20 +2964,16 @@
           <t>2025-10-20</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>35週継続中</t>
-        </is>
+      <c r="C42" t="n">
+        <v>21</v>
       </c>
       <c r="D42" t="n">
         <v>35</v>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F42" s="14" t="inlineStr">
+      <c r="E42" t="n">
+        <v>14</v>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -3257,7 +3005,7 @@
       <c r="O42" t="n">
         <v>-7</v>
       </c>
-      <c r="P42" s="14" t="inlineStr">
+      <c r="P42" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3274,22 +3022,18 @@
           <t>2025-10-20</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>5週で終了</t>
-        </is>
+      <c r="C43" t="n">
+        <v>3</v>
       </c>
       <c r="D43" t="n">
         <v>5</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F43" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -3316,7 +3060,7 @@
       <c r="O43" t="n">
         <v>-11</v>
       </c>
-      <c r="P43" s="13" t="inlineStr">
+      <c r="P43" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -3333,20 +3077,16 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>37週継続中</t>
-        </is>
+      <c r="C44" t="n">
+        <v>14</v>
       </c>
       <c r="D44" t="n">
         <v>37</v>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F44" s="14" t="inlineStr">
+      <c r="E44" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -3378,7 +3118,7 @@
       <c r="O44" t="n">
         <v>-54</v>
       </c>
-      <c r="P44" s="14" t="inlineStr">
+      <c r="P44" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3395,20 +3135,16 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>37週継続中</t>
-        </is>
+      <c r="C45" t="n">
+        <v>15</v>
       </c>
       <c r="D45" t="n">
         <v>37</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="inlineStr">
+      <c r="E45" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -3440,7 +3176,7 @@
       <c r="O45" t="n">
         <v>-52</v>
       </c>
-      <c r="P45" s="14" t="inlineStr">
+      <c r="P45" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3457,22 +3193,18 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>21週で終了</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="n">
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="n">
         <v>21</v>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F46" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E46" t="n">
+        <v>19</v>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3502,7 +3234,7 @@
       <c r="O46" t="n">
         <v>-31</v>
       </c>
-      <c r="P46" s="13" t="inlineStr">
+      <c r="P46" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -3519,20 +3251,16 @@
           <t>2025-09-22</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>39週継続中</t>
-        </is>
+      <c r="C47" t="n">
+        <v>7</v>
       </c>
       <c r="D47" t="n">
         <v>39</v>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="inlineStr">
+      <c r="E47" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -3564,7 +3292,7 @@
       <c r="O47" t="n">
         <v>-31</v>
       </c>
-      <c r="P47" s="16" t="inlineStr">
+      <c r="P47" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3581,20 +3309,16 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>41週継続中</t>
-        </is>
+      <c r="C48" t="n">
+        <v>19</v>
       </c>
       <c r="D48" t="n">
         <v>41</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="inlineStr">
+      <c r="E48" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -3626,7 +3350,7 @@
       <c r="O48" t="n">
         <v>-16</v>
       </c>
-      <c r="P48" s="14" t="inlineStr">
+      <c r="P48" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3643,20 +3367,16 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>41週継続中</t>
-        </is>
+      <c r="C49" t="n">
+        <v>5</v>
       </c>
       <c r="D49" t="n">
         <v>41</v>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="inlineStr">
+      <c r="E49" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -3688,7 +3408,7 @@
       <c r="O49" t="n">
         <v>-27</v>
       </c>
-      <c r="P49" s="16" t="inlineStr">
+      <c r="P49" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3705,20 +3425,16 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>41週継続中</t>
-        </is>
+      <c r="C50" t="n">
+        <v>15</v>
       </c>
       <c r="D50" t="n">
         <v>41</v>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
+      <c r="E50" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -3750,7 +3466,7 @@
       <c r="O50" t="n">
         <v>-64</v>
       </c>
-      <c r="P50" s="14" t="inlineStr">
+      <c r="P50" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3767,20 +3483,16 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>46週継続中</t>
-        </is>
+      <c r="C51" t="n">
+        <v>6</v>
       </c>
       <c r="D51" t="n">
         <v>46</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F51" s="16" t="inlineStr">
+      <c r="E51" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -3812,7 +3524,7 @@
       <c r="O51" t="n">
         <v>-48</v>
       </c>
-      <c r="P51" s="16" t="inlineStr">
+      <c r="P51" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3829,20 +3541,16 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>46週継続中</t>
-        </is>
+      <c r="C52" t="n">
+        <v>3</v>
       </c>
       <c r="D52" t="n">
         <v>46</v>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F52" s="16" t="inlineStr">
+      <c r="E52" s="15" t="n">
+        <v>43</v>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -3874,7 +3582,7 @@
       <c r="O52" t="n">
         <v>-37</v>
       </c>
-      <c r="P52" s="16" t="inlineStr">
+      <c r="P52" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -3891,20 +3599,16 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>46週継続中</t>
-        </is>
+      <c r="C53" t="n">
+        <v>31</v>
       </c>
       <c r="D53" t="n">
         <v>46</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F53" s="14" t="inlineStr">
+      <c r="E53" t="n">
+        <v>15</v>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -3936,7 +3640,7 @@
       <c r="O53" t="n">
         <v>-9</v>
       </c>
-      <c r="P53" s="14" t="inlineStr">
+      <c r="P53" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -3953,20 +3657,16 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>46週継続中</t>
-        </is>
+      <c r="C54" t="n">
+        <v>6</v>
       </c>
       <c r="D54" t="n">
         <v>46</v>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="inlineStr">
+      <c r="E54" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -3998,7 +3698,7 @@
       <c r="O54" t="n">
         <v>-66</v>
       </c>
-      <c r="P54" s="16" t="inlineStr">
+      <c r="P54" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4015,20 +3715,16 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>46週継続中</t>
-        </is>
+      <c r="C55" t="n">
+        <v>6</v>
       </c>
       <c r="D55" t="n">
         <v>46</v>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F55" s="16" t="inlineStr">
+      <c r="E55" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -4060,7 +3756,7 @@
       <c r="O55" t="n">
         <v>-50</v>
       </c>
-      <c r="P55" s="16" t="inlineStr">
+      <c r="P55" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4077,20 +3773,16 @@
           <t>2025-07-21</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>48週継続中</t>
-        </is>
+      <c r="C56" t="n">
+        <v>27</v>
       </c>
       <c r="D56" t="n">
         <v>48</v>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F56" s="14" t="inlineStr">
+      <c r="E56" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -4122,7 +3814,7 @@
       <c r="O56" t="n">
         <v>-11</v>
       </c>
-      <c r="P56" s="14" t="inlineStr">
+      <c r="P56" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -4139,20 +3831,16 @@
           <t>2025-07-21</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>48週継続中</t>
-        </is>
+      <c r="C57" t="n">
+        <v>11</v>
       </c>
       <c r="D57" t="n">
         <v>48</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F57" s="14" t="inlineStr">
+      <c r="E57" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -4184,7 +3872,7 @@
       <c r="O57" t="n">
         <v>-50</v>
       </c>
-      <c r="P57" s="14" t="inlineStr">
+      <c r="P57" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -4201,20 +3889,16 @@
           <t>2025-07-21</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>48週継続中</t>
-        </is>
+      <c r="C58" t="n">
+        <v>7</v>
       </c>
       <c r="D58" t="n">
         <v>48</v>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F58" s="14" t="inlineStr">
+      <c r="E58" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -4246,7 +3930,7 @@
       <c r="O58" t="n">
         <v>-45</v>
       </c>
-      <c r="P58" s="14" t="inlineStr">
+      <c r="P58" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -4263,20 +3947,16 @@
           <t>2025-07-21</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>18週で終了</t>
-        </is>
+      <c r="C59" t="n">
+        <v>2</v>
       </c>
       <c r="D59" t="n">
         <v>18</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F59" s="14" t="inlineStr">
+      <c r="E59" t="n">
+        <v>16</v>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -4308,7 +3988,7 @@
       <c r="O59" t="n">
         <v>-69</v>
       </c>
-      <c r="P59" s="14" t="inlineStr">
+      <c r="P59" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -4325,22 +4005,18 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>32週で終了</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="n">
+      <c r="C60" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" t="n">
         <v>32</v>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F60" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E60" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -4370,7 +4046,7 @@
       <c r="O60" t="n">
         <v>-33</v>
       </c>
-      <c r="P60" s="13" t="inlineStr">
+      <c r="P60" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4387,20 +4063,16 @@
           <t>2025-06-02</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>53週継続中</t>
-        </is>
+      <c r="C61" t="n">
+        <v>4</v>
       </c>
       <c r="D61" t="n">
         <v>53</v>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F61" s="16" t="inlineStr">
+      <c r="E61" s="15" t="n">
+        <v>49</v>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -4432,7 +4104,7 @@
       <c r="O61" t="n">
         <v>-45</v>
       </c>
-      <c r="P61" s="16" t="inlineStr">
+      <c r="P61" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4449,20 +4121,16 @@
           <t>2025-06-02</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>53週継続中</t>
-        </is>
+      <c r="C62" t="n">
+        <v>8</v>
       </c>
       <c r="D62" t="n">
         <v>53</v>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F62" s="14" t="inlineStr">
+      <c r="E62" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -4494,7 +4162,7 @@
       <c r="O62" t="n">
         <v>-45</v>
       </c>
-      <c r="P62" s="14" t="inlineStr">
+      <c r="P62" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -4511,20 +4179,16 @@
           <t>2025-06-02</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>53週継続中</t>
-        </is>
+      <c r="C63" t="n">
+        <v>24</v>
       </c>
       <c r="D63" t="n">
         <v>53</v>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F63" s="14" t="inlineStr">
+      <c r="E63" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="F63" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -4556,7 +4220,7 @@
       <c r="O63" t="n">
         <v>-21</v>
       </c>
-      <c r="P63" s="14" t="inlineStr">
+      <c r="P63" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -4573,22 +4237,18 @@
           <t>2025-06-02</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>53週継続中</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="n">
+      <c r="C64" t="n">
+        <v>5</v>
+      </c>
+      <c r="D64" t="n">
         <v>53</v>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F64" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E64" s="15" t="n">
+        <v>48</v>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -4618,7 +4278,7 @@
       <c r="O64" t="n">
         <v>-50</v>
       </c>
-      <c r="P64" s="13" t="inlineStr">
+      <c r="P64" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4635,20 +4295,16 @@
           <t>2025-06-02</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>53週継続中</t>
-        </is>
+      <c r="C65" t="n">
+        <v>8</v>
       </c>
       <c r="D65" t="n">
         <v>53</v>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F65" s="16" t="inlineStr">
+      <c r="E65" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -4680,7 +4336,7 @@
       <c r="O65" t="n">
         <v>-61</v>
       </c>
-      <c r="P65" s="16" t="inlineStr">
+      <c r="P65" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4697,20 +4353,16 @@
           <t>2025-06-02</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>12週で終了</t>
-        </is>
+      <c r="C66" t="n">
+        <v>6</v>
       </c>
       <c r="D66" t="n">
         <v>12</v>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F66" s="16" t="inlineStr">
+      <c r="E66" t="n">
+        <v>6</v>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -4742,7 +4394,7 @@
       <c r="O66" t="n">
         <v>-8</v>
       </c>
-      <c r="P66" s="16" t="inlineStr">
+      <c r="P66" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4759,20 +4411,16 @@
           <t>2025-06-02</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>25週で終了</t>
-        </is>
+      <c r="C67" t="n">
+        <v>4</v>
       </c>
       <c r="D67" t="n">
         <v>25</v>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F67" s="16" t="inlineStr">
+      <c r="E67" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -4804,7 +4452,7 @@
       <c r="O67" t="n">
         <v>-15</v>
       </c>
-      <c r="P67" s="16" t="inlineStr">
+      <c r="P67" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4821,22 +4469,18 @@
           <t>2025-06-02</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>21週で終了</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="n">
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="n">
         <v>21</v>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F68" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E68" t="n">
+        <v>19</v>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -4866,7 +4510,7 @@
       <c r="O68" t="n">
         <v>-21</v>
       </c>
-      <c r="P68" s="13" t="inlineStr">
+      <c r="P68" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -4883,20 +4527,16 @@
           <t>2025-05-19</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>55週継続中</t>
-        </is>
+      <c r="C69" t="n">
+        <v>25</v>
       </c>
       <c r="D69" t="n">
         <v>55</v>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F69" s="16" t="inlineStr">
+      <c r="E69" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -4928,7 +4568,7 @@
       <c r="O69" t="n">
         <v>-41</v>
       </c>
-      <c r="P69" s="16" t="inlineStr">
+      <c r="P69" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -4945,22 +4585,18 @@
           <t>2025-05-19</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>18週で終了</t>
-        </is>
+      <c r="C70" t="n">
+        <v>3</v>
       </c>
       <c r="D70" t="n">
         <v>18</v>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F70" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E70" t="n">
+        <v>15</v>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -4990,7 +4626,7 @@
       <c r="O70" t="n">
         <v>-71</v>
       </c>
-      <c r="P70" s="13" t="inlineStr">
+      <c r="P70" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -5007,22 +4643,18 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>46週で終了</t>
-        </is>
-      </c>
-      <c r="D71" s="17" t="n">
+      <c r="C71" t="n">
+        <v>5</v>
+      </c>
+      <c r="D71" t="n">
         <v>46</v>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F71" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E71" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -5052,7 +4684,7 @@
       <c r="O71" t="n">
         <v>-45</v>
       </c>
-      <c r="P71" s="13" t="inlineStr">
+      <c r="P71" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -5069,22 +4701,18 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>53週で終了</t>
-        </is>
-      </c>
-      <c r="D72" s="17" t="n">
+      <c r="C72" t="n">
+        <v>4</v>
+      </c>
+      <c r="D72" t="n">
         <v>53</v>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F72" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E72" s="15" t="n">
+        <v>49</v>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -5114,7 +4742,7 @@
       <c r="O72" t="n">
         <v>-77</v>
       </c>
-      <c r="P72" s="13" t="inlineStr">
+      <c r="P72" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -5131,20 +4759,16 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>57週継続中</t>
-        </is>
+      <c r="C73" t="n">
+        <v>6</v>
       </c>
       <c r="D73" t="n">
         <v>57</v>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F73" s="16" t="inlineStr">
+      <c r="E73" s="15" t="n">
+        <v>51</v>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -5176,7 +4800,7 @@
       <c r="O73" t="n">
         <v>-71</v>
       </c>
-      <c r="P73" s="16" t="inlineStr">
+      <c r="P73" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5193,20 +4817,16 @@
           <t>2025-04-21</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>59週継続中</t>
-        </is>
+      <c r="C74" t="n">
+        <v>7</v>
       </c>
       <c r="D74" t="n">
         <v>59</v>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F74" s="16" t="inlineStr">
+      <c r="E74" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="F74" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -5238,7 +4858,7 @@
       <c r="O74" t="n">
         <v>-63</v>
       </c>
-      <c r="P74" s="16" t="inlineStr">
+      <c r="P74" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5255,20 +4875,16 @@
           <t>2025-04-21</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>59週継続中</t>
-        </is>
+      <c r="C75" t="n">
+        <v>25</v>
       </c>
       <c r="D75" t="n">
         <v>59</v>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F75" s="14" t="inlineStr">
+      <c r="E75" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -5300,7 +4916,7 @@
       <c r="O75" t="n">
         <v>-45</v>
       </c>
-      <c r="P75" s="14" t="inlineStr">
+      <c r="P75" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5317,22 +4933,18 @@
           <t>2025-04-21</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>36週で終了</t>
-        </is>
-      </c>
-      <c r="D76" s="17" t="n">
+      <c r="C76" t="n">
+        <v>3</v>
+      </c>
+      <c r="D76" t="n">
         <v>36</v>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F76" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E76" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="F76" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -5362,7 +4974,7 @@
       <c r="O76" t="n">
         <v>-59</v>
       </c>
-      <c r="P76" s="13" t="inlineStr">
+      <c r="P76" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -5379,20 +4991,16 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>52週で終了</t>
-        </is>
+      <c r="C77" t="n">
+        <v>6</v>
       </c>
       <c r="D77" t="n">
         <v>52</v>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F77" s="14" t="inlineStr">
+      <c r="E77" s="15" t="n">
+        <v>46</v>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -5424,7 +5032,7 @@
       <c r="O77" t="n">
         <v>-48</v>
       </c>
-      <c r="P77" s="14" t="inlineStr">
+      <c r="P77" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5441,20 +5049,16 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>61週継続中</t>
-        </is>
+      <c r="C78" t="n">
+        <v>29</v>
       </c>
       <c r="D78" t="n">
         <v>61</v>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F78" s="14" t="inlineStr">
+      <c r="E78" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -5486,7 +5090,7 @@
       <c r="O78" t="n">
         <v>-10</v>
       </c>
-      <c r="P78" s="14" t="inlineStr">
+      <c r="P78" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5503,22 +5107,18 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>5週で終了</t>
-        </is>
+      <c r="C79" t="n">
+        <v>2</v>
       </c>
       <c r="D79" t="n">
         <v>5</v>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F79" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E79" t="n">
+        <v>3</v>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -5545,7 +5145,7 @@
       <c r="O79" t="n">
         <v>-11</v>
       </c>
-      <c r="P79" s="13" t="inlineStr">
+      <c r="P79" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -5562,22 +5162,18 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>29週で終了</t>
-        </is>
-      </c>
-      <c r="D80" s="17" t="n">
+      <c r="C80" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" t="n">
         <v>29</v>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F80" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E80" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="F80" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -5607,7 +5203,7 @@
       <c r="O80" t="n">
         <v>-58</v>
       </c>
-      <c r="P80" s="13" t="inlineStr">
+      <c r="P80" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -5624,22 +5220,18 @@
           <t>2025-03-17</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>28週で終了</t>
-        </is>
-      </c>
-      <c r="D81" s="17" t="n">
+      <c r="C81" t="n">
+        <v>3</v>
+      </c>
+      <c r="D81" t="n">
         <v>28</v>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F81" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E81" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -5669,7 +5261,7 @@
       <c r="O81" t="n">
         <v>-27</v>
       </c>
-      <c r="P81" s="13" t="inlineStr">
+      <c r="P81" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -5686,20 +5278,16 @@
           <t>2025-03-03</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>66週継続中</t>
-        </is>
+      <c r="C82" t="n">
+        <v>6</v>
       </c>
       <c r="D82" t="n">
         <v>66</v>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F82" s="16" t="inlineStr">
+      <c r="E82" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -5731,7 +5319,7 @@
       <c r="O82" t="n">
         <v>-54</v>
       </c>
-      <c r="P82" s="16" t="inlineStr">
+      <c r="P82" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5748,20 +5336,16 @@
           <t>2025-03-03</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>66週継続中</t>
-        </is>
+      <c r="C83" t="n">
+        <v>14</v>
       </c>
       <c r="D83" t="n">
         <v>66</v>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F83" s="14" t="inlineStr">
+      <c r="E83" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -5793,7 +5377,7 @@
       <c r="O83" t="n">
         <v>-58</v>
       </c>
-      <c r="P83" s="14" t="inlineStr">
+      <c r="P83" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5810,20 +5394,16 @@
           <t>2025-03-03</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>66週継続中</t>
-        </is>
+      <c r="C84" t="n">
+        <v>7</v>
       </c>
       <c r="D84" t="n">
         <v>66</v>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F84" s="16" t="inlineStr">
+      <c r="E84" s="15" t="n">
+        <v>59</v>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -5855,7 +5435,7 @@
       <c r="O84" t="n">
         <v>-58</v>
       </c>
-      <c r="P84" s="16" t="inlineStr">
+      <c r="P84" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -5872,20 +5452,16 @@
           <t>2025-03-03</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>66週継続中</t>
-        </is>
+      <c r="C85" t="n">
+        <v>25</v>
       </c>
       <c r="D85" t="n">
         <v>66</v>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F85" s="14" t="inlineStr">
+      <c r="E85" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -5917,7 +5493,7 @@
       <c r="O85" t="n">
         <v>-13</v>
       </c>
-      <c r="P85" s="14" t="inlineStr">
+      <c r="P85" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -5934,22 +5510,18 @@
           <t>2025-03-03</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>10週で終了</t>
-        </is>
+      <c r="C86" t="n">
+        <v>1</v>
       </c>
       <c r="D86" t="n">
         <v>10</v>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F86" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E86" t="n">
+        <v>9</v>
+      </c>
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -5979,7 +5551,7 @@
       <c r="O86" t="n">
         <v>-59</v>
       </c>
-      <c r="P86" s="13" t="inlineStr">
+      <c r="P86" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -5996,20 +5568,16 @@
           <t>2025-02-03</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>70週継続中</t>
-        </is>
+      <c r="C87" t="n">
+        <v>5</v>
       </c>
       <c r="D87" t="n">
         <v>70</v>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F87" s="16" t="inlineStr">
+      <c r="E87" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="F87" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -6041,7 +5609,7 @@
       <c r="O87" t="n">
         <v>-63</v>
       </c>
-      <c r="P87" s="16" t="inlineStr">
+      <c r="P87" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6058,20 +5626,16 @@
           <t>2025-02-03</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>70週継続中</t>
-        </is>
+      <c r="C88" t="n">
+        <v>9</v>
       </c>
       <c r="D88" t="n">
         <v>70</v>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F88" s="14" t="inlineStr">
+      <c r="E88" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="F88" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -6103,7 +5667,7 @@
       <c r="O88" t="n">
         <v>-40</v>
       </c>
-      <c r="P88" s="14" t="inlineStr">
+      <c r="P88" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -6120,20 +5684,16 @@
           <t>2025-02-03</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>70週継続中</t>
-        </is>
+      <c r="C89" t="n">
+        <v>20</v>
       </c>
       <c r="D89" t="n">
         <v>70</v>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F89" s="14" t="inlineStr">
+      <c r="E89" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -6165,7 +5725,7 @@
       <c r="O89" t="n">
         <v>-43</v>
       </c>
-      <c r="P89" s="14" t="inlineStr">
+      <c r="P89" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -6182,20 +5742,16 @@
           <t>2025-02-03</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>70週継続中</t>
-        </is>
+      <c r="C90" t="n">
+        <v>71</v>
       </c>
       <c r="D90" t="n">
         <v>70</v>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F90" s="14" t="inlineStr">
+      <c r="E90" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F90" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -6227,7 +5783,7 @@
       <c r="O90" t="n">
         <v>143</v>
       </c>
-      <c r="P90" s="14" t="inlineStr">
+      <c r="P90" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -6244,20 +5800,16 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>72週継続中</t>
-        </is>
+      <c r="C91" t="n">
+        <v>8</v>
       </c>
       <c r="D91" t="n">
         <v>72</v>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F91" s="16" t="inlineStr">
+      <c r="E91" s="15" t="n">
+        <v>64</v>
+      </c>
+      <c r="F91" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -6289,7 +5841,7 @@
       <c r="O91" t="n">
         <v>-43</v>
       </c>
-      <c r="P91" s="16" t="inlineStr">
+      <c r="P91" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6306,20 +5858,16 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>72週継続中</t>
-        </is>
+      <c r="C92" t="n">
+        <v>73</v>
       </c>
       <c r="D92" t="n">
         <v>72</v>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F92" s="14" t="inlineStr">
+      <c r="E92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -6351,7 +5899,7 @@
       <c r="O92" t="n">
         <v>5</v>
       </c>
-      <c r="P92" s="14" t="inlineStr">
+      <c r="P92" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -6368,20 +5916,16 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>72週継続中</t>
-        </is>
+      <c r="C93" t="n">
+        <v>17</v>
       </c>
       <c r="D93" t="n">
         <v>72</v>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F93" s="14" t="inlineStr">
+      <c r="E93" s="15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -6413,7 +5957,7 @@
       <c r="O93" t="n">
         <v>-20</v>
       </c>
-      <c r="P93" s="14" t="inlineStr">
+      <c r="P93" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -6430,22 +5974,18 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>51週で終了</t>
-        </is>
-      </c>
-      <c r="D94" s="17" t="n">
+      <c r="C94" t="n">
+        <v>4</v>
+      </c>
+      <c r="D94" t="n">
         <v>51</v>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F94" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E94" s="15" t="n">
+        <v>47</v>
+      </c>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -6475,7 +6015,7 @@
       <c r="O94" t="n">
         <v>-62</v>
       </c>
-      <c r="P94" s="13" t="inlineStr">
+      <c r="P94" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -6492,22 +6032,18 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>49週で終了</t>
-        </is>
-      </c>
-      <c r="D95" s="17" t="n">
+      <c r="C95" t="n">
+        <v>5</v>
+      </c>
+      <c r="D95" t="n">
         <v>49</v>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F95" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E95" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -6537,7 +6073,7 @@
       <c r="O95" t="n">
         <v>-50</v>
       </c>
-      <c r="P95" s="13" t="inlineStr">
+      <c r="P95" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -6554,20 +6090,16 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>48週で終了</t>
-        </is>
+      <c r="C96" t="n">
+        <v>3</v>
       </c>
       <c r="D96" t="n">
         <v>48</v>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F96" s="16" t="inlineStr">
+      <c r="E96" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="F96" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -6599,7 +6131,7 @@
       <c r="O96" t="n">
         <v>-85</v>
       </c>
-      <c r="P96" s="16" t="inlineStr">
+      <c r="P96" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6616,20 +6148,16 @@
           <t>2025-01-06</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>63週で終了</t>
-        </is>
+      <c r="C97" t="n">
+        <v>7</v>
       </c>
       <c r="D97" t="n">
         <v>63</v>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F97" s="16" t="inlineStr">
+      <c r="E97" s="15" t="n">
+        <v>56</v>
+      </c>
+      <c r="F97" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -6661,7 +6189,7 @@
       <c r="O97" t="n">
         <v>-52</v>
       </c>
-      <c r="P97" s="16" t="inlineStr">
+      <c r="P97" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6678,20 +6206,16 @@
           <t>2025-01-06</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>74週継続中</t>
-        </is>
+      <c r="C98" t="n">
+        <v>2</v>
       </c>
       <c r="D98" t="n">
         <v>74</v>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F98" s="16" t="inlineStr">
+      <c r="E98" s="15" t="n">
+        <v>72</v>
+      </c>
+      <c r="F98" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -6723,7 +6247,7 @@
       <c r="O98" t="n">
         <v>-48</v>
       </c>
-      <c r="P98" s="16" t="inlineStr">
+      <c r="P98" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6740,20 +6264,16 @@
           <t>2024-12-16</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>77週継続中</t>
-        </is>
+      <c r="C99" t="n">
+        <v>15</v>
       </c>
       <c r="D99" t="n">
         <v>77</v>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F99" s="14" t="inlineStr">
+      <c r="E99" s="15" t="n">
+        <v>62</v>
+      </c>
+      <c r="F99" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -6785,7 +6305,7 @@
       <c r="O99" t="n">
         <v>-36</v>
       </c>
-      <c r="P99" s="14" t="inlineStr">
+      <c r="P99" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -6802,20 +6322,16 @@
           <t>2024-12-16</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>77週継続中</t>
-        </is>
+      <c r="C100" t="n">
+        <v>8</v>
       </c>
       <c r="D100" t="n">
         <v>77</v>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F100" s="16" t="inlineStr">
+      <c r="E100" s="15" t="n">
+        <v>69</v>
+      </c>
+      <c r="F100" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -6847,7 +6363,7 @@
       <c r="O100" t="n">
         <v>-78</v>
       </c>
-      <c r="P100" s="16" t="inlineStr">
+      <c r="P100" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6864,22 +6380,18 @@
           <t>2024-12-16</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>69週で終了</t>
-        </is>
-      </c>
-      <c r="D101" s="17" t="n">
+      <c r="C101" t="n">
+        <v>4</v>
+      </c>
+      <c r="D101" t="n">
         <v>69</v>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F101" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E101" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -6909,7 +6421,7 @@
       <c r="O101" t="n">
         <v>-59</v>
       </c>
-      <c r="P101" s="13" t="inlineStr">
+      <c r="P101" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -6926,20 +6438,16 @@
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>79週継続中</t>
-        </is>
+      <c r="C102" t="n">
+        <v>8</v>
       </c>
       <c r="D102" t="n">
         <v>79</v>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F102" s="16" t="inlineStr">
+      <c r="E102" s="15" t="n">
+        <v>71</v>
+      </c>
+      <c r="F102" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -6971,7 +6479,7 @@
       <c r="O102" t="n">
         <v>-57</v>
       </c>
-      <c r="P102" s="16" t="inlineStr">
+      <c r="P102" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -6988,20 +6496,16 @@
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>79週継続中</t>
-        </is>
+      <c r="C103" t="n">
+        <v>12</v>
       </c>
       <c r="D103" t="n">
         <v>79</v>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F103" s="14" t="inlineStr">
+      <c r="E103" s="15" t="n">
+        <v>67</v>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -7033,7 +6537,7 @@
       <c r="O103" t="n">
         <v>-62</v>
       </c>
-      <c r="P103" s="14" t="inlineStr">
+      <c r="P103" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7050,20 +6554,16 @@
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>69週で終了</t>
-        </is>
+      <c r="C104" t="n">
+        <v>8</v>
       </c>
       <c r="D104" t="n">
         <v>69</v>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F104" s="16" t="inlineStr">
+      <c r="E104" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="F104" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -7095,7 +6595,7 @@
       <c r="O104" t="n">
         <v>-38</v>
       </c>
-      <c r="P104" s="16" t="inlineStr">
+      <c r="P104" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7112,20 +6612,16 @@
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>43週で終了</t>
-        </is>
+      <c r="C105" t="n">
+        <v>6</v>
       </c>
       <c r="D105" t="n">
         <v>43</v>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F105" s="16" t="inlineStr">
+      <c r="E105" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="F105" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -7157,7 +6653,7 @@
       <c r="O105" t="n">
         <v>-62</v>
       </c>
-      <c r="P105" s="16" t="inlineStr">
+      <c r="P105" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7174,20 +6670,16 @@
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>81週継続中</t>
-        </is>
+      <c r="C106" t="n">
+        <v>26</v>
       </c>
       <c r="D106" t="n">
         <v>81</v>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F106" s="14" t="inlineStr">
+      <c r="E106" s="15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F106" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -7219,7 +6711,7 @@
       <c r="O106" t="n">
         <v>-41</v>
       </c>
-      <c r="P106" s="14" t="inlineStr">
+      <c r="P106" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7236,20 +6728,16 @@
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>3週で終了</t>
-        </is>
+      <c r="C107" t="n">
+        <v>0</v>
       </c>
       <c r="D107" t="n">
         <v>3</v>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F107" s="12" t="inlineStr">
+      <c r="E107" t="n">
+        <v>3</v>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
         <is>
           <t>計測中</t>
         </is>
@@ -7275,7 +6763,7 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="P107" s="13" t="inlineStr">
+      <c r="P107" s="11" t="inlineStr">
         <is>
           <t>危険(暫定)</t>
         </is>
@@ -7292,22 +6780,18 @@
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>11週で終了</t>
-        </is>
+      <c r="C108" t="n">
+        <v>3</v>
       </c>
       <c r="D108" t="n">
         <v>11</v>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F108" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E108" t="n">
+        <v>8</v>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -7337,7 +6821,7 @@
       <c r="O108" t="n">
         <v>-21</v>
       </c>
-      <c r="P108" s="13" t="inlineStr">
+      <c r="P108" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -7354,22 +6838,18 @@
           <t>2024-11-04</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>83週継続中</t>
-        </is>
-      </c>
-      <c r="D109" s="17" t="n">
+      <c r="C109" t="n">
+        <v>5</v>
+      </c>
+      <c r="D109" t="n">
         <v>83</v>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F109" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E109" s="15" t="n">
+        <v>78</v>
+      </c>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -7399,7 +6879,7 @@
       <c r="O109" t="n">
         <v>-53</v>
       </c>
-      <c r="P109" s="13" t="inlineStr">
+      <c r="P109" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -7416,20 +6896,16 @@
           <t>2024-11-04</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>38週で終了</t>
-        </is>
+      <c r="C110" t="n">
+        <v>5</v>
       </c>
       <c r="D110" t="n">
         <v>38</v>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F110" s="16" t="inlineStr">
+      <c r="E110" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="F110" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -7461,7 +6937,7 @@
       <c r="O110" t="n">
         <v>-38</v>
       </c>
-      <c r="P110" s="16" t="inlineStr">
+      <c r="P110" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7478,22 +6954,18 @@
           <t>2024-10-21</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>83週継続中</t>
-        </is>
-      </c>
-      <c r="D111" s="17" t="n">
+      <c r="C111" t="n">
+        <v>7</v>
+      </c>
+      <c r="D111" t="n">
         <v>83</v>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F111" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E111" s="15" t="n">
+        <v>76</v>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -7523,7 +6995,7 @@
       <c r="O111" t="n">
         <v>-83</v>
       </c>
-      <c r="P111" s="13" t="inlineStr">
+      <c r="P111" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -7540,20 +7012,16 @@
           <t>2024-10-07</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>87週継続中</t>
-        </is>
+      <c r="C112" t="n">
+        <v>9</v>
       </c>
       <c r="D112" t="n">
         <v>87</v>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F112" s="16" t="inlineStr">
+      <c r="E112" s="15" t="n">
+        <v>78</v>
+      </c>
+      <c r="F112" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -7585,7 +7053,7 @@
       <c r="O112" t="n">
         <v>-52</v>
       </c>
-      <c r="P112" s="16" t="inlineStr">
+      <c r="P112" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7602,20 +7070,16 @@
           <t>2024-10-07</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>85週継続中</t>
-        </is>
+      <c r="C113" t="n">
+        <v>9</v>
       </c>
       <c r="D113" t="n">
         <v>85</v>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F113" s="16" t="inlineStr">
+      <c r="E113" s="15" t="n">
+        <v>76</v>
+      </c>
+      <c r="F113" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -7647,7 +7111,7 @@
       <c r="O113" t="n">
         <v>-35</v>
       </c>
-      <c r="P113" s="16" t="inlineStr">
+      <c r="P113" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7664,20 +7128,16 @@
           <t>2024-10-07</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>87週継続中</t>
-        </is>
+      <c r="C114" t="n">
+        <v>18</v>
       </c>
       <c r="D114" t="n">
         <v>87</v>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F114" s="14" t="inlineStr">
+      <c r="E114" s="15" t="n">
+        <v>69</v>
+      </c>
+      <c r="F114" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -7709,7 +7169,7 @@
       <c r="O114" t="n">
         <v>-37</v>
       </c>
-      <c r="P114" s="14" t="inlineStr">
+      <c r="P114" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7726,22 +7186,18 @@
           <t>2024-10-07</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>70週で終了</t>
-        </is>
-      </c>
-      <c r="D115" s="17" t="n">
+      <c r="C115" t="n">
+        <v>4</v>
+      </c>
+      <c r="D115" t="n">
         <v>70</v>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F115" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E115" s="15" t="n">
+        <v>66</v>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -7771,7 +7227,7 @@
       <c r="O115" t="n">
         <v>-58</v>
       </c>
-      <c r="P115" s="13" t="inlineStr">
+      <c r="P115" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -7788,20 +7244,16 @@
           <t>2024-09-02</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>92週継続中</t>
-        </is>
+      <c r="C116" t="n">
+        <v>10</v>
       </c>
       <c r="D116" t="n">
         <v>92</v>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F116" s="14" t="inlineStr">
+      <c r="E116" s="15" t="n">
+        <v>82</v>
+      </c>
+      <c r="F116" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -7833,7 +7285,7 @@
       <c r="O116" t="n">
         <v>-35</v>
       </c>
-      <c r="P116" s="14" t="inlineStr">
+      <c r="P116" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7850,20 +7302,16 @@
           <t>2024-09-02</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>92週継続中</t>
-        </is>
+      <c r="C117" t="n">
+        <v>8</v>
       </c>
       <c r="D117" t="n">
         <v>92</v>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F117" s="16" t="inlineStr">
+      <c r="E117" s="15" t="n">
+        <v>84</v>
+      </c>
+      <c r="F117" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -7895,7 +7343,7 @@
       <c r="O117" t="n">
         <v>-35</v>
       </c>
-      <c r="P117" s="16" t="inlineStr">
+      <c r="P117" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -7912,20 +7360,16 @@
           <t>2024-09-02</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>92週継続中</t>
-        </is>
+      <c r="C118" t="n">
+        <v>57</v>
       </c>
       <c r="D118" t="n">
         <v>92</v>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F118" s="14" t="inlineStr">
+      <c r="E118" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="F118" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -7957,7 +7401,7 @@
       <c r="O118" t="n">
         <v>-46</v>
       </c>
-      <c r="P118" s="14" t="inlineStr">
+      <c r="P118" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -7974,22 +7418,18 @@
           <t>2024-09-02</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>45週で終了</t>
-        </is>
-      </c>
-      <c r="D119" s="17" t="n">
+      <c r="C119" t="n">
+        <v>4</v>
+      </c>
+      <c r="D119" t="n">
         <v>45</v>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F119" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E119" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -8019,7 +7459,7 @@
       <c r="O119" t="n">
         <v>-57</v>
       </c>
-      <c r="P119" s="13" t="inlineStr">
+      <c r="P119" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -8036,20 +7476,16 @@
           <t>2024-08-05</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>43週で終了</t>
-        </is>
+      <c r="C120" t="n">
+        <v>3</v>
       </c>
       <c r="D120" t="n">
         <v>43</v>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F120" s="16" t="inlineStr">
+      <c r="E120" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="F120" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -8081,7 +7517,7 @@
       <c r="O120" t="n">
         <v>-56</v>
       </c>
-      <c r="P120" s="16" t="inlineStr">
+      <c r="P120" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8098,20 +7534,16 @@
           <t>2024-08-05</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>64週で終了</t>
-        </is>
+      <c r="C121" t="n">
+        <v>5</v>
       </c>
       <c r="D121" t="n">
         <v>64</v>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F121" s="16" t="inlineStr">
+      <c r="E121" s="15" t="n">
+        <v>59</v>
+      </c>
+      <c r="F121" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -8143,7 +7575,7 @@
       <c r="O121" t="n">
         <v>-71</v>
       </c>
-      <c r="P121" s="16" t="inlineStr">
+      <c r="P121" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8160,20 +7592,16 @@
           <t>2024-08-05</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>23週で終了</t>
-        </is>
+      <c r="C122" t="n">
+        <v>1</v>
       </c>
       <c r="D122" t="n">
         <v>23</v>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F122" s="16" t="inlineStr">
+      <c r="E122" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="F122" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -8205,7 +7633,7 @@
       <c r="O122" t="n">
         <v>-53</v>
       </c>
-      <c r="P122" s="16" t="inlineStr">
+      <c r="P122" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8222,20 +7650,16 @@
           <t>2024-08-05</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>49週で終了</t>
-        </is>
+      <c r="C123" t="n">
+        <v>5</v>
       </c>
       <c r="D123" t="n">
         <v>49</v>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F123" s="16" t="inlineStr">
+      <c r="E123" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="F123" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -8267,7 +7691,7 @@
       <c r="O123" t="n">
         <v>-52</v>
       </c>
-      <c r="P123" s="16" t="inlineStr">
+      <c r="P123" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8284,20 +7708,16 @@
           <t>2024-07-22</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>98週継続中</t>
-        </is>
+      <c r="C124" t="n">
+        <v>43</v>
       </c>
       <c r="D124" t="n">
         <v>98</v>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F124" s="14" t="inlineStr">
+      <c r="E124" s="15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F124" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -8329,7 +7749,7 @@
       <c r="O124" t="n">
         <v>-21</v>
       </c>
-      <c r="P124" s="14" t="inlineStr">
+      <c r="P124" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8346,20 +7766,16 @@
           <t>2024-07-22</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>98週継続中</t>
-        </is>
+      <c r="C125" t="n">
+        <v>14</v>
       </c>
       <c r="D125" t="n">
         <v>98</v>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F125" s="14" t="inlineStr">
+      <c r="E125" s="15" t="n">
+        <v>84</v>
+      </c>
+      <c r="F125" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -8391,7 +7807,7 @@
       <c r="O125" t="n">
         <v>-29</v>
       </c>
-      <c r="P125" s="14" t="inlineStr">
+      <c r="P125" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8408,22 +7824,18 @@
           <t>2024-07-22</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>20週で終了</t>
-        </is>
-      </c>
-      <c r="D126" s="17" t="n">
+      <c r="C126" t="n">
+        <v>3</v>
+      </c>
+      <c r="D126" t="n">
         <v>20</v>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F126" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E126" t="n">
+        <v>17</v>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -8453,7 +7865,7 @@
       <c r="O126" t="n">
         <v>-57</v>
       </c>
-      <c r="P126" s="13" t="inlineStr">
+      <c r="P126" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -8470,22 +7882,18 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>30週で終了</t>
-        </is>
-      </c>
-      <c r="D127" s="17" t="n">
+      <c r="C127" t="n">
+        <v>3</v>
+      </c>
+      <c r="D127" t="n">
         <v>30</v>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F127" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E127" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -8515,7 +7923,7 @@
       <c r="O127" t="n">
         <v>-48</v>
       </c>
-      <c r="P127" s="13" t="inlineStr">
+      <c r="P127" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -8532,22 +7940,18 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>100週継続中</t>
-        </is>
-      </c>
-      <c r="D128" s="17" t="n">
+      <c r="C128" t="n">
+        <v>5</v>
+      </c>
+      <c r="D128" t="n">
         <v>100</v>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F128" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E128" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -8577,7 +7981,7 @@
       <c r="O128" t="n">
         <v>-73</v>
       </c>
-      <c r="P128" s="13" t="inlineStr">
+      <c r="P128" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -8594,20 +7998,16 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>100週継続中</t>
-        </is>
+      <c r="C129" t="n">
+        <v>7</v>
       </c>
       <c r="D129" t="n">
         <v>100</v>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F129" s="16" t="inlineStr">
+      <c r="E129" s="15" t="n">
+        <v>93</v>
+      </c>
+      <c r="F129" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -8639,7 +8039,7 @@
       <c r="O129" t="n">
         <v>-78</v>
       </c>
-      <c r="P129" s="16" t="inlineStr">
+      <c r="P129" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8656,20 +8056,16 @@
           <t>2024-06-02</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>105週継続中</t>
-        </is>
+      <c r="C130" t="n">
+        <v>36</v>
       </c>
       <c r="D130" t="n">
         <v>105</v>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F130" s="14" t="inlineStr">
+      <c r="E130" s="15" t="n">
+        <v>69</v>
+      </c>
+      <c r="F130" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -8701,7 +8097,7 @@
       <c r="O130" t="n">
         <v>-38</v>
       </c>
-      <c r="P130" s="14" t="inlineStr">
+      <c r="P130" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8718,20 +8114,16 @@
           <t>2024-06-02</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>28週で終了</t>
-        </is>
+      <c r="C131" t="n">
+        <v>4</v>
       </c>
       <c r="D131" t="n">
         <v>28</v>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F131" s="16" t="inlineStr">
+      <c r="E131" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F131" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -8763,7 +8155,7 @@
       <c r="O131" t="n">
         <v>-43</v>
       </c>
-      <c r="P131" s="16" t="inlineStr">
+      <c r="P131" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8780,20 +8172,16 @@
           <t>2024-06-02</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>105週継続中</t>
-        </is>
+      <c r="C132" t="n">
+        <v>24</v>
       </c>
       <c r="D132" t="n">
         <v>105</v>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F132" s="14" t="inlineStr">
+      <c r="E132" s="15" t="n">
+        <v>81</v>
+      </c>
+      <c r="F132" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -8825,7 +8213,7 @@
       <c r="O132" t="n">
         <v>-41</v>
       </c>
-      <c r="P132" s="14" t="inlineStr">
+      <c r="P132" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8842,20 +8230,16 @@
           <t>2024-06-02</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>105週継続中</t>
-        </is>
+      <c r="C133" t="n">
+        <v>12</v>
       </c>
       <c r="D133" t="n">
         <v>105</v>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F133" s="14" t="inlineStr">
+      <c r="E133" s="15" t="n">
+        <v>93</v>
+      </c>
+      <c r="F133" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -8887,7 +8271,7 @@
       <c r="O133" t="n">
         <v>-73</v>
       </c>
-      <c r="P133" s="14" t="inlineStr">
+      <c r="P133" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -8904,20 +8288,16 @@
           <t>2024-05-06</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>40週で終了</t>
-        </is>
+      <c r="C134" t="n">
+        <v>4</v>
       </c>
       <c r="D134" t="n">
         <v>40</v>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F134" s="16" t="inlineStr">
+      <c r="E134" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="F134" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -8949,7 +8329,7 @@
       <c r="O134" t="n">
         <v>-42</v>
       </c>
-      <c r="P134" s="16" t="inlineStr">
+      <c r="P134" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -8966,22 +8346,18 @@
           <t>2024-05-06</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>61週で終了</t>
-        </is>
-      </c>
-      <c r="D135" s="17" t="n">
+      <c r="C135" t="n">
+        <v>4</v>
+      </c>
+      <c r="D135" t="n">
         <v>61</v>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F135" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E135" s="15" t="n">
+        <v>57</v>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -9011,7 +8387,7 @@
       <c r="O135" t="n">
         <v>-67</v>
       </c>
-      <c r="P135" s="13" t="inlineStr">
+      <c r="P135" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -9028,20 +8404,16 @@
           <t>2024-05-06</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>109週継続中</t>
-        </is>
+      <c r="C136" t="n">
+        <v>18</v>
       </c>
       <c r="D136" t="n">
         <v>109</v>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F136" s="14" t="inlineStr">
+      <c r="E136" s="15" t="n">
+        <v>91</v>
+      </c>
+      <c r="F136" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -9073,7 +8445,7 @@
       <c r="O136" t="n">
         <v>-56</v>
       </c>
-      <c r="P136" s="14" t="inlineStr">
+      <c r="P136" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9090,20 +8462,16 @@
           <t>2024-04-22</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>111週継続中</t>
-        </is>
+      <c r="C137" t="n">
+        <v>14</v>
       </c>
       <c r="D137" t="n">
         <v>111</v>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F137" s="14" t="inlineStr">
+      <c r="E137" s="15" t="n">
+        <v>97</v>
+      </c>
+      <c r="F137" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -9135,7 +8503,7 @@
       <c r="O137" t="n">
         <v>-75</v>
       </c>
-      <c r="P137" s="14" t="inlineStr">
+      <c r="P137" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9152,20 +8520,16 @@
           <t>2024-04-08</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>73週で終了</t>
-        </is>
+      <c r="C138" t="n">
+        <v>5</v>
       </c>
       <c r="D138" t="n">
         <v>73</v>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F138" s="14" t="inlineStr">
+      <c r="E138" s="15" t="n">
+        <v>68</v>
+      </c>
+      <c r="F138" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -9197,7 +8561,7 @@
       <c r="O138" t="n">
         <v>-39</v>
       </c>
-      <c r="P138" s="14" t="inlineStr">
+      <c r="P138" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9214,20 +8578,16 @@
           <t>2024-04-08</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>113週継続中</t>
-        </is>
+      <c r="C139" t="n">
+        <v>6</v>
       </c>
       <c r="D139" t="n">
         <v>113</v>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F139" s="14" t="inlineStr">
+      <c r="E139" s="15" t="n">
+        <v>107</v>
+      </c>
+      <c r="F139" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -9259,7 +8619,7 @@
       <c r="O139" t="n">
         <v>-71</v>
       </c>
-      <c r="P139" s="14" t="inlineStr">
+      <c r="P139" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9276,20 +8636,16 @@
           <t>2024-04-08</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>77週で終了</t>
-        </is>
+      <c r="C140" t="n">
+        <v>9</v>
       </c>
       <c r="D140" t="n">
         <v>77</v>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F140" s="14" t="inlineStr">
+      <c r="E140" s="15" t="n">
+        <v>68</v>
+      </c>
+      <c r="F140" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -9321,7 +8677,7 @@
       <c r="O140" t="n">
         <v>-29</v>
       </c>
-      <c r="P140" s="14" t="inlineStr">
+      <c r="P140" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9338,20 +8694,16 @@
           <t>2024-03-25</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>115週継続中</t>
-        </is>
+      <c r="C141" t="n">
+        <v>8</v>
       </c>
       <c r="D141" t="n">
         <v>115</v>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F141" s="16" t="inlineStr">
+      <c r="E141" s="15" t="n">
+        <v>107</v>
+      </c>
+      <c r="F141" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -9383,7 +8735,7 @@
       <c r="O141" t="n">
         <v>-59</v>
       </c>
-      <c r="P141" s="16" t="inlineStr">
+      <c r="P141" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -9400,20 +8752,16 @@
           <t>2024-03-18</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>116週継続中</t>
-        </is>
+      <c r="C142" t="n">
+        <v>5</v>
       </c>
       <c r="D142" t="n">
         <v>116</v>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F142" s="16" t="inlineStr">
+      <c r="E142" s="15" t="n">
+        <v>111</v>
+      </c>
+      <c r="F142" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -9445,7 +8793,7 @@
       <c r="O142" t="n">
         <v>-25</v>
       </c>
-      <c r="P142" s="16" t="inlineStr">
+      <c r="P142" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -9462,20 +8810,16 @@
           <t>2024-03-04</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>118週継続中</t>
-        </is>
+      <c r="C143" t="n">
+        <v>10</v>
       </c>
       <c r="D143" t="n">
         <v>118</v>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F143" s="16" t="inlineStr">
+      <c r="E143" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="F143" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -9507,7 +8851,7 @@
       <c r="O143" t="n">
         <v>-54</v>
       </c>
-      <c r="P143" s="16" t="inlineStr">
+      <c r="P143" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -9524,20 +8868,16 @@
           <t>2024-03-04</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>118週継続中</t>
-        </is>
+      <c r="C144" t="n">
+        <v>106</v>
       </c>
       <c r="D144" t="n">
         <v>118</v>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F144" s="14" t="inlineStr">
+      <c r="E144" t="n">
+        <v>12</v>
+      </c>
+      <c r="F144" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -9569,7 +8909,7 @@
       <c r="O144" t="n">
         <v>-66</v>
       </c>
-      <c r="P144" s="14" t="inlineStr">
+      <c r="P144" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9586,20 +8926,16 @@
           <t>2024-03-04</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>118週継続中</t>
-        </is>
+      <c r="C145" t="n">
+        <v>10</v>
       </c>
       <c r="D145" t="n">
         <v>118</v>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F145" s="16" t="inlineStr">
+      <c r="E145" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="F145" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -9631,7 +8967,7 @@
       <c r="O145" t="n">
         <v>-73</v>
       </c>
-      <c r="P145" s="16" t="inlineStr">
+      <c r="P145" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -9648,20 +8984,16 @@
           <t>2024-02-05</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>122週継続中</t>
-        </is>
+      <c r="C146" t="n">
+        <v>14</v>
       </c>
       <c r="D146" t="n">
         <v>122</v>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F146" s="14" t="inlineStr">
+      <c r="E146" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="F146" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -9693,7 +9025,7 @@
       <c r="O146" t="n">
         <v>-27</v>
       </c>
-      <c r="P146" s="14" t="inlineStr">
+      <c r="P146" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9710,20 +9042,16 @@
           <t>2024-02-05</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>122週継続中</t>
-        </is>
+      <c r="C147" t="n">
+        <v>6</v>
       </c>
       <c r="D147" t="n">
         <v>122</v>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F147" s="16" t="inlineStr">
+      <c r="E147" s="15" t="n">
+        <v>116</v>
+      </c>
+      <c r="F147" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -9755,7 +9083,7 @@
       <c r="O147" t="n">
         <v>-68</v>
       </c>
-      <c r="P147" s="16" t="inlineStr">
+      <c r="P147" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -9772,20 +9100,16 @@
           <t>2024-02-05</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>122週継続中</t>
-        </is>
+      <c r="C148" t="n">
+        <v>26</v>
       </c>
       <c r="D148" t="n">
         <v>122</v>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F148" s="14" t="inlineStr">
+      <c r="E148" s="15" t="n">
+        <v>96</v>
+      </c>
+      <c r="F148" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -9817,7 +9141,7 @@
       <c r="O148" t="n">
         <v>-39</v>
       </c>
-      <c r="P148" s="14" t="inlineStr">
+      <c r="P148" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9834,22 +9158,18 @@
           <t>2024-02-05</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>27週で終了</t>
-        </is>
-      </c>
-      <c r="D149" s="17" t="n">
+      <c r="C149" t="n">
+        <v>3</v>
+      </c>
+      <c r="D149" t="n">
         <v>27</v>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F149" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E149" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F149" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -9879,7 +9199,7 @@
       <c r="O149" t="n">
         <v>-52</v>
       </c>
-      <c r="P149" s="13" t="inlineStr">
+      <c r="P149" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -9896,20 +9216,16 @@
           <t>2024-02-05</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>62週で終了</t>
-        </is>
+      <c r="C150" t="n">
+        <v>6</v>
       </c>
       <c r="D150" t="n">
         <v>62</v>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F150" s="14" t="inlineStr">
+      <c r="E150" s="15" t="n">
+        <v>56</v>
+      </c>
+      <c r="F150" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -9941,7 +9257,7 @@
       <c r="O150" t="n">
         <v>-41</v>
       </c>
-      <c r="P150" s="14" t="inlineStr">
+      <c r="P150" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -9958,20 +9274,16 @@
           <t>2024-02-05</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>122週継続中</t>
-        </is>
+      <c r="C151" t="n">
+        <v>8</v>
       </c>
       <c r="D151" t="n">
         <v>122</v>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F151" s="16" t="inlineStr">
+      <c r="E151" s="15" t="n">
+        <v>114</v>
+      </c>
+      <c r="F151" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -10003,7 +9315,7 @@
       <c r="O151" t="n">
         <v>-68</v>
       </c>
-      <c r="P151" s="16" t="inlineStr">
+      <c r="P151" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -10020,22 +9332,18 @@
           <t>2024-02-05</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>30週で終了</t>
-        </is>
-      </c>
-      <c r="D152" s="17" t="n">
+      <c r="C152" t="n">
+        <v>2</v>
+      </c>
+      <c r="D152" t="n">
         <v>30</v>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F152" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E152" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="F152" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -10065,7 +9373,7 @@
       <c r="O152" t="n">
         <v>-45</v>
       </c>
-      <c r="P152" s="13" t="inlineStr">
+      <c r="P152" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -10082,20 +9390,16 @@
           <t>2024-01-08</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>89週で終了</t>
-        </is>
+      <c r="C153" t="n">
+        <v>5</v>
       </c>
       <c r="D153" t="n">
         <v>89</v>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F153" s="16" t="inlineStr">
+      <c r="E153" s="15" t="n">
+        <v>84</v>
+      </c>
+      <c r="F153" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -10127,7 +9431,7 @@
       <c r="O153" t="n">
         <v>-62</v>
       </c>
-      <c r="P153" s="16" t="inlineStr">
+      <c r="P153" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -10144,20 +9448,16 @@
           <t>2024-01-08</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>70週で終了</t>
-        </is>
+      <c r="C154" t="n">
+        <v>9</v>
       </c>
       <c r="D154" t="n">
         <v>70</v>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F154" s="14" t="inlineStr">
+      <c r="E154" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="F154" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -10189,7 +9489,7 @@
       <c r="O154" t="n">
         <v>-21</v>
       </c>
-      <c r="P154" s="14" t="inlineStr">
+      <c r="P154" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10206,20 +9506,16 @@
           <t>2024-01-08</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>103週で終了</t>
-        </is>
+      <c r="C155" t="n">
+        <v>8</v>
       </c>
       <c r="D155" t="n">
         <v>103</v>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F155" s="16" t="inlineStr">
+      <c r="E155" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="F155" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -10251,7 +9547,7 @@
       <c r="O155" t="n">
         <v>-68</v>
       </c>
-      <c r="P155" s="16" t="inlineStr">
+      <c r="P155" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -10268,20 +9564,16 @@
           <t>2024-01-08</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>54週で終了</t>
-        </is>
+      <c r="C156" t="n">
+        <v>5</v>
       </c>
       <c r="D156" t="n">
         <v>54</v>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F156" s="16" t="inlineStr">
+      <c r="E156" s="15" t="n">
+        <v>49</v>
+      </c>
+      <c r="F156" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -10313,7 +9605,7 @@
       <c r="O156" t="n">
         <v>-71</v>
       </c>
-      <c r="P156" s="16" t="inlineStr">
+      <c r="P156" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -10330,20 +9622,16 @@
           <t>2023-12-18</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>129週継続中</t>
-        </is>
+      <c r="C157" t="n">
+        <v>17</v>
       </c>
       <c r="D157" t="n">
         <v>129</v>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F157" s="14" t="inlineStr">
+      <c r="E157" s="15" t="n">
+        <v>112</v>
+      </c>
+      <c r="F157" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -10375,14 +9663,14 @@
       <c r="O157" t="n">
         <v>-71</v>
       </c>
-      <c r="P157" s="14" t="inlineStr">
+      <c r="P157" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="15" t="inlineStr">
+      <c r="A158" s="13" t="inlineStr">
         <is>
           <t>LスマスロモンキーターンＶ</t>
         </is>
@@ -10392,20 +9680,16 @@
           <t>2023-12-04</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>131週継続中</t>
-        </is>
+      <c r="C158" t="n">
+        <v>111</v>
       </c>
       <c r="D158" t="n">
         <v>131</v>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F158" s="14" t="inlineStr">
+      <c r="E158" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F158" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -10437,7 +9721,7 @@
       <c r="O158" t="n">
         <v>95</v>
       </c>
-      <c r="P158" s="14" t="inlineStr">
+      <c r="P158" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10454,20 +9738,16 @@
           <t>2023-12-04</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>131週継続中</t>
-        </is>
+      <c r="C159" t="n">
+        <v>11</v>
       </c>
       <c r="D159" t="n">
         <v>131</v>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F159" s="14" t="inlineStr">
+      <c r="E159" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="F159" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -10499,7 +9779,7 @@
       <c r="O159" t="n">
         <v>-35</v>
       </c>
-      <c r="P159" s="14" t="inlineStr">
+      <c r="P159" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10516,20 +9796,16 @@
           <t>2023-12-04</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>76週で終了</t>
-        </is>
+      <c r="C160" t="n">
+        <v>9</v>
       </c>
       <c r="D160" t="n">
         <v>76</v>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F160" s="14" t="inlineStr">
+      <c r="E160" s="15" t="n">
+        <v>67</v>
+      </c>
+      <c r="F160" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -10561,7 +9837,7 @@
       <c r="O160" t="n">
         <v>-42</v>
       </c>
-      <c r="P160" s="14" t="inlineStr">
+      <c r="P160" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10578,20 +9854,16 @@
           <t>2023-12-04</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>131週継続中</t>
-        </is>
+      <c r="C161" t="n">
+        <v>14</v>
       </c>
       <c r="D161" t="n">
         <v>131</v>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F161" s="14" t="inlineStr">
+      <c r="E161" s="15" t="n">
+        <v>117</v>
+      </c>
+      <c r="F161" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -10623,7 +9895,7 @@
       <c r="O161" t="n">
         <v>-40</v>
       </c>
-      <c r="P161" s="14" t="inlineStr">
+      <c r="P161" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10640,22 +9912,18 @@
           <t>2023-12-04</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>36週で終了</t>
-        </is>
-      </c>
-      <c r="D162" s="17" t="n">
+      <c r="C162" t="n">
+        <v>3</v>
+      </c>
+      <c r="D162" t="n">
         <v>36</v>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F162" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E162" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="F162" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -10685,7 +9953,7 @@
       <c r="O162" t="n">
         <v>-74</v>
       </c>
-      <c r="P162" s="13" t="inlineStr">
+      <c r="P162" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -10702,22 +9970,18 @@
           <t>2023-11-20</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>23週で終了</t>
-        </is>
-      </c>
-      <c r="D163" s="17" t="n">
+      <c r="C163" t="n">
+        <v>3</v>
+      </c>
+      <c r="D163" t="n">
         <v>23</v>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F163" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E163" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F163" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -10747,7 +10011,7 @@
       <c r="O163" t="n">
         <v>-59</v>
       </c>
-      <c r="P163" s="13" t="inlineStr">
+      <c r="P163" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -10764,20 +10028,16 @@
           <t>2023-11-06</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>135週継続中</t>
-        </is>
+      <c r="C164" t="n">
+        <v>10</v>
       </c>
       <c r="D164" t="n">
         <v>135</v>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F164" s="14" t="inlineStr">
+      <c r="E164" s="15" t="n">
+        <v>125</v>
+      </c>
+      <c r="F164" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -10809,7 +10069,7 @@
       <c r="O164" t="n">
         <v>-67</v>
       </c>
-      <c r="P164" s="14" t="inlineStr">
+      <c r="P164" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10826,22 +10086,18 @@
           <t>2023-11-06</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>50週で終了</t>
-        </is>
-      </c>
-      <c r="D165" s="17" t="n">
+      <c r="C165" t="n">
+        <v>2</v>
+      </c>
+      <c r="D165" t="n">
         <v>50</v>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F165" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E165" s="15" t="n">
+        <v>48</v>
+      </c>
+      <c r="F165" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -10871,7 +10127,7 @@
       <c r="O165" t="n">
         <v>-76</v>
       </c>
-      <c r="P165" s="13" t="inlineStr">
+      <c r="P165" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -10888,20 +10144,16 @@
           <t>2023-11-06</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>120週継続中</t>
-        </is>
+      <c r="C166" t="n">
+        <v>4</v>
       </c>
       <c r="D166" t="n">
         <v>120</v>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F166" s="14" t="inlineStr">
+      <c r="E166" s="15" t="n">
+        <v>116</v>
+      </c>
+      <c r="F166" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -10933,7 +10185,7 @@
       <c r="O166" t="n">
         <v>-48</v>
       </c>
-      <c r="P166" s="14" t="inlineStr">
+      <c r="P166" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -10950,22 +10202,18 @@
           <t>2023-11-06</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>57週で終了</t>
-        </is>
-      </c>
-      <c r="D167" s="17" t="n">
+      <c r="C167" t="n">
+        <v>5</v>
+      </c>
+      <c r="D167" t="n">
         <v>57</v>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F167" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E167" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="F167" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -10995,7 +10243,7 @@
       <c r="O167" t="n">
         <v>-60</v>
       </c>
-      <c r="P167" s="13" t="inlineStr">
+      <c r="P167" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -11012,22 +10260,18 @@
           <t>2023-10-02</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>36週で終了</t>
-        </is>
-      </c>
-      <c r="D168" s="17" t="n">
+      <c r="C168" t="n">
+        <v>2</v>
+      </c>
+      <c r="D168" t="n">
         <v>36</v>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F168" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E168" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="F168" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -11057,7 +10301,7 @@
       <c r="O168" t="n">
         <v>-70</v>
       </c>
-      <c r="P168" s="13" t="inlineStr">
+      <c r="P168" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -11074,20 +10318,16 @@
           <t>2023-10-02</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>108週で終了</t>
-        </is>
+      <c r="C169" t="n">
+        <v>9</v>
       </c>
       <c r="D169" t="n">
         <v>108</v>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F169" s="16" t="inlineStr">
+      <c r="E169" s="15" t="n">
+        <v>99</v>
+      </c>
+      <c r="F169" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -11119,7 +10359,7 @@
       <c r="O169" t="n">
         <v>-63</v>
       </c>
-      <c r="P169" s="16" t="inlineStr">
+      <c r="P169" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -11136,20 +10376,16 @@
           <t>2023-09-18</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>107週で終了</t>
-        </is>
+      <c r="C170" t="n">
+        <v>8</v>
       </c>
       <c r="D170" t="n">
         <v>107</v>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F170" s="16" t="inlineStr">
+      <c r="E170" s="15" t="n">
+        <v>99</v>
+      </c>
+      <c r="F170" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -11181,7 +10417,7 @@
       <c r="O170" t="n">
         <v>-42</v>
       </c>
-      <c r="P170" s="16" t="inlineStr">
+      <c r="P170" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -11198,20 +10434,16 @@
           <t>2023-09-18</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>142週継続中</t>
-        </is>
+      <c r="C171" t="n">
+        <v>12</v>
       </c>
       <c r="D171" t="n">
         <v>142</v>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F171" s="16" t="inlineStr">
+      <c r="E171" s="15" t="n">
+        <v>130</v>
+      </c>
+      <c r="F171" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -11243,7 +10475,7 @@
       <c r="O171" t="n">
         <v>-43</v>
       </c>
-      <c r="P171" s="16" t="inlineStr">
+      <c r="P171" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -11260,20 +10492,16 @@
           <t>2023-09-04</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>79週で終了</t>
-        </is>
+      <c r="C172" t="n">
+        <v>6</v>
       </c>
       <c r="D172" t="n">
         <v>79</v>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F172" s="16" t="inlineStr">
+      <c r="E172" s="15" t="n">
+        <v>73</v>
+      </c>
+      <c r="F172" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -11305,14 +10533,14 @@
       <c r="O172" t="n">
         <v>-54</v>
       </c>
-      <c r="P172" s="16" t="inlineStr">
+      <c r="P172" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="15" t="inlineStr">
+      <c r="A173" s="13" t="inlineStr">
         <is>
           <t>L戦国乙女４戦乱に閃く炯眼の軍師</t>
         </is>
@@ -11322,20 +10550,16 @@
           <t>2023-09-04</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>144週継続中</t>
-        </is>
+      <c r="C173" t="n">
+        <v>47</v>
       </c>
       <c r="D173" t="n">
         <v>144</v>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F173" s="14" t="inlineStr">
+      <c r="E173" s="15" t="n">
+        <v>97</v>
+      </c>
+      <c r="F173" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -11367,7 +10591,7 @@
       <c r="O173" t="n">
         <v>-24</v>
       </c>
-      <c r="P173" s="14" t="inlineStr">
+      <c r="P173" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -11384,20 +10608,16 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>146週継続中</t>
-        </is>
+      <c r="C174" t="n">
+        <v>15</v>
       </c>
       <c r="D174" t="n">
         <v>146</v>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F174" s="14" t="inlineStr">
+      <c r="E174" s="15" t="n">
+        <v>131</v>
+      </c>
+      <c r="F174" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -11429,7 +10649,7 @@
       <c r="O174" t="n">
         <v>-64</v>
       </c>
-      <c r="P174" s="14" t="inlineStr">
+      <c r="P174" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -11446,22 +10666,18 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>44週で終了</t>
-        </is>
-      </c>
-      <c r="D175" s="17" t="n">
+      <c r="C175" t="n">
+        <v>3</v>
+      </c>
+      <c r="D175" t="n">
         <v>44</v>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F175" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E175" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="F175" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -11491,7 +10707,7 @@
       <c r="O175" t="n">
         <v>-66</v>
       </c>
-      <c r="P175" s="13" t="inlineStr">
+      <c r="P175" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -11508,20 +10724,16 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>106週で終了</t>
-        </is>
+      <c r="C176" t="n">
+        <v>9</v>
       </c>
       <c r="D176" t="n">
         <v>106</v>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F176" s="14" t="inlineStr">
+      <c r="E176" s="15" t="n">
+        <v>97</v>
+      </c>
+      <c r="F176" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -11553,7 +10765,7 @@
       <c r="O176" t="n">
         <v>-45</v>
       </c>
-      <c r="P176" s="14" t="inlineStr">
+      <c r="P176" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -11570,20 +10782,16 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>100週で終了</t>
-        </is>
+      <c r="C177" t="n">
+        <v>9</v>
       </c>
       <c r="D177" t="n">
         <v>100</v>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F177" s="14" t="inlineStr">
+      <c r="E177" s="15" t="n">
+        <v>91</v>
+      </c>
+      <c r="F177" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -11615,7 +10823,7 @@
       <c r="O177" t="n">
         <v>-48</v>
       </c>
-      <c r="P177" s="14" t="inlineStr">
+      <c r="P177" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -11632,20 +10840,16 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>97週で終了</t>
-        </is>
+      <c r="C178" t="n">
+        <v>5</v>
       </c>
       <c r="D178" t="n">
         <v>97</v>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F178" s="16" t="inlineStr">
+      <c r="E178" s="15" t="n">
+        <v>92</v>
+      </c>
+      <c r="F178" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -11677,7 +10881,7 @@
       <c r="O178" t="n">
         <v>-83</v>
       </c>
-      <c r="P178" s="16" t="inlineStr">
+      <c r="P178" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -11694,20 +10898,16 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>153週継続中</t>
-        </is>
+      <c r="C179" t="n">
+        <v>89</v>
       </c>
       <c r="D179" t="n">
         <v>153</v>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F179" s="14" t="inlineStr">
+      <c r="E179" s="15" t="n">
+        <v>64</v>
+      </c>
+      <c r="F179" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -11739,7 +10939,7 @@
       <c r="O179" t="n">
         <v>-15</v>
       </c>
-      <c r="P179" s="14" t="inlineStr">
+      <c r="P179" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -11756,20 +10956,16 @@
           <t>2023-06-05</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>81週で終了</t>
-        </is>
+      <c r="C180" t="n">
+        <v>8</v>
       </c>
       <c r="D180" t="n">
         <v>81</v>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F180" s="14" t="inlineStr">
+      <c r="E180" s="15" t="n">
+        <v>73</v>
+      </c>
+      <c r="F180" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -11801,7 +10997,7 @@
       <c r="O180" t="n">
         <v>-70</v>
       </c>
-      <c r="P180" s="14" t="inlineStr">
+      <c r="P180" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -11818,22 +11014,18 @@
           <t>2023-06-05</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>60週で終了</t>
-        </is>
-      </c>
-      <c r="D181" s="17" t="n">
+      <c r="C181" t="n">
+        <v>4</v>
+      </c>
+      <c r="D181" t="n">
         <v>60</v>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F181" s="13" t="inlineStr">
-        <is>
-          <t>実質死亡(設置のみ)</t>
+      <c r="E181" s="15" t="n">
+        <v>56</v>
+      </c>
+      <c r="F181" s="11" t="inlineStr">
+        <is>
+          <t>実質死亡</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -11863,7 +11055,7 @@
       <c r="O181" t="n">
         <v>-69</v>
       </c>
-      <c r="P181" s="13" t="inlineStr">
+      <c r="P181" s="11" t="inlineStr">
         <is>
           <t>危険</t>
         </is>
@@ -11880,20 +11072,16 @@
           <t>2023-05-15</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>160週継続中</t>
-        </is>
+      <c r="C182" t="n">
+        <v>17</v>
       </c>
       <c r="D182" t="n">
         <v>160</v>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F182" s="16" t="inlineStr">
+      <c r="E182" s="15" t="n">
+        <v>143</v>
+      </c>
+      <c r="F182" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -11925,7 +11113,7 @@
       <c r="O182" t="n">
         <v>-71</v>
       </c>
-      <c r="P182" s="16" t="inlineStr">
+      <c r="P182" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -11942,20 +11130,16 @@
           <t>2023-05-08</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>161週継続中</t>
-        </is>
+      <c r="C183" t="n">
+        <v>36</v>
       </c>
       <c r="D183" t="n">
         <v>161</v>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F183" s="14" t="inlineStr">
+      <c r="E183" s="15" t="n">
+        <v>125</v>
+      </c>
+      <c r="F183" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -11987,7 +11171,7 @@
       <c r="O183" t="n">
         <v>-68</v>
       </c>
-      <c r="P183" s="14" t="inlineStr">
+      <c r="P183" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -12004,20 +11188,16 @@
           <t>2023-04-17</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>150週で終了</t>
-        </is>
+      <c r="C184" t="n">
+        <v>15</v>
       </c>
       <c r="D184" t="n">
         <v>150</v>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F184" s="16" t="inlineStr">
+      <c r="E184" s="15" t="n">
+        <v>135</v>
+      </c>
+      <c r="F184" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -12049,14 +11229,14 @@
       <c r="O184" t="n">
         <v>-70</v>
       </c>
-      <c r="P184" s="16" t="inlineStr">
+      <c r="P184" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="15" t="inlineStr">
+      <c r="A185" s="13" t="inlineStr">
         <is>
           <t>Lスマスロ北斗の拳</t>
         </is>
@@ -12066,20 +11246,16 @@
           <t>2023-04-03</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>166週継続中</t>
-        </is>
+      <c r="C185" t="n">
+        <v>88</v>
       </c>
       <c r="D185" t="n">
         <v>166</v>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F185" s="14" t="inlineStr">
+      <c r="E185" s="15" t="n">
+        <v>78</v>
+      </c>
+      <c r="F185" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -12111,7 +11287,7 @@
       <c r="O185" t="n">
         <v>-16</v>
       </c>
-      <c r="P185" s="14" t="inlineStr">
+      <c r="P185" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -12128,20 +11304,16 @@
           <t>2022-12-26</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>180週継続中</t>
-        </is>
+      <c r="C186" t="n">
+        <v>19</v>
       </c>
       <c r="D186" t="n">
         <v>180</v>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F186" s="14" t="inlineStr">
+      <c r="E186" s="15" t="n">
+        <v>161</v>
+      </c>
+      <c r="F186" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -12173,7 +11345,7 @@
       <c r="O186" t="n">
         <v>-80</v>
       </c>
-      <c r="P186" s="14" t="inlineStr">
+      <c r="P186" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -12190,20 +11362,16 @@
           <t>2022-12-26</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>43週で終了</t>
-        </is>
+      <c r="C187" t="n">
+        <v>2</v>
       </c>
       <c r="D187" t="n">
         <v>43</v>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F187" s="14" t="inlineStr">
+      <c r="E187" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="F187" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -12235,7 +11403,7 @@
       <c r="O187" t="n">
         <v>-61</v>
       </c>
-      <c r="P187" s="14" t="inlineStr">
+      <c r="P187" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
@@ -12252,20 +11420,16 @@
           <t>2022-12-26</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>108週で終了</t>
-        </is>
+      <c r="C188" t="n">
+        <v>9</v>
       </c>
       <c r="D188" t="n">
         <v>108</v>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="F188" s="16" t="inlineStr">
+      <c r="E188" s="15" t="n">
+        <v>99</v>
+      </c>
+      <c r="F188" s="14" t="inlineStr">
         <is>
           <t>微妙</t>
         </is>
@@ -12297,7 +11461,7 @@
       <c r="O188" t="n">
         <v>-77</v>
       </c>
-      <c r="P188" s="16" t="inlineStr">
+      <c r="P188" s="14" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -12314,20 +11478,16 @@
           <t>2022-12-26</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>180週継続中</t>
-        </is>
+      <c r="C189" t="n">
+        <v>25</v>
       </c>
       <c r="D189" t="n">
         <v>180</v>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>継続中</t>
-        </is>
-      </c>
-      <c r="F189" s="14" t="inlineStr">
+      <c r="E189" s="15" t="n">
+        <v>155</v>
+      </c>
+      <c r="F189" s="12" t="inlineStr">
         <is>
           <t>健全</t>
         </is>
@@ -12359,7 +11519,7 @@
       <c r="O189" t="n">
         <v>-42</v>
       </c>
-      <c r="P189" s="14" t="inlineStr">
+      <c r="P189" s="12" t="inlineStr">
         <is>
           <t>優秀</t>
         </is>
